--- a/Soft X-ray/Four-View/fiberPositions.xlsx
+++ b/Soft X-ray/Four-View/fiberPositions.xlsx
@@ -1,35 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shohgookazaki/Documents/GitHub/test-open/Soft X-ray/Four-View/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3581D5DB-81AD-524E-9F36-3767ACFAAEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F822E21-4F95-784B-A154-43E7FBDAE471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="16160" firstSheet="3" activeTab="16"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19120" firstSheet="7" activeTab="23"/>
   </bookViews>
   <sheets>
     <sheet name="230429" sheetId="16" r:id="rId1"/>
-    <sheet name="230829" sheetId="18" r:id="rId2"/>
-    <sheet name="230830" sheetId="15" r:id="rId3"/>
-    <sheet name="230921" sheetId="4" r:id="rId4"/>
-    <sheet name="230920_backup" sheetId="3" r:id="rId5"/>
-    <sheet name="230920_backup2" sheetId="5" r:id="rId6"/>
-    <sheet name="230721" sheetId="1" r:id="rId7"/>
-    <sheet name="230712" sheetId="2" r:id="rId8"/>
-    <sheet name="230920" sheetId="6" r:id="rId9"/>
-    <sheet name="231216" sheetId="13" r:id="rId10"/>
-    <sheet name="240111_backup" sheetId="8" r:id="rId11"/>
-    <sheet name="240111" sheetId="7" r:id="rId12"/>
-    <sheet name="240501" sheetId="9" r:id="rId13"/>
-    <sheet name="240621" sheetId="10" r:id="rId14"/>
-    <sheet name="240622" sheetId="11" r:id="rId15"/>
-    <sheet name="240828" sheetId="17" r:id="rId16"/>
-    <sheet name="241110" sheetId="20" r:id="rId17"/>
+    <sheet name="230826" sheetId="21" r:id="rId2"/>
+    <sheet name="230829" sheetId="18" r:id="rId3"/>
+    <sheet name="230830" sheetId="15" r:id="rId4"/>
+    <sheet name="230920" sheetId="6" r:id="rId5"/>
+    <sheet name="230921" sheetId="4" r:id="rId6"/>
+    <sheet name="230920_backup" sheetId="3" r:id="rId7"/>
+    <sheet name="230920_backup2" sheetId="5" r:id="rId8"/>
+    <sheet name="230721" sheetId="1" r:id="rId9"/>
+    <sheet name="230712" sheetId="2" r:id="rId10"/>
+    <sheet name="231216" sheetId="13" r:id="rId11"/>
+    <sheet name="240111_backup" sheetId="8" r:id="rId12"/>
+    <sheet name="240111" sheetId="7" r:id="rId13"/>
+    <sheet name="240501" sheetId="9" r:id="rId14"/>
+    <sheet name="240621" sheetId="10" r:id="rId15"/>
+    <sheet name="240622" sheetId="11" r:id="rId16"/>
+    <sheet name="240828" sheetId="17" r:id="rId17"/>
+    <sheet name="241110" sheetId="20" r:id="rId18"/>
+    <sheet name="241229" sheetId="22" r:id="rId19"/>
+    <sheet name="241230-case-I" sheetId="23" r:id="rId20"/>
+    <sheet name="241230" sheetId="24" r:id="rId21"/>
+    <sheet name="250125" sheetId="26" r:id="rId22"/>
+    <sheet name="250205" sheetId="25" r:id="rId23"/>
+    <sheet name="250206" sheetId="27" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
@@ -52,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="119" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="123" uniqueCount="23">
   <si>
     <t>center_X</t>
     <phoneticPr fontId="1"/>
@@ -1098,6 +1105,581 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A8B513D-DF9C-6D4B-8EB9-67E97D41F236}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="4" width="12.6640625" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1604.6029030107932</v>
+      </c>
+      <c r="D2">
+        <v>280.65774254218428</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1628.7162893371674</v>
+      </c>
+      <c r="D3">
+        <v>811.65681418393456</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1263</v>
+      </c>
+      <c r="D4">
+        <v>830</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1241</v>
+      </c>
+      <c r="D5">
+        <v>285</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>860.27323359172738</v>
+      </c>
+      <c r="D6">
+        <v>290.99912082838</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>885.96699056537875</v>
+      </c>
+      <c r="D7">
+        <v>834</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>506</v>
+      </c>
+      <c r="D8">
+        <v>842.45891560138898</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>481.40090797133456</v>
+      </c>
+      <c r="D9">
+        <v>299.58901290582963</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1606</v>
+      </c>
+      <c r="D10">
+        <v>425</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1620.9445240019663</v>
+      </c>
+      <c r="D11">
+        <v>959.47984336260345</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1256</v>
+      </c>
+      <c r="D12">
+        <v>974</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1237.2074574032038</v>
+      </c>
+      <c r="D13">
+        <v>431.50098570018065</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>852.36344463680052</v>
+      </c>
+      <c r="D14">
+        <v>437.74724778007908</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>882.53773646259197</v>
+      </c>
+      <c r="D15">
+        <v>981.00000000000011</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>500.64185533341998</v>
+      </c>
+      <c r="D16">
+        <v>989.32192413899827</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>474.89341345569784</v>
+      </c>
+      <c r="D17">
+        <v>448.84585525987632</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1467.5283069529205</v>
+      </c>
+      <c r="D18">
+        <v>279.48143931656074</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1489.5885413497574</v>
+      </c>
+      <c r="D19">
+        <v>813.23295593386445</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1117.0168346154469</v>
+      </c>
+      <c r="D20">
+        <v>829.28943124222167</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1093.2565289139898</v>
+      </c>
+      <c r="D21">
+        <v>282.76894231476359</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>710.50943405789167</v>
+      </c>
+      <c r="D22">
+        <v>291.00000000000006</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>739</v>
+      </c>
+      <c r="D23">
+        <v>831.51615876175674</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>358.00000000000006</v>
+      </c>
+      <c r="D24">
+        <v>836.56843813389787</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>335.52599426336445</v>
+      </c>
+      <c r="D25">
+        <v>300.52825243257473</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1464.0259861843795</v>
+      </c>
+      <c r="D26">
+        <v>421.85523734651008</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1482.3243065783529</v>
+      </c>
+      <c r="D27">
+        <v>959.6627249231442</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1111.9187726325586</v>
+      </c>
+      <c r="D28">
+        <v>970.49048829824119</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1091</v>
+      </c>
+      <c r="D29">
+        <v>425.00000000000006</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>707.47963024160333</v>
+      </c>
+      <c r="D30">
+        <v>434.47315275655529</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>737.00198143642649</v>
+      </c>
+      <c r="D31">
+        <v>977.26118909195395</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>361</v>
+      </c>
+      <c r="D32">
+        <v>982.99999999999989</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>329.35137120907115</v>
+      </c>
+      <c r="D33">
+        <v>444.80155102258573</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ABE9A69-76CE-E74C-8B0D-F73C461671C6}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1673,7 +2255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B4C6AA-75FF-D04D-AEB0-D50F87D3190D}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2250,576 +2832,575 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" customWidth="true"/>
-    <col min="3" max="3" width="13.28515625" customWidth="true"/>
-    <col min="5" max="5" width="5.42578125" customWidth="true"/>
-    <col min="2" max="2" width="7.140625" customWidth="true"/>
-    <col min="4" max="4" width="13.28515625" customWidth="true"/>
+    <col min="1" max="1" width="8.33203125" customWidth="true"/>
+    <col min="2" max="2" width="7.1640625" customWidth="true"/>
+    <col min="3" max="4" width="13.33203125" customWidth="true"/>
+    <col min="5" max="5" width="5.5" customWidth="true"/>
   </cols>
   <sheetData>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="0" t="s">
+      <c r="A1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>22</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
-      <c r="A2" s="0">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1634.5832371432114</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>883</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
-      <c r="A3" s="0">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0">
-        <v>2</v>
-      </c>
-      <c r="C3" s="0">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1632.4265443435393</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>348.1904554392429</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
-      <c r="A4" s="0">
-        <v>1</v>
-      </c>
-      <c r="B4" s="0">
-        <v>3</v>
-      </c>
-      <c r="C4" s="0">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <v>1264.2992618674946</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>339.8398448017395</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
-      <c r="A5" s="0">
-        <v>1</v>
-      </c>
-      <c r="B5" s="0">
-        <v>4</v>
-      </c>
-      <c r="C5" s="0">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>1272.4976351483458</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>884.50371781189858</v>
       </c>
-      <c r="E5" s="0">
+      <c r="E5">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
-      <c r="A6" s="0">
-        <v>1</v>
-      </c>
-      <c r="B6" s="0">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>896.0054514726379</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>886.00067032311472</v>
       </c>
-      <c r="E6" s="0">
+      <c r="E6">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
-      <c r="A7" s="0">
-        <v>1</v>
-      </c>
-      <c r="B7" s="0">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7">
         <v>884.39997528745789</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>338.15420968300811</v>
       </c>
-      <c r="E7" s="0">
+      <c r="E7">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
-      <c r="A8" s="0">
-        <v>1</v>
-      </c>
-      <c r="B8" s="0">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C8">
         <v>504</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>338</v>
       </c>
-      <c r="E8" s="0">
+      <c r="E8">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
-      <c r="A9" s="0">
-        <v>1</v>
-      </c>
-      <c r="B9" s="0">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C9">
         <v>515.458800788433</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>879.01899490184496</v>
       </c>
-      <c r="E9" s="0">
+      <c r="E9">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
-      <c r="A10" s="0">
-        <v>2</v>
-      </c>
-      <c r="B10" s="0">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>1619.4630275922909</v>
       </c>
-      <c r="D10" s="0">
+      <c r="D10">
         <v>1026.9493538404563</v>
       </c>
-      <c r="E10" s="0">
+      <c r="E10">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
-      <c r="A11" s="0">
-        <v>2</v>
-      </c>
-      <c r="B11" s="0">
-        <v>2</v>
-      </c>
-      <c r="C11" s="0">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
         <v>1615</v>
       </c>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>490.5340062361679</v>
       </c>
-      <c r="E11" s="0">
+      <c r="E11">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
-      <c r="A12" s="0">
-        <v>2</v>
-      </c>
-      <c r="B12" s="0">
-        <v>3</v>
-      </c>
-      <c r="C12" s="0">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <v>1246.8986241372759</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>489.98930052173625</v>
       </c>
-      <c r="E12" s="0">
+      <c r="E12">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
-      <c r="A13" s="0">
-        <v>2</v>
-      </c>
-      <c r="B13" s="0">
-        <v>4</v>
-      </c>
-      <c r="C13" s="0">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
         <v>1250.6105560128537</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D13">
         <v>1033.1994263586266</v>
       </c>
-      <c r="E13" s="0">
+      <c r="E13">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
-      <c r="A14" s="0">
-        <v>2</v>
-      </c>
-      <c r="B14" s="0">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14">
         <v>876.30901366636238</v>
       </c>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>1029.3414742931636</v>
       </c>
-      <c r="E14" s="0">
+      <c r="E14">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="0">
-        <v>2</v>
-      </c>
-      <c r="B15" s="0">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
         <v>6</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>863.11815473245372</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>482.1151043261882</v>
       </c>
-      <c r="E15" s="0">
+      <c r="E15">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="0">
-        <v>2</v>
-      </c>
-      <c r="B16" s="0">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>483.03760659484539</v>
       </c>
-      <c r="D16" s="0">
+      <c r="D16">
         <v>482.63522811947422</v>
       </c>
-      <c r="E16" s="0">
+      <c r="E16">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="0">
-        <v>2</v>
-      </c>
-      <c r="B17" s="0">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
         <v>8</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C17">
         <v>494.06667877099005</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>1024.4941583555815</v>
       </c>
-      <c r="E17" s="0">
+      <c r="E17">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="0">
-        <v>3</v>
-      </c>
-      <c r="B18" s="0">
-        <v>1</v>
-      </c>
-      <c r="C18" s="0">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
         <v>1479.4170525137188</v>
       </c>
-      <c r="D18" s="0">
+      <c r="D18">
         <v>878.80732756498946</v>
       </c>
-      <c r="E18" s="0">
+      <c r="E18">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
-      <c r="A19" s="0">
-        <v>3</v>
-      </c>
-      <c r="B19" s="0">
-        <v>2</v>
-      </c>
-      <c r="C19" s="0">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
         <v>1472</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D19">
         <v>339</v>
       </c>
-      <c r="E19" s="0">
+      <c r="E19">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="0">
-        <v>3</v>
-      </c>
-      <c r="B20" s="0">
-        <v>3</v>
-      </c>
-      <c r="C20" s="0">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
         <v>1098.9999999999998</v>
       </c>
-      <c r="D20" s="0">
+      <c r="D20">
         <v>333.46386067619034</v>
       </c>
-      <c r="E20" s="0">
+      <c r="E20">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
-      <c r="A21" s="0">
-        <v>3</v>
-      </c>
-      <c r="B21" s="0">
-        <v>4</v>
-      </c>
-      <c r="C21" s="0">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
         <v>1106.8380913459309</v>
       </c>
-      <c r="D21" s="0">
+      <c r="D21">
         <v>878.36948917416635</v>
       </c>
-      <c r="E21" s="0">
+      <c r="E21">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
-      <c r="A22" s="0">
-        <v>3</v>
-      </c>
-      <c r="B22" s="0">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
         <v>5</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C22">
         <v>730</v>
       </c>
-      <c r="D22" s="0">
+      <c r="D22">
         <v>875</v>
       </c>
-      <c r="E22" s="0">
+      <c r="E22">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
-      <c r="A23" s="0">
-        <v>3</v>
-      </c>
-      <c r="B23" s="0">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
         <v>6</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C23">
         <v>718.66826419851839</v>
       </c>
-      <c r="D23" s="0">
+      <c r="D23">
         <v>331.37423485472425</v>
       </c>
-      <c r="E23" s="0">
+      <c r="E23">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
-      <c r="A24" s="0">
-        <v>3</v>
-      </c>
-      <c r="B24" s="0">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
         <v>7</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C24">
         <v>338.1778550489546</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D24">
         <v>331.41781057527805</v>
       </c>
-      <c r="E24" s="0">
+      <c r="E24">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
-      <c r="A25" s="0">
-        <v>3</v>
-      </c>
-      <c r="B25" s="0">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
         <v>8</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C25">
         <v>348.66064541799346</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D25">
         <v>872.97155739522611</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E25">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
-      <c r="A26" s="0">
-        <v>4</v>
-      </c>
-      <c r="B26" s="0">
-        <v>1</v>
-      </c>
-      <c r="C26" s="0">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
         <v>1471.0269453062842</v>
       </c>
-      <c r="D26" s="0">
+      <c r="D26">
         <v>1014.9619501882065</v>
       </c>
-      <c r="E26" s="0">
+      <c r="E26">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
-      <c r="A27" s="0">
-        <v>4</v>
-      </c>
-      <c r="B27" s="0">
-        <v>2</v>
-      </c>
-      <c r="C27" s="0">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
         <v>1465</v>
       </c>
-      <c r="D27" s="0">
+      <c r="D27">
         <v>474</v>
       </c>
-      <c r="E27" s="0">
+      <c r="E27">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
-      <c r="A28" s="0">
-        <v>4</v>
-      </c>
-      <c r="B28" s="0">
-        <v>3</v>
-      </c>
-      <c r="C28" s="0">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
         <v>1092</v>
       </c>
-      <c r="D28" s="0">
+      <c r="D28">
         <v>472</v>
       </c>
-      <c r="E28" s="0">
+      <c r="E28">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
-      <c r="A29" s="0">
-        <v>4</v>
-      </c>
-      <c r="B29" s="0">
-        <v>4</v>
-      </c>
-      <c r="C29" s="0">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
         <v>1098.5015147541376</v>
       </c>
-      <c r="D29" s="0">
+      <c r="D29">
         <v>1017.4988351453728</v>
       </c>
-      <c r="E29" s="0">
+      <c r="E29">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="0">
-        <v>4</v>
-      </c>
-      <c r="B30" s="0">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
         <v>5</v>
       </c>
-      <c r="C30" s="0">
+      <c r="C30">
         <v>722.70855122616899</v>
       </c>
-      <c r="D30" s="0">
+      <c r="D30">
         <v>1015.2579986889109</v>
       </c>
-      <c r="E30" s="0">
+      <c r="E30">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
-      <c r="A31" s="0">
-        <v>4</v>
-      </c>
-      <c r="B31" s="0">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
         <v>6</v>
       </c>
-      <c r="C31" s="0">
+      <c r="C31">
         <v>707.00866303979069</v>
       </c>
-      <c r="D31" s="0">
+      <c r="D31">
         <v>468.17576007912305</v>
       </c>
-      <c r="E31" s="0">
+      <c r="E31">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
-      <c r="A32" s="0">
-        <v>4</v>
-      </c>
-      <c r="B32" s="0">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C32" s="0">
+      <c r="C32">
         <v>328.49685359317334</v>
       </c>
-      <c r="D32" s="0">
+      <c r="D32">
         <v>469.008965874051</v>
       </c>
-      <c r="E32" s="0">
+      <c r="E32">
         <v>65</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
-      <c r="A33" s="0">
-        <v>4</v>
-      </c>
-      <c r="B33" s="0">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
         <v>8</v>
       </c>
-      <c r="C33" s="0">
+      <c r="C33">
         <v>344.52202340700165</v>
       </c>
-      <c r="D33" s="0">
+      <c r="D33">
         <v>1006.9625696988209</v>
       </c>
-      <c r="E33" s="0">
+      <c r="E33">
         <v>65</v>
       </c>
     </row>
@@ -2829,7 +3410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3405,7 +3986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B96200FB-67F2-FE48-B485-4355BB1B4F4F}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3982,7 +4563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA00A1D1-EF52-DA4A-871D-DB1992668D0B}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4559,7 +5140,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D7F6DC-A464-BD4E-AA5D-734B14C371F3}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4595,10 +5176,10 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1631.7425030099457</v>
+        <v>1632.7425030099457</v>
       </c>
       <c r="D2">
-        <v>876.02871194456884</v>
+        <v>871.02871194456884</v>
       </c>
       <c r="E2">
         <v>65</v>
@@ -4612,10 +5193,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1622.4061483041658</v>
+        <v>1623.4061483041658</v>
       </c>
       <c r="D3">
-        <v>341.32671346786896</v>
+        <v>336.32671346786896</v>
       </c>
       <c r="E3">
         <v>65</v>
@@ -4629,10 +5210,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D4">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E4">
         <v>65</v>
@@ -4646,10 +5227,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>1263.520209029972</v>
+        <v>1264.520209029972</v>
       </c>
       <c r="D5">
-        <v>879.01460290365162</v>
+        <v>874.01460290365162</v>
       </c>
       <c r="E5">
         <v>65</v>
@@ -4663,10 +5244,10 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>891.62459762139895</v>
+        <v>892.62459762139895</v>
       </c>
       <c r="D6">
-        <v>879.04376388709545</v>
+        <v>874.04376388709545</v>
       </c>
       <c r="E6">
         <v>65</v>
@@ -4680,10 +5261,10 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>875.28458590452396</v>
+        <v>876.28458590452396</v>
       </c>
       <c r="D7">
-        <v>333.24413555490423</v>
+        <v>328.24413555490423</v>
       </c>
       <c r="E7">
         <v>65</v>
@@ -4697,10 +5278,10 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>496.83493585304365</v>
+        <v>497.83493585304365</v>
       </c>
       <c r="D8">
-        <v>332.79972769377798</v>
+        <v>327.79972769377798</v>
       </c>
       <c r="E8">
         <v>65</v>
@@ -4714,10 +5295,10 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>504.0101420458949</v>
+        <v>505.0101420458949</v>
       </c>
       <c r="D9">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="E9">
         <v>65</v>
@@ -5003,10 +5584,10 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="D26">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="E26">
         <v>65</v>
@@ -5020,10 +5601,10 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>1466.3355062255928</v>
+        <v>1469.3355062255928</v>
       </c>
       <c r="D27">
-        <v>466.68324673024046</v>
+        <v>468.68324673024046</v>
       </c>
       <c r="E27">
         <v>65</v>
@@ -5037,10 +5618,10 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="D28">
-        <v>464.06282172105097</v>
+        <v>466.06282172105097</v>
       </c>
       <c r="E28">
         <v>65</v>
@@ -5054,10 +5635,10 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>1101.0510306101908</v>
+        <v>1104.0510306101908</v>
       </c>
       <c r="D29">
-        <v>1009.2580222016863</v>
+        <v>1011.2580222016863</v>
       </c>
       <c r="E29">
         <v>65</v>
@@ -5071,10 +5652,10 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>727.28422113454724</v>
+        <v>730.28422113454724</v>
       </c>
       <c r="D30">
-        <v>1005.2802447597348</v>
+        <v>1007.2802447597348</v>
       </c>
       <c r="E30">
         <v>65</v>
@@ -5088,10 +5669,10 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>709.43600904846016</v>
+        <v>712.43600904846016</v>
       </c>
       <c r="D31">
-        <v>463.80569376586431</v>
+        <v>465.80569376586431</v>
       </c>
       <c r="E31">
         <v>65</v>
@@ -5105,10 +5686,10 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>332.48909359995025</v>
+        <v>335.48909359995025</v>
       </c>
       <c r="D32">
-        <v>463.47228629221291</v>
+        <v>465.47228629221291</v>
       </c>
       <c r="E32">
         <v>65</v>
@@ -5122,10 +5703,10 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>348.68442286943787</v>
+        <v>351.68442286943787</v>
       </c>
       <c r="D33">
-        <v>1000.3292348100124</v>
+        <v>1002.3292348100124</v>
       </c>
       <c r="E33">
         <v>65</v>
@@ -5136,16 +5717,3783 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17488004-B21B-E446-814B-138ED2231A25}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="true"/>
+    <col min="2" max="2" width="7.1640625" customWidth="true"/>
+    <col min="3" max="4" width="13.33203125" customWidth="true"/>
+    <col min="5" max="5" width="5.5" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1631.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>856.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1622.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>321.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1256</v>
+      </c>
+      <c r="D4">
+        <v>316</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1263.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>859.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>891.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>859.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>875.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>313.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>496.83493585304365</v>
+      </c>
+      <c r="D8">
+        <v>312.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>504.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>857</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1482.3846762361873</v>
+      </c>
+      <c r="D10">
+        <v>871.182620379632</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1471.7054596333444</v>
+      </c>
+      <c r="D11">
+        <v>330.98346611431509</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1099.5063568822814</v>
+      </c>
+      <c r="D12">
+        <v>330.46121207422669</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1108.5494197876064</v>
+      </c>
+      <c r="D13">
+        <v>870</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>732.37055943669645</v>
+      </c>
+      <c r="D14">
+        <v>871.87694241073473</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>717</v>
+      </c>
+      <c r="D15">
+        <v>329</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>340.59998908096031</v>
+      </c>
+      <c r="D16">
+        <v>329.18836282597613</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>350.52787151824356</v>
+      </c>
+      <c r="D17">
+        <v>867.00000000000011</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1668.8746535296575</v>
+      </c>
+      <c r="D18">
+        <v>1114.0845244489574</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1665.9734582162946</v>
+      </c>
+      <c r="D19">
+        <v>578</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1296.9999999999998</v>
+      </c>
+      <c r="D20">
+        <v>575</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1301.3493827116019</v>
+      </c>
+      <c r="D21">
+        <v>1120.3012493082249</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>929.52484896262547</v>
+      </c>
+      <c r="D22">
+        <v>1121.5206728589721</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>914.4076645902577</v>
+      </c>
+      <c r="D23">
+        <v>571.7948190298614</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>532.46508385439233</v>
+      </c>
+      <c r="D24">
+        <v>574.4455764172319</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>547</v>
+      </c>
+      <c r="D25">
+        <v>1114.0980695012088</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1471</v>
+      </c>
+      <c r="D26">
+        <v>996</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1463.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>454.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1091</v>
+      </c>
+      <c r="D28">
+        <v>452.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1098.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>997.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>724.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>993.28024475973484</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>706.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>451.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>329.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>451.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>345.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>988.32923481001239</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F69764-960C-0444-9962-FAA80943B317}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="true"/>
+    <col min="2" max="2" width="7.1640625" customWidth="true"/>
+    <col min="3" max="4" width="13.33203125" customWidth="true"/>
+    <col min="5" max="5" width="5.5" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1633.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>914.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1624.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>379.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1258</v>
+      </c>
+      <c r="D4">
+        <v>374</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1265.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>917.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>893.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>917.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>877.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>371.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>498.83493585304365</v>
+      </c>
+      <c r="D8">
+        <v>370.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>506.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>915</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1477.3846762361873</v>
+      </c>
+      <c r="D10">
+        <v>902.182620379632</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1466.7054596333444</v>
+      </c>
+      <c r="D11">
+        <v>361.98346611431509</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1094.5063568822814</v>
+      </c>
+      <c r="D12">
+        <v>361.46121207422669</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1103.5494197876064</v>
+      </c>
+      <c r="D13">
+        <v>901</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>727.37055943669645</v>
+      </c>
+      <c r="D14">
+        <v>902.87694241073473</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>712</v>
+      </c>
+      <c r="D15">
+        <v>360</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>335.59998908096031</v>
+      </c>
+      <c r="D16">
+        <v>360.18836282597613</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>345.52787151824356</v>
+      </c>
+      <c r="D17">
+        <v>898.00000000000011</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1673.8746535296575</v>
+      </c>
+      <c r="D18">
+        <v>1104.0845244489574</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1670.9734582162946</v>
+      </c>
+      <c r="D19">
+        <v>568</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1301.9999999999998</v>
+      </c>
+      <c r="D20">
+        <v>565</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1306.3493827116019</v>
+      </c>
+      <c r="D21">
+        <v>1110.3012493082249</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>934.52484896262547</v>
+      </c>
+      <c r="D22">
+        <v>1111.5206728589721</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>919.4076645902577</v>
+      </c>
+      <c r="D23">
+        <v>561.7948190298614</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>537.46508385439233</v>
+      </c>
+      <c r="D24">
+        <v>564.4455764172319</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>552</v>
+      </c>
+      <c r="D25">
+        <v>1104.0980695012088</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1477</v>
+      </c>
+      <c r="D26">
+        <v>1036</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1469.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>494.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1097</v>
+      </c>
+      <c r="D28">
+        <v>492.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1104.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>1037.2580222016863</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>730.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>1033.2802447597348</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>712.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>491.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>335.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>491.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>351.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>1028.3292348100124</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9609A55A-41FF-2148-866A-D8873CA10C1C}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="true"/>
+    <col min="2" max="2" width="7.1640625" customWidth="true"/>
+    <col min="3" max="4" width="13.33203125" customWidth="true"/>
+    <col min="5" max="5" width="5.5" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>1278</v>
+      </c>
+      <c r="D2">
+        <v>349</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>1285.520209029972</v>
+      </c>
+      <c r="D3">
+        <v>892.01460290365162</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>744.37055943669645</v>
+      </c>
+      <c r="D4">
+        <v>881.87694241073473</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>729</v>
+      </c>
+      <c r="D5">
+        <v>339</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1332.9999999999998</v>
+      </c>
+      <c r="D6">
+        <v>466</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>1337.3493827116019</v>
+      </c>
+      <c r="D7">
+        <v>1011.3012493082249</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>751.28422113454724</v>
+      </c>
+      <c r="D8">
+        <v>1015.2802447597348</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>733.43600904846016</v>
+      </c>
+      <c r="D9">
+        <v>473.80569376586431</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>1111.5063568822814</v>
+      </c>
+      <c r="D10">
+        <v>340.46121207422669</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>1120.5494197876064</v>
+      </c>
+      <c r="D11">
+        <v>880</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>352.59998908096031</v>
+      </c>
+      <c r="D12">
+        <v>339.18836282597613</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>362.52787151824356</v>
+      </c>
+      <c r="D13">
+        <v>877.00000000000011</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>1118</v>
+      </c>
+      <c r="D14">
+        <v>474.06282172105097</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>1125.0510306101908</v>
+      </c>
+      <c r="D15">
+        <v>1019.2580222016863</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>356.48909359995025</v>
+      </c>
+      <c r="D16">
+        <v>473.47228629221291</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>4</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>372.68442286943787</v>
+      </c>
+      <c r="D17">
+        <v>1010.3292348100124</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E529F6-9DED-134C-8281-CEF3CC322206}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="true"/>
+    <col min="2" max="2" width="7.1640625" customWidth="true"/>
+    <col min="3" max="4" width="13.33203125" customWidth="true"/>
+    <col min="5" max="5" width="5.5" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1615.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>909.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1606.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>374.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1240</v>
+      </c>
+      <c r="D4">
+        <v>369</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1247.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>912.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>875.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>912.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>859.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>366.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>480.83493585304365</v>
+      </c>
+      <c r="D8">
+        <v>365.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>488.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>910</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1616.8746535296575</v>
+      </c>
+      <c r="D10">
+        <v>1113.0845244489574</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1613.9734582162946</v>
+      </c>
+      <c r="D11">
+        <v>577</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1244.9999999999998</v>
+      </c>
+      <c r="D12">
+        <v>574</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1249.3493827116019</v>
+      </c>
+      <c r="D13">
+        <v>1119.3012493082249</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>877.52484896262547</v>
+      </c>
+      <c r="D14">
+        <v>1120.5206728589721</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>862.4076645902577</v>
+      </c>
+      <c r="D15">
+        <v>570.7948190298614</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>480.46508385439239</v>
+      </c>
+      <c r="D16">
+        <v>573.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>494.99999999999994</v>
+      </c>
+      <c r="D17">
+        <v>1113.0980695012088</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1485.3846762361873</v>
+      </c>
+      <c r="D18">
+        <v>898.182620379632</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1474.7054596333444</v>
+      </c>
+      <c r="D19">
+        <v>357.98346611431509</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1102.5063568822814</v>
+      </c>
+      <c r="D20">
+        <v>357.46121207422669</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1111.5494197876064</v>
+      </c>
+      <c r="D21">
+        <v>897</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>735.37055943669645</v>
+      </c>
+      <c r="D22">
+        <v>898.87694241073473</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>720</v>
+      </c>
+      <c r="D23">
+        <v>356</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>343.59998908096031</v>
+      </c>
+      <c r="D24">
+        <v>356.18836282597613</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>353.52787151824356</v>
+      </c>
+      <c r="D25">
+        <v>894.00000000000011</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1480</v>
+      </c>
+      <c r="D26">
+        <v>1030</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1478.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>489.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1097</v>
+      </c>
+      <c r="D28">
+        <v>486.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1110.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>1028.2580222016863</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>731.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>1025.2802447597348</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>718.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>483.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>336.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>483.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>356.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>1022.3292348100124</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5430EBD-D9FC-C84A-AD7C-66CACE71C5DF}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="true"/>
+    <col min="2" max="2" width="7.1640625" customWidth="true"/>
+    <col min="3" max="4" width="13.33203125" customWidth="true"/>
+    <col min="5" max="5" width="5.5" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1615.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>909.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1606.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>374.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1240</v>
+      </c>
+      <c r="D4">
+        <v>369</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1247.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>912.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>875.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>912.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>859.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>366.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>480.83493585304365</v>
+      </c>
+      <c r="D8">
+        <v>365.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>488.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>910</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1616.8746535296575</v>
+      </c>
+      <c r="D10">
+        <v>1113.0845244489574</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1613.9734582162946</v>
+      </c>
+      <c r="D11">
+        <v>577</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1244.9999999999998</v>
+      </c>
+      <c r="D12">
+        <v>574</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1249.3493827116019</v>
+      </c>
+      <c r="D13">
+        <v>1119.3012493082249</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>877.52484896262547</v>
+      </c>
+      <c r="D14">
+        <v>1120.5206728589721</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>862.4076645902577</v>
+      </c>
+      <c r="D15">
+        <v>570.7948190298614</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>480.46508385439239</v>
+      </c>
+      <c r="D16">
+        <v>573.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>494.99999999999994</v>
+      </c>
+      <c r="D17">
+        <v>1113.0980695012088</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1485.3846762361873</v>
+      </c>
+      <c r="D18">
+        <v>898.182620379632</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1474.7054596333444</v>
+      </c>
+      <c r="D19">
+        <v>357.98346611431509</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1102.5063568822814</v>
+      </c>
+      <c r="D20">
+        <v>357.46121207422669</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1111.5494197876064</v>
+      </c>
+      <c r="D21">
+        <v>897</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>735.37055943669645</v>
+      </c>
+      <c r="D22">
+        <v>898.87694241073473</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>720</v>
+      </c>
+      <c r="D23">
+        <v>356</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>343.59998908096031</v>
+      </c>
+      <c r="D24">
+        <v>356.18836282597613</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>353.52787151824356</v>
+      </c>
+      <c r="D25">
+        <v>894.00000000000011</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1479</v>
+      </c>
+      <c r="D26">
+        <v>1034</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1477.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>493.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1096</v>
+      </c>
+      <c r="D28">
+        <v>490.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1109.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>1032.2580222016863</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>730.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>1029.2802447597348</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>717.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>487.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>335.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>487.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>355.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>1026.3292348100124</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBDCD85-D70E-BC4D-BDB7-526A457D2270}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="true"/>
+    <col min="2" max="2" width="7.1640625" customWidth="true"/>
+    <col min="3" max="4" width="13.33203125" customWidth="true"/>
+    <col min="5" max="5" width="5.5" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1615.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>909.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1606.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>374.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1240</v>
+      </c>
+      <c r="D4">
+        <v>369</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1247.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>912.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>875.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>912.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>859.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>366.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>480.83493585304365</v>
+      </c>
+      <c r="D8">
+        <v>365.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>488.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>910</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1485.3846762361873</v>
+      </c>
+      <c r="D10">
+        <v>898.182620379632</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1474.7054596333444</v>
+      </c>
+      <c r="D11">
+        <v>357.98346611431509</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1102.5063568822814</v>
+      </c>
+      <c r="D12">
+        <v>357.46121207422669</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1111.5494197876064</v>
+      </c>
+      <c r="D13">
+        <v>897</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>735.37055943669645</v>
+      </c>
+      <c r="D14">
+        <v>898.87694241073473</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>720</v>
+      </c>
+      <c r="D15">
+        <v>356</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>343.59998908096031</v>
+      </c>
+      <c r="D16">
+        <v>356.18836282597613</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>353.52787151824356</v>
+      </c>
+      <c r="D17">
+        <v>894.00000000000011</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1616.8746535296575</v>
+      </c>
+      <c r="D18">
+        <v>1113.0845244489574</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1613.9734582162946</v>
+      </c>
+      <c r="D19">
+        <v>577</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1244.9999999999998</v>
+      </c>
+      <c r="D20">
+        <v>574</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1249.3493827116019</v>
+      </c>
+      <c r="D21">
+        <v>1119.3012493082249</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>877.52484896262547</v>
+      </c>
+      <c r="D22">
+        <v>1120.5206728589721</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>862.4076645902577</v>
+      </c>
+      <c r="D23">
+        <v>570.7948190298614</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>480.46508385439239</v>
+      </c>
+      <c r="D24">
+        <v>573.4455764172319</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>494.99999999999994</v>
+      </c>
+      <c r="D25">
+        <v>1113.0980695012088</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1479</v>
+      </c>
+      <c r="D26">
+        <v>1037</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1477.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>496.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1096</v>
+      </c>
+      <c r="D28">
+        <v>493.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1109.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>1035.2580222016863</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>730.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>1032.2802447597348</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>717.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>490.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>335.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>490.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>355.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>1029.3292348100124</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35AB823B-EE8B-884B-8078-DB714A06E485}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="true"/>
+    <col min="2" max="2" width="7.1640625" customWidth="true"/>
+    <col min="3" max="4" width="13.33203125" customWidth="true"/>
+    <col min="5" max="5" width="5.5" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1620.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>902.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1611.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>367.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1245</v>
+      </c>
+      <c r="D4">
+        <v>362</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1252.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>905.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>880.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>905.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>864.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>359.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>485.83493585304365</v>
+      </c>
+      <c r="D8">
+        <v>358.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>493.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>903</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1485.3846762361873</v>
+      </c>
+      <c r="D10">
+        <v>898.182620379632</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1474.7054596333444</v>
+      </c>
+      <c r="D11">
+        <v>357.98346611431509</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1102.5063568822814</v>
+      </c>
+      <c r="D12">
+        <v>357.46121207422669</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1111.5494197876064</v>
+      </c>
+      <c r="D13">
+        <v>897</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>735.37055943669645</v>
+      </c>
+      <c r="D14">
+        <v>898.87694241073473</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>720</v>
+      </c>
+      <c r="D15">
+        <v>356</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>343.59998908096031</v>
+      </c>
+      <c r="D16">
+        <v>356.18836282597613</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>353.52787151824356</v>
+      </c>
+      <c r="D17">
+        <v>894.00000000000011</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1625.8746535296575</v>
+      </c>
+      <c r="D18">
+        <v>1106.0845244489574</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1622.9734582162946</v>
+      </c>
+      <c r="D19">
+        <v>570</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1253.9999999999998</v>
+      </c>
+      <c r="D20">
+        <v>567</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1258.3493827116019</v>
+      </c>
+      <c r="D21">
+        <v>1112.3012493082249</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>886.52484896262547</v>
+      </c>
+      <c r="D22">
+        <v>1113.5206728589721</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>871.4076645902577</v>
+      </c>
+      <c r="D23">
+        <v>563.7948190298614</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>489.46508385439239</v>
+      </c>
+      <c r="D24">
+        <v>566.4455764172319</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>503.99999999999994</v>
+      </c>
+      <c r="D25">
+        <v>1106.0980695012088</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1488</v>
+      </c>
+      <c r="D26">
+        <v>1030</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1486.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>489.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1105</v>
+      </c>
+      <c r="D28">
+        <v>486.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1118.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>1028.2580222016863</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>739.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>1025.2802447597348</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>726.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>483.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>344.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>483.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>364.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>1022.3292348100124</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10ED578-1041-AE4A-92E3-D474DE915247}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="true"/>
     <col min="2" max="2" width="7.140625" customWidth="true"/>
     <col min="3" max="3" width="13.28515625" customWidth="true"/>
+    <col min="5" max="5" width="5.42578125" customWidth="true"/>
     <col min="4" max="4" width="13.28515625" customWidth="true"/>
-    <col min="5" max="5" width="5.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
@@ -5173,10 +9521,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="0">
-        <v>1631.7425030099457</v>
+        <v>1620.7425030099457</v>
       </c>
       <c r="D2" s="0">
-        <v>856.02871194456884</v>
+        <v>912.02871194456884</v>
       </c>
       <c r="E2" s="0">
         <v>65</v>
@@ -5190,10 +9538,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="0">
-        <v>1622.4061483041658</v>
+        <v>1611.4061483041658</v>
       </c>
       <c r="D3" s="0">
-        <v>321.32671346786896</v>
+        <v>377.32671346786896</v>
       </c>
       <c r="E3" s="0">
         <v>65</v>
@@ -5207,10 +9555,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="0">
-        <v>1256</v>
+        <v>1245</v>
       </c>
       <c r="D4" s="0">
-        <v>316</v>
+        <v>372</v>
       </c>
       <c r="E4" s="0">
         <v>65</v>
@@ -5224,10 +9572,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="0">
-        <v>1263.520209029972</v>
+        <v>1252.520209029972</v>
       </c>
       <c r="D5" s="0">
-        <v>859.01460290365162</v>
+        <v>915.01460290365162</v>
       </c>
       <c r="E5" s="0">
         <v>65</v>
@@ -5241,10 +9589,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="0">
-        <v>891.62459762139895</v>
+        <v>880.62459762139895</v>
       </c>
       <c r="D6" s="0">
-        <v>859.04376388709545</v>
+        <v>915.04376388709545</v>
       </c>
       <c r="E6" s="0">
         <v>65</v>
@@ -5258,10 +9606,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="0">
-        <v>875.28458590452396</v>
+        <v>864.28458590452396</v>
       </c>
       <c r="D7" s="0">
-        <v>313.24413555490423</v>
+        <v>369.24413555490423</v>
       </c>
       <c r="E7" s="0">
         <v>65</v>
@@ -5275,10 +9623,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="0">
-        <v>496.83493585304365</v>
+        <v>485.83493585304365</v>
       </c>
       <c r="D8" s="0">
-        <v>312.79972769377798</v>
+        <v>368.79972769377798</v>
       </c>
       <c r="E8" s="0">
         <v>65</v>
@@ -5292,10 +9640,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="0">
-        <v>504.0101420458949</v>
+        <v>493.0101420458949</v>
       </c>
       <c r="D9" s="0">
-        <v>857</v>
+        <v>913</v>
       </c>
       <c r="E9" s="0">
         <v>65</v>
@@ -5309,10 +9657,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="0">
-        <v>1482.3846762361873</v>
+        <v>1485.3846762361873</v>
       </c>
       <c r="D10" s="0">
-        <v>871.182620379632</v>
+        <v>898.182620379632</v>
       </c>
       <c r="E10" s="0">
         <v>65</v>
@@ -5326,10 +9674,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="0">
-        <v>1471.7054596333444</v>
+        <v>1474.7054596333444</v>
       </c>
       <c r="D11" s="0">
-        <v>330.98346611431509</v>
+        <v>357.98346611431509</v>
       </c>
       <c r="E11" s="0">
         <v>65</v>
@@ -5343,10 +9691,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="0">
-        <v>1099.5063568822814</v>
+        <v>1102.5063568822814</v>
       </c>
       <c r="D12" s="0">
-        <v>330.46121207422669</v>
+        <v>357.46121207422669</v>
       </c>
       <c r="E12" s="0">
         <v>65</v>
@@ -5360,10 +9708,10 @@
         <v>4</v>
       </c>
       <c r="C13" s="0">
-        <v>1108.5494197876064</v>
+        <v>1111.5494197876064</v>
       </c>
       <c r="D13" s="0">
-        <v>870</v>
+        <v>897</v>
       </c>
       <c r="E13" s="0">
         <v>65</v>
@@ -5377,10 +9725,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="0">
-        <v>732.37055943669645</v>
+        <v>735.37055943669645</v>
       </c>
       <c r="D14" s="0">
-        <v>871.87694241073473</v>
+        <v>898.87694241073473</v>
       </c>
       <c r="E14" s="0">
         <v>65</v>
@@ -5394,10 +9742,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="0">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D15" s="0">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="E15" s="0">
         <v>65</v>
@@ -5411,10 +9759,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="0">
-        <v>340.59998908096031</v>
+        <v>343.59998908096031</v>
       </c>
       <c r="D16" s="0">
-        <v>329.18836282597613</v>
+        <v>356.18836282597613</v>
       </c>
       <c r="E16" s="0">
         <v>65</v>
@@ -5428,10 +9776,10 @@
         <v>8</v>
       </c>
       <c r="C17" s="0">
-        <v>350.52787151824356</v>
+        <v>353.52787151824356</v>
       </c>
       <c r="D17" s="0">
-        <v>867.00000000000011</v>
+        <v>894.00000000000011</v>
       </c>
       <c r="E17" s="0">
         <v>65</v>
@@ -5445,10 +9793,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="0">
-        <v>1668.8746535296575</v>
+        <v>1625.8746535296575</v>
       </c>
       <c r="D18" s="0">
-        <v>1114.0845244489574</v>
+        <v>1106.0845244489574</v>
       </c>
       <c r="E18" s="0">
         <v>65</v>
@@ -5462,10 +9810,10 @@
         <v>2</v>
       </c>
       <c r="C19" s="0">
-        <v>1665.9734582162946</v>
+        <v>1622.9734582162946</v>
       </c>
       <c r="D19" s="0">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="E19" s="0">
         <v>65</v>
@@ -5479,10 +9827,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="0">
-        <v>1296.9999999999998</v>
+        <v>1253.9999999999998</v>
       </c>
       <c r="D20" s="0">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="E20" s="0">
         <v>65</v>
@@ -5496,10 +9844,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="0">
-        <v>1301.3493827116019</v>
+        <v>1258.3493827116019</v>
       </c>
       <c r="D21" s="0">
-        <v>1120.3012493082249</v>
+        <v>1112.3012493082249</v>
       </c>
       <c r="E21" s="0">
         <v>65</v>
@@ -5513,10 +9861,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="0">
-        <v>929.52484896262547</v>
+        <v>886.52484896262547</v>
       </c>
       <c r="D22" s="0">
-        <v>1121.5206728589721</v>
+        <v>1113.5206728589721</v>
       </c>
       <c r="E22" s="0">
         <v>65</v>
@@ -5530,10 +9878,10 @@
         <v>6</v>
       </c>
       <c r="C23" s="0">
-        <v>914.4076645902577</v>
+        <v>871.4076645902577</v>
       </c>
       <c r="D23" s="0">
-        <v>571.7948190298614</v>
+        <v>563.7948190298614</v>
       </c>
       <c r="E23" s="0">
         <v>65</v>
@@ -5547,10 +9895,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="0">
-        <v>532.46508385439233</v>
+        <v>489.46508385439239</v>
       </c>
       <c r="D24" s="0">
-        <v>574.4455764172319</v>
+        <v>566.4455764172319</v>
       </c>
       <c r="E24" s="0">
         <v>65</v>
@@ -5564,10 +9912,10 @@
         <v>8</v>
       </c>
       <c r="C25" s="0">
-        <v>547</v>
+        <v>503.99999999999994</v>
       </c>
       <c r="D25" s="0">
-        <v>1114.0980695012088</v>
+        <v>1106.0980695012088</v>
       </c>
       <c r="E25" s="0">
         <v>65</v>
@@ -5581,10 +9929,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="0">
-        <v>1471</v>
+        <v>1484</v>
       </c>
       <c r="D26" s="0">
-        <v>996</v>
+        <v>1040</v>
       </c>
       <c r="E26" s="0">
         <v>65</v>
@@ -5598,10 +9946,10 @@
         <v>2</v>
       </c>
       <c r="C27" s="0">
-        <v>1463.3355062255928</v>
+        <v>1482.3355062255928</v>
       </c>
       <c r="D27" s="0">
-        <v>454.68324673024046</v>
+        <v>499.68324673024046</v>
       </c>
       <c r="E27" s="0">
         <v>65</v>
@@ -5615,10 +9963,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="0">
-        <v>1091</v>
+        <v>1101</v>
       </c>
       <c r="D28" s="0">
-        <v>452.06282172105097</v>
+        <v>496.06282172105097</v>
       </c>
       <c r="E28" s="0">
         <v>65</v>
@@ -5632,10 +9980,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="0">
-        <v>1098.0510306101908</v>
+        <v>1114.0510306101908</v>
       </c>
       <c r="D29" s="0">
-        <v>997.25802220168634</v>
+        <v>1038.2580222016863</v>
       </c>
       <c r="E29" s="0">
         <v>65</v>
@@ -5649,10 +9997,10 @@
         <v>5</v>
       </c>
       <c r="C30" s="0">
-        <v>724.28422113454724</v>
+        <v>735.28422113454724</v>
       </c>
       <c r="D30" s="0">
-        <v>993.28024475973484</v>
+        <v>1035.2802447597348</v>
       </c>
       <c r="E30" s="0">
         <v>65</v>
@@ -5666,10 +10014,10 @@
         <v>6</v>
       </c>
       <c r="C31" s="0">
-        <v>706.43600904846016</v>
+        <v>722.43600904846016</v>
       </c>
       <c r="D31" s="0">
-        <v>451.80569376586431</v>
+        <v>493.80569376586431</v>
       </c>
       <c r="E31" s="0">
         <v>65</v>
@@ -5683,10 +10031,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="0">
-        <v>329.48909359995025</v>
+        <v>340.48909359995025</v>
       </c>
       <c r="D32" s="0">
-        <v>451.47228629221291</v>
+        <v>493.47228629221291</v>
       </c>
       <c r="E32" s="0">
         <v>65</v>
@@ -5700,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="C33" s="0">
-        <v>345.68442286943787</v>
+        <v>360.68442286943787</v>
       </c>
       <c r="D33" s="0">
-        <v>988.32923481001239</v>
+        <v>1032.3292348100124</v>
       </c>
       <c r="E33" s="0">
         <v>65</v>
@@ -5714,7 +10062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE73315-C7F9-A74D-8A67-278E0C929C6C}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -6291,7 +10639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82059635-BEA6-F747-8536-EA5A758DA55C}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -6868,9 +11216,586 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="7.6640625" customWidth="true"/>
+    <col min="3" max="4" width="12.6640625" customWidth="true"/>
+    <col min="5" max="5" width="6.6640625" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1643.9999999999998</v>
+      </c>
+      <c r="D2">
+        <v>890.46737652347861</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1639.1717314198845</v>
+      </c>
+      <c r="D3">
+        <v>355.83237973804944</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1268.5762666689691</v>
+      </c>
+      <c r="D4">
+        <v>350</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1272.5801841324005</v>
+      </c>
+      <c r="D5">
+        <v>894.18178999713712</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>901.40459917471139</v>
+      </c>
+      <c r="D6">
+        <v>891.07874963393658</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>885.59657808465863</v>
+      </c>
+      <c r="D7">
+        <v>349</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>506.96689540353066</v>
+      </c>
+      <c r="D8">
+        <v>346.86695692728279</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>519.34751984964259</v>
+      </c>
+      <c r="D9">
+        <v>890</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1635.2250068153903</v>
+      </c>
+      <c r="D10">
+        <v>1033.651358203427</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1628.7010749651322</v>
+      </c>
+      <c r="D11">
+        <v>495.27290178450977</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1257.0758786270517</v>
+      </c>
+      <c r="D12">
+        <v>492.19384543003525</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1261.2034747743264</v>
+      </c>
+      <c r="D13">
+        <v>1036.3494990915842</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>888.85975735881163</v>
+      </c>
+      <c r="D14">
+        <v>1036.1252570136976</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>875.48745637488901</v>
+      </c>
+      <c r="D15">
+        <v>488.53178358312277</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>495.782476538195</v>
+      </c>
+      <c r="D16">
+        <v>489.51792350975768</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>506.55653425087291</v>
+      </c>
+      <c r="D17">
+        <v>1029.8142339811116</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1501</v>
+      </c>
+      <c r="D18">
+        <v>878.00000000000011</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1489</v>
+      </c>
+      <c r="D19">
+        <v>341</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1120.4400268714517</v>
+      </c>
+      <c r="D20">
+        <v>337.01796391130733</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1127.2251969457127</v>
+      </c>
+      <c r="D21">
+        <v>879.06141688646005</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>750.50109136046171</v>
+      </c>
+      <c r="D22">
+        <v>873.48663760499494</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>737.4743615261151</v>
+      </c>
+      <c r="D23">
+        <v>333</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>360.05779300371512</v>
+      </c>
+      <c r="D24">
+        <v>336.31099366099261</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>370.82446642322049</v>
+      </c>
+      <c r="D25">
+        <v>872.11683665181329</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1485.7148948701831</v>
+      </c>
+      <c r="D26">
+        <v>1016.6335969067704</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1479.2353306905293</v>
+      </c>
+      <c r="D27">
+        <v>478.50236367984337</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1107.2219701040583</v>
+      </c>
+      <c r="D28">
+        <v>477.16738984616353</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1113.4112184328715</v>
+      </c>
+      <c r="D29">
+        <v>1017.5839006362315</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>739.47095031350148</v>
+      </c>
+      <c r="D30">
+        <v>1016</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>725.00373505082587</v>
+      </c>
+      <c r="D31">
+        <v>474.4840362551991</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>345</v>
+      </c>
+      <c r="D32">
+        <v>473</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>363.43228956640741</v>
+      </c>
+      <c r="D33">
+        <v>1009.2040069956981</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="4" width="12.6640625" customWidth="true"/>
@@ -6879,22 +11804,19 @@
   <sheetData>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
@@ -6905,34 +11827,17 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <f>G2+5</f>
         <v>1643.4265443435393</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:D3" si="0">H2+30</f>
         <v>344.1904554392429</v>
       </c>
       <c r="E2">
         <v>65</v>
       </c>
-      <c r="G2">
-        <v>1638.4265443435393</v>
-      </c>
-      <c r="H2">
-        <v>314.1904554392429</v>
-      </c>
-      <c r="I2">
-        <v>65</v>
-      </c>
-      <c r="K2" s="2">
-        <v>1643.4265439999999</v>
-      </c>
-      <c r="L2" s="2">
-        <v>344.19045540000002</v>
-      </c>
-      <c r="M2" s="2">
-        <v>65</v>
-      </c>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -6942,34 +11847,17 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <f>G3+5</f>
         <v>1645.5832371432114</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
         <v>879</v>
       </c>
       <c r="E3">
         <v>65</v>
       </c>
-      <c r="G3">
-        <v>1640.5832371432114</v>
-      </c>
-      <c r="H3">
-        <v>849</v>
-      </c>
-      <c r="I3">
-        <v>65</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1645.5832370000001</v>
-      </c>
-      <c r="L3" s="2">
-        <v>879</v>
-      </c>
-      <c r="M3" s="2">
-        <v>65</v>
-      </c>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -6979,34 +11867,17 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C17" si="1">G4+5</f>
         <v>1283.4976351483458</v>
       </c>
       <c r="D4">
-        <f>H4+30</f>
         <v>880.50371781189858</v>
       </c>
       <c r="E4">
         <v>65</v>
       </c>
-      <c r="G4">
-        <v>1278.4976351483458</v>
-      </c>
-      <c r="H4">
-        <v>850.50371781189858</v>
-      </c>
-      <c r="I4">
-        <v>65</v>
-      </c>
-      <c r="K4" s="2">
-        <v>1283.4976349999999</v>
-      </c>
-      <c r="L4" s="2">
-        <v>880.5037178</v>
-      </c>
-      <c r="M4" s="2">
-        <v>65</v>
-      </c>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -7016,34 +11887,17 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <f t="shared" si="1"/>
         <v>1275.2992618674946</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:D17" si="2">H5+30</f>
         <v>335.8398448017395</v>
       </c>
       <c r="E5">
         <v>65</v>
       </c>
-      <c r="G5">
-        <v>1270.2992618674946</v>
-      </c>
-      <c r="H5">
-        <v>305.8398448017395</v>
-      </c>
-      <c r="I5">
-        <v>65</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1275.299262</v>
-      </c>
-      <c r="L5" s="2">
-        <v>335.83984479999998</v>
-      </c>
-      <c r="M5" s="2">
-        <v>65</v>
-      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -7053,34 +11907,17 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <f t="shared" si="1"/>
         <v>895.39997528745789</v>
       </c>
       <c r="D6">
-        <f t="shared" si="2"/>
         <v>334.15420968300811</v>
       </c>
       <c r="E6">
         <v>65</v>
       </c>
-      <c r="G6">
-        <v>890.39997528745789</v>
-      </c>
-      <c r="H6">
-        <v>304.15420968300811</v>
-      </c>
-      <c r="I6">
-        <v>65</v>
-      </c>
-      <c r="K6" s="2">
-        <v>895.39997530000005</v>
-      </c>
-      <c r="L6" s="2">
-        <v>334.15420970000002</v>
-      </c>
-      <c r="M6" s="2">
-        <v>65</v>
-      </c>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -7090,34 +11927,17 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <f t="shared" si="1"/>
         <v>907.0054514726379</v>
       </c>
       <c r="D7">
-        <f t="shared" si="2"/>
         <v>882.00067032311472</v>
       </c>
       <c r="E7">
         <v>65</v>
       </c>
-      <c r="G7">
-        <v>902.0054514726379</v>
-      </c>
-      <c r="H7">
-        <v>852.00067032311472</v>
-      </c>
-      <c r="I7">
-        <v>65</v>
-      </c>
-      <c r="K7" s="2">
-        <v>907.00545150000005</v>
-      </c>
-      <c r="L7" s="2">
-        <v>882.00067030000002</v>
-      </c>
-      <c r="M7" s="2">
-        <v>65</v>
-      </c>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -7127,34 +11947,17 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <f t="shared" si="1"/>
         <v>526.458800788433</v>
       </c>
       <c r="D8">
-        <f t="shared" si="2"/>
         <v>875.01899490184496</v>
       </c>
       <c r="E8">
         <v>65</v>
       </c>
-      <c r="G8">
-        <v>521.458800788433</v>
-      </c>
-      <c r="H8">
-        <v>845.01899490184496</v>
-      </c>
-      <c r="I8">
-        <v>65</v>
-      </c>
-      <c r="K8" s="2">
-        <v>526.45880079999995</v>
-      </c>
-      <c r="L8" s="2">
-        <v>875.01899490000005</v>
-      </c>
-      <c r="M8" s="2">
-        <v>65</v>
-      </c>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -7164,34 +11967,17 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <f t="shared" si="1"/>
         <v>515</v>
       </c>
       <c r="D9">
-        <f t="shared" si="2"/>
         <v>334</v>
       </c>
       <c r="E9">
         <v>65</v>
       </c>
-      <c r="G9">
-        <v>510</v>
-      </c>
-      <c r="H9">
-        <v>304</v>
-      </c>
-      <c r="I9">
-        <v>65</v>
-      </c>
-      <c r="K9" s="2">
-        <v>515</v>
-      </c>
-      <c r="L9" s="2">
-        <v>334</v>
-      </c>
-      <c r="M9" s="2">
-        <v>65</v>
-      </c>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -7201,34 +11987,17 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <f t="shared" si="1"/>
         <v>1638</v>
       </c>
       <c r="D10">
-        <f t="shared" si="2"/>
         <v>483.5340062361679</v>
       </c>
       <c r="E10">
         <v>65</v>
       </c>
-      <c r="G10">
-        <v>1633</v>
-      </c>
-      <c r="H10">
-        <v>453.5340062361679</v>
-      </c>
-      <c r="I10">
-        <v>65</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1638</v>
-      </c>
-      <c r="L10" s="2">
-        <v>483.53400620000002</v>
-      </c>
-      <c r="M10" s="2">
-        <v>65</v>
-      </c>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -7238,34 +12007,17 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <f t="shared" si="1"/>
         <v>1642.4630275922909</v>
       </c>
       <c r="D11">
-        <f t="shared" si="2"/>
         <v>1019.9493538404563</v>
       </c>
       <c r="E11">
         <v>65</v>
       </c>
-      <c r="G11">
-        <v>1637.4630275922909</v>
-      </c>
-      <c r="H11">
-        <v>989.9493538404563</v>
-      </c>
-      <c r="I11">
-        <v>65</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1642.4630279999999</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1019.949354</v>
-      </c>
-      <c r="M11" s="2">
-        <v>65</v>
-      </c>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -7275,34 +12027,17 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <f t="shared" si="1"/>
         <v>1273.6105560128537</v>
       </c>
       <c r="D12">
-        <f t="shared" si="2"/>
         <v>1026.1994263586266</v>
       </c>
       <c r="E12">
         <v>65</v>
       </c>
-      <c r="G12">
-        <v>1268.6105560128537</v>
-      </c>
-      <c r="H12">
-        <v>996.19942635862651</v>
-      </c>
-      <c r="I12">
-        <v>65</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1273.6105560000001</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1026.1994259999999</v>
-      </c>
-      <c r="M12" s="2">
-        <v>65</v>
-      </c>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -7312,34 +12047,17 @@
         <v>4</v>
       </c>
       <c r="C13">
-        <f t="shared" si="1"/>
         <v>1269.8986241372759</v>
       </c>
       <c r="D13">
-        <f t="shared" si="2"/>
         <v>482.98930052173625</v>
       </c>
       <c r="E13">
         <v>65</v>
       </c>
-      <c r="G13">
-        <v>1264.8986241372759</v>
-      </c>
-      <c r="H13">
-        <v>452.98930052173625</v>
-      </c>
-      <c r="I13">
-        <v>65</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1269.8986239999999</v>
-      </c>
-      <c r="L13" s="2">
-        <v>482.98930050000001</v>
-      </c>
-      <c r="M13" s="2">
-        <v>65</v>
-      </c>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
       <c r="A14">
@@ -7349,34 +12067,17 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <f t="shared" si="1"/>
         <v>886.11815473245372</v>
       </c>
       <c r="D14">
-        <f>H14+30</f>
         <v>475.1151043261882</v>
       </c>
       <c r="E14">
         <v>65</v>
       </c>
-      <c r="G14">
-        <v>881.11815473245372</v>
-      </c>
-      <c r="H14">
-        <v>445.1151043261882</v>
-      </c>
-      <c r="I14">
-        <v>65</v>
-      </c>
-      <c r="K14" s="2">
-        <v>886.11815469999999</v>
-      </c>
-      <c r="L14" s="2">
-        <v>475.11510429999998</v>
-      </c>
-      <c r="M14" s="2">
-        <v>65</v>
-      </c>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -7386,34 +12087,17 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <f>G15+5</f>
         <v>899.30901366636238</v>
       </c>
       <c r="D15">
-        <f t="shared" si="2"/>
         <v>1022.3414742931637</v>
       </c>
       <c r="E15">
         <v>65</v>
       </c>
-      <c r="G15">
-        <v>894.30901366636238</v>
-      </c>
-      <c r="H15">
-        <v>992.34147429316374</v>
-      </c>
-      <c r="I15">
-        <v>65</v>
-      </c>
-      <c r="K15" s="2">
-        <v>899.30901370000004</v>
-      </c>
-      <c r="L15" s="2">
-        <v>1022.3414739999999</v>
-      </c>
-      <c r="M15" s="2">
-        <v>65</v>
-      </c>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -7423,34 +12107,17 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <f t="shared" si="1"/>
         <v>517.06667877099005</v>
       </c>
       <c r="D16">
-        <f t="shared" si="2"/>
         <v>1017.4941583555814</v>
       </c>
       <c r="E16">
         <v>65</v>
       </c>
-      <c r="G16">
-        <v>512.06667877099005</v>
-      </c>
-      <c r="H16">
-        <v>987.49415835558136</v>
-      </c>
-      <c r="I16">
-        <v>65</v>
-      </c>
-      <c r="K16" s="2">
-        <v>517.06667879999998</v>
-      </c>
-      <c r="L16" s="2">
-        <v>1017.494158</v>
-      </c>
-      <c r="M16" s="2">
-        <v>65</v>
-      </c>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
       <c r="A17">
@@ -7460,34 +12127,17 @@
         <v>8</v>
       </c>
       <c r="C17">
-        <f t="shared" si="1"/>
         <v>506.03760659484539</v>
       </c>
       <c r="D17">
-        <f t="shared" si="2"/>
         <v>475.63522811947422</v>
       </c>
       <c r="E17">
         <v>65</v>
       </c>
-      <c r="G17">
-        <v>501.03760659484539</v>
-      </c>
-      <c r="H17">
-        <v>445.63522811947422</v>
-      </c>
-      <c r="I17">
-        <v>65</v>
-      </c>
-      <c r="K17" s="2">
-        <v>506.0376066</v>
-      </c>
-      <c r="L17" s="2">
-        <v>475.63522810000001</v>
-      </c>
-      <c r="M17" s="2">
-        <v>65</v>
-      </c>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
       <c r="A18">
@@ -7497,34 +12147,17 @@
         <v>1</v>
       </c>
       <c r="C18">
-        <f>C2-C10+C26</f>
         <v>1480.4265443435393</v>
       </c>
       <c r="D18">
-        <f>D2-D10+D26</f>
         <v>329.656449203075</v>
       </c>
       <c r="E18">
         <v>65</v>
       </c>
-      <c r="G18">
-        <v>1500</v>
-      </c>
-      <c r="H18">
-        <v>309</v>
-      </c>
-      <c r="I18">
-        <v>65</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1480.4265439999999</v>
-      </c>
-      <c r="L18" s="2">
-        <v>329.6564492</v>
-      </c>
-      <c r="M18" s="2">
-        <v>65</v>
-      </c>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
       <c r="A19">
@@ -7534,34 +12167,17 @@
         <v>2</v>
       </c>
       <c r="C19">
-        <f t="shared" ref="C19:D25" si="3">C3-C11+C27</f>
         <v>1484.1471548572047</v>
       </c>
       <c r="D19">
-        <f t="shared" si="3"/>
         <v>869.01259634775022</v>
       </c>
       <c r="E19">
         <v>65</v>
       </c>
-      <c r="G19">
-        <v>1507.4170525137188</v>
-      </c>
-      <c r="H19">
-        <v>848.80732756498946</v>
-      </c>
-      <c r="I19">
-        <v>65</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1484.1471550000001</v>
-      </c>
-      <c r="L19" s="2">
-        <v>869.01259630000004</v>
-      </c>
-      <c r="M19" s="2">
-        <v>65</v>
-      </c>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
       <c r="A20">
@@ -7571,34 +12187,17 @@
         <v>3</v>
       </c>
       <c r="C20">
-        <f t="shared" si="3"/>
         <v>1118.3885938896296</v>
       </c>
       <c r="D20">
-        <f t="shared" si="3"/>
         <v>866.80312659864478</v>
       </c>
       <c r="E20">
         <v>65</v>
       </c>
-      <c r="G20">
-        <v>1134.8380913459309</v>
-      </c>
-      <c r="H20">
-        <v>848.36948917416635</v>
-      </c>
-      <c r="I20">
-        <v>65</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1118.388594</v>
-      </c>
-      <c r="L20" s="2">
-        <v>866.80312660000004</v>
-      </c>
-      <c r="M20" s="2">
-        <v>65</v>
-      </c>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
       <c r="A21">
@@ -7608,34 +12207,17 @@
         <v>4</v>
       </c>
       <c r="C21">
-        <f t="shared" si="3"/>
         <v>1107.4006377302187</v>
       </c>
       <c r="D21">
-        <f t="shared" si="3"/>
         <v>319.85054428000325</v>
       </c>
       <c r="E21">
         <v>65</v>
       </c>
-      <c r="G21">
-        <v>1126.9999999999998</v>
-      </c>
-      <c r="H21">
-        <v>303.46386067619034</v>
-      </c>
-      <c r="I21">
-        <v>65</v>
-      </c>
-      <c r="K21" s="2">
-        <v>1107.4006380000001</v>
-      </c>
-      <c r="L21" s="2">
-        <v>319.85054430000002</v>
-      </c>
-      <c r="M21" s="2">
-        <v>65</v>
-      </c>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
       <c r="A22">
@@ -7645,34 +12227,17 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <f t="shared" si="3"/>
         <v>726.29048359479486</v>
       </c>
       <c r="D22">
-        <f t="shared" si="3"/>
         <v>322.21486543594295</v>
       </c>
       <c r="E22">
         <v>65</v>
       </c>
-      <c r="G22">
-        <v>746.66826419851839</v>
-      </c>
-      <c r="H22">
-        <v>301.37423485472425</v>
-      </c>
-      <c r="I22">
-        <v>65</v>
-      </c>
-      <c r="K22" s="2">
-        <v>726.29048360000002</v>
-      </c>
-      <c r="L22" s="2">
-        <v>322.21486540000001</v>
-      </c>
-      <c r="M22" s="2">
-        <v>65</v>
-      </c>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
       <c r="A23">
@@ -7682,34 +12247,17 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <f t="shared" si="3"/>
         <v>740.40498903244452</v>
       </c>
       <c r="D23">
-        <f t="shared" si="3"/>
         <v>869.91719471886188</v>
       </c>
       <c r="E23">
         <v>65</v>
       </c>
-      <c r="G23">
-        <v>758</v>
-      </c>
-      <c r="H23">
-        <v>845</v>
-      </c>
-      <c r="I23">
-        <v>65</v>
-      </c>
-      <c r="K23" s="2">
-        <v>740.404989</v>
-      </c>
-      <c r="L23" s="2">
-        <v>869.91719469999998</v>
-      </c>
-      <c r="M23" s="2">
-        <v>65</v>
-      </c>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
       <c r="A24">
@@ -7719,34 +12267,17 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <f t="shared" si="3"/>
         <v>363.9141454244446</v>
       </c>
       <c r="D24">
-        <f t="shared" si="3"/>
         <v>859.48740624508446</v>
       </c>
       <c r="E24">
         <v>65</v>
       </c>
-      <c r="G24">
-        <v>376.66064541799346</v>
-      </c>
-      <c r="H24">
-        <v>842.97155739522611</v>
-      </c>
-      <c r="I24">
-        <v>65</v>
-      </c>
-      <c r="K24" s="2">
-        <v>363.9141454</v>
-      </c>
-      <c r="L24" s="2">
-        <v>859.48740620000001</v>
-      </c>
-      <c r="M24" s="2">
-        <v>65</v>
-      </c>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
       <c r="A25">
@@ -7756,34 +12287,17 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <f t="shared" si="3"/>
         <v>347.45924699832796</v>
       </c>
       <c r="D25">
-        <f t="shared" si="3"/>
         <v>322.37373775457678</v>
       </c>
       <c r="E25">
         <v>65</v>
       </c>
-      <c r="G25">
-        <v>366.1778550489546</v>
-      </c>
-      <c r="H25">
-        <v>301.41781057527805</v>
-      </c>
-      <c r="I25">
-        <v>65</v>
-      </c>
-      <c r="K25" s="2">
-        <v>347.459247</v>
-      </c>
-      <c r="L25" s="2">
-        <v>322.37373780000001</v>
-      </c>
-      <c r="M25" s="2">
-        <v>65</v>
-      </c>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
       <c r="A26">
@@ -7793,34 +12307,17 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <f t="shared" ref="C26:C32" si="4">G26-20</f>
         <v>1475</v>
       </c>
       <c r="D26">
-        <f t="shared" ref="D26:D27" si="5">H26+25</f>
         <v>469</v>
       </c>
       <c r="E26">
         <v>65</v>
       </c>
-      <c r="G26">
-        <v>1495</v>
-      </c>
-      <c r="H26">
-        <v>444</v>
-      </c>
-      <c r="I26">
-        <v>65</v>
-      </c>
-      <c r="K26" s="2">
-        <v>1475</v>
-      </c>
-      <c r="L26" s="2">
-        <v>469</v>
-      </c>
-      <c r="M26" s="2">
-        <v>65</v>
-      </c>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
       <c r="A27">
@@ -7830,34 +12327,17 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <f t="shared" si="4"/>
         <v>1481.0269453062842</v>
       </c>
       <c r="D27">
-        <f t="shared" si="5"/>
         <v>1009.9619501882065</v>
       </c>
       <c r="E27">
         <v>65</v>
       </c>
-      <c r="G27">
-        <v>1501.0269453062842</v>
-      </c>
-      <c r="H27">
-        <v>984.96195018820652</v>
-      </c>
-      <c r="I27">
-        <v>65</v>
-      </c>
-      <c r="K27" s="2">
-        <v>1481.0269450000001</v>
-      </c>
-      <c r="L27" s="2">
-        <v>1009.96195</v>
-      </c>
-      <c r="M27" s="2">
-        <v>65</v>
-      </c>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
       <c r="A28">
@@ -7867,34 +12347,17 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <f t="shared" si="4"/>
         <v>1108.5015147541376</v>
       </c>
       <c r="D28">
-        <f>H28+25</f>
         <v>1012.4988351453728</v>
       </c>
       <c r="E28">
         <v>65</v>
       </c>
-      <c r="G28">
-        <v>1128.5015147541376</v>
-      </c>
-      <c r="H28">
-        <v>987.49883514537282</v>
-      </c>
-      <c r="I28">
-        <v>65</v>
-      </c>
-      <c r="K28" s="2">
-        <v>1108.5015149999999</v>
-      </c>
-      <c r="L28" s="2">
-        <v>1012.498835</v>
-      </c>
-      <c r="M28" s="2">
-        <v>65</v>
-      </c>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
       <c r="A29">
@@ -7904,34 +12367,17 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <f t="shared" si="4"/>
         <v>1102</v>
       </c>
       <c r="D29">
-        <f t="shared" ref="D29:D33" si="6">H29+25</f>
         <v>467</v>
       </c>
       <c r="E29">
         <v>65</v>
       </c>
-      <c r="G29">
-        <v>1122</v>
-      </c>
-      <c r="H29">
-        <v>442</v>
-      </c>
-      <c r="I29">
-        <v>65</v>
-      </c>
-      <c r="K29" s="2">
-        <v>1102</v>
-      </c>
-      <c r="L29" s="2">
-        <v>467</v>
-      </c>
-      <c r="M29" s="2">
-        <v>65</v>
-      </c>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
       <c r="A30">
@@ -7941,34 +12387,17 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <f t="shared" si="4"/>
         <v>717.00866303979069</v>
       </c>
       <c r="D30">
-        <f t="shared" si="6"/>
         <v>463.17576007912305</v>
       </c>
       <c r="E30">
         <v>65</v>
       </c>
-      <c r="G30">
-        <v>737.00866303979069</v>
-      </c>
-      <c r="H30">
-        <v>438.17576007912305</v>
-      </c>
-      <c r="I30">
-        <v>65</v>
-      </c>
-      <c r="K30" s="2">
-        <v>717.00866299999996</v>
-      </c>
-      <c r="L30" s="2">
-        <v>463.17576009999999</v>
-      </c>
-      <c r="M30" s="2">
-        <v>65</v>
-      </c>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
       <c r="A31">
@@ -7978,34 +12407,17 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <f t="shared" si="4"/>
         <v>732.70855122616899</v>
       </c>
       <c r="D31">
-        <f t="shared" si="6"/>
         <v>1010.2579986889109</v>
       </c>
       <c r="E31">
         <v>65</v>
       </c>
-      <c r="G31">
-        <v>752.70855122616899</v>
-      </c>
-      <c r="H31">
-        <v>985.2579986889109</v>
-      </c>
-      <c r="I31">
-        <v>65</v>
-      </c>
-      <c r="K31" s="2">
-        <v>732.70855119999999</v>
-      </c>
-      <c r="L31" s="2">
-        <v>1010.257999</v>
-      </c>
-      <c r="M31" s="2">
-        <v>65</v>
-      </c>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
       <c r="A32">
@@ -8015,34 +12427,17 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <f t="shared" si="4"/>
         <v>354.52202340700165</v>
       </c>
       <c r="D32">
-        <f t="shared" si="6"/>
         <v>1001.9625696988209</v>
       </c>
       <c r="E32">
         <v>65</v>
       </c>
-      <c r="G32">
-        <v>374.52202340700165</v>
-      </c>
-      <c r="H32">
-        <v>976.96256969882086</v>
-      </c>
-      <c r="I32">
-        <v>65</v>
-      </c>
-      <c r="K32" s="2">
-        <v>354.52202340000002</v>
-      </c>
-      <c r="L32" s="2">
-        <v>1001.96257</v>
-      </c>
-      <c r="M32" s="2">
-        <v>65</v>
-      </c>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
       <c r="A33">
@@ -8052,34 +12447,17 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <f>G33-20</f>
         <v>338.49685359317334</v>
       </c>
       <c r="D33">
-        <f t="shared" si="6"/>
         <v>464.008965874051</v>
       </c>
       <c r="E33">
         <v>65</v>
       </c>
-      <c r="G33">
-        <v>358.49685359317334</v>
-      </c>
-      <c r="H33">
-        <v>439.008965874051</v>
-      </c>
-      <c r="I33">
-        <v>65</v>
-      </c>
-      <c r="K33" s="2">
-        <v>338.49685360000001</v>
-      </c>
-      <c r="L33" s="2">
-        <v>464.00896590000002</v>
-      </c>
-      <c r="M33" s="2">
-        <v>65</v>
-      </c>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -8087,7 +12465,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55619896-D09A-7746-A7AB-407CD32ABD7F}">
   <dimension ref="A1:AC33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -9372,7 +13750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P4"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -9587,7 +13965,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12331FAC-F287-564D-A828-85EA3FEE69F0}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -10163,1156 +14541,4 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A8B513D-DF9C-6D4B-8EB9-67E97D41F236}">
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="4" width="12.6640625" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1604.6029030107932</v>
-      </c>
-      <c r="D2">
-        <v>280.65774254218428</v>
-      </c>
-      <c r="E2">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1628.7162893371674</v>
-      </c>
-      <c r="D3">
-        <v>811.65681418393456</v>
-      </c>
-      <c r="E3">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1263</v>
-      </c>
-      <c r="D4">
-        <v>830</v>
-      </c>
-      <c r="E4">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1241</v>
-      </c>
-      <c r="D5">
-        <v>285</v>
-      </c>
-      <c r="E5">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>860.27323359172738</v>
-      </c>
-      <c r="D6">
-        <v>290.99912082838</v>
-      </c>
-      <c r="E6">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>885.96699056537875</v>
-      </c>
-      <c r="D7">
-        <v>834</v>
-      </c>
-      <c r="E7">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>506</v>
-      </c>
-      <c r="D8">
-        <v>842.45891560138898</v>
-      </c>
-      <c r="E8">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9">
-        <v>481.40090797133456</v>
-      </c>
-      <c r="D9">
-        <v>299.58901290582963</v>
-      </c>
-      <c r="E9">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1606</v>
-      </c>
-      <c r="D10">
-        <v>425</v>
-      </c>
-      <c r="E10">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>1620.9445240019663</v>
-      </c>
-      <c r="D11">
-        <v>959.47984336260345</v>
-      </c>
-      <c r="E11">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>1256</v>
-      </c>
-      <c r="D12">
-        <v>974</v>
-      </c>
-      <c r="E12">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>1237.2074574032038</v>
-      </c>
-      <c r="D13">
-        <v>431.50098570018065</v>
-      </c>
-      <c r="E13">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14">
-        <v>5</v>
-      </c>
-      <c r="C14">
-        <v>852.36344463680052</v>
-      </c>
-      <c r="D14">
-        <v>437.74724778007908</v>
-      </c>
-      <c r="E14">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>882.53773646259197</v>
-      </c>
-      <c r="D15">
-        <v>981.00000000000011</v>
-      </c>
-      <c r="E15">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="B16">
-        <v>7</v>
-      </c>
-      <c r="C16">
-        <v>500.64185533341998</v>
-      </c>
-      <c r="D16">
-        <v>989.32192413899827</v>
-      </c>
-      <c r="E16">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17">
-        <v>8</v>
-      </c>
-      <c r="C17">
-        <v>474.89341345569784</v>
-      </c>
-      <c r="D17">
-        <v>448.84585525987632</v>
-      </c>
-      <c r="E17">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>3</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>1467.5283069529205</v>
-      </c>
-      <c r="D18">
-        <v>279.48143931656074</v>
-      </c>
-      <c r="E18">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>3</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19">
-        <v>1489.5885413497574</v>
-      </c>
-      <c r="D19">
-        <v>813.23295593386445</v>
-      </c>
-      <c r="E19">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>3</v>
-      </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20">
-        <v>1117.0168346154469</v>
-      </c>
-      <c r="D20">
-        <v>829.28943124222167</v>
-      </c>
-      <c r="E20">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>3</v>
-      </c>
-      <c r="B21">
-        <v>4</v>
-      </c>
-      <c r="C21">
-        <v>1093.2565289139898</v>
-      </c>
-      <c r="D21">
-        <v>282.76894231476359</v>
-      </c>
-      <c r="E21">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>3</v>
-      </c>
-      <c r="B22">
-        <v>5</v>
-      </c>
-      <c r="C22">
-        <v>710.50943405789167</v>
-      </c>
-      <c r="D22">
-        <v>291.00000000000006</v>
-      </c>
-      <c r="E22">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>3</v>
-      </c>
-      <c r="B23">
-        <v>6</v>
-      </c>
-      <c r="C23">
-        <v>739</v>
-      </c>
-      <c r="D23">
-        <v>831.51615876175674</v>
-      </c>
-      <c r="E23">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24">
-        <v>7</v>
-      </c>
-      <c r="C24">
-        <v>358.00000000000006</v>
-      </c>
-      <c r="D24">
-        <v>836.56843813389787</v>
-      </c>
-      <c r="E24">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>3</v>
-      </c>
-      <c r="B25">
-        <v>8</v>
-      </c>
-      <c r="C25">
-        <v>335.52599426336445</v>
-      </c>
-      <c r="D25">
-        <v>300.52825243257473</v>
-      </c>
-      <c r="E25">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>4</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>1464.0259861843795</v>
-      </c>
-      <c r="D26">
-        <v>421.85523734651008</v>
-      </c>
-      <c r="E26">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>4</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <v>1482.3243065783529</v>
-      </c>
-      <c r="D27">
-        <v>959.6627249231442</v>
-      </c>
-      <c r="E27">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>4</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
-      </c>
-      <c r="C28">
-        <v>1111.9187726325586</v>
-      </c>
-      <c r="D28">
-        <v>970.49048829824119</v>
-      </c>
-      <c r="E28">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>4</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29">
-        <v>1091</v>
-      </c>
-      <c r="D29">
-        <v>425.00000000000006</v>
-      </c>
-      <c r="E29">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>4</v>
-      </c>
-      <c r="B30">
-        <v>5</v>
-      </c>
-      <c r="C30">
-        <v>707.47963024160333</v>
-      </c>
-      <c r="D30">
-        <v>434.47315275655529</v>
-      </c>
-      <c r="E30">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>4</v>
-      </c>
-      <c r="B31">
-        <v>6</v>
-      </c>
-      <c r="C31">
-        <v>737.00198143642649</v>
-      </c>
-      <c r="D31">
-        <v>977.26118909195395</v>
-      </c>
-      <c r="E31">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>4</v>
-      </c>
-      <c r="B32">
-        <v>7</v>
-      </c>
-      <c r="C32">
-        <v>361</v>
-      </c>
-      <c r="D32">
-        <v>982.99999999999989</v>
-      </c>
-      <c r="E32">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>4</v>
-      </c>
-      <c r="B33">
-        <v>8</v>
-      </c>
-      <c r="C33">
-        <v>329.35137120907115</v>
-      </c>
-      <c r="D33">
-        <v>444.80155102258573</v>
-      </c>
-      <c r="E33">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="7.6640625" customWidth="true"/>
-    <col min="3" max="4" width="12.6640625" customWidth="true"/>
-    <col min="5" max="5" width="6.6640625" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1643.9999999999998</v>
-      </c>
-      <c r="D2">
-        <v>890.46737652347861</v>
-      </c>
-      <c r="E2">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1639.1717314198845</v>
-      </c>
-      <c r="D3">
-        <v>355.83237973804944</v>
-      </c>
-      <c r="E3">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1268.5762666689691</v>
-      </c>
-      <c r="D4">
-        <v>350</v>
-      </c>
-      <c r="E4">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1272.5801841324005</v>
-      </c>
-      <c r="D5">
-        <v>894.18178999713712</v>
-      </c>
-      <c r="E5">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>901.40459917471139</v>
-      </c>
-      <c r="D6">
-        <v>891.07874963393658</v>
-      </c>
-      <c r="E6">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>885.59657808465863</v>
-      </c>
-      <c r="D7">
-        <v>349</v>
-      </c>
-      <c r="E7">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>506.96689540353066</v>
-      </c>
-      <c r="D8">
-        <v>346.86695692728279</v>
-      </c>
-      <c r="E8">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9">
-        <v>519.34751984964259</v>
-      </c>
-      <c r="D9">
-        <v>890</v>
-      </c>
-      <c r="E9">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1635.2250068153903</v>
-      </c>
-      <c r="D10">
-        <v>1033.651358203427</v>
-      </c>
-      <c r="E10">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>1628.7010749651322</v>
-      </c>
-      <c r="D11">
-        <v>495.27290178450977</v>
-      </c>
-      <c r="E11">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>1257.0758786270517</v>
-      </c>
-      <c r="D12">
-        <v>492.19384543003525</v>
-      </c>
-      <c r="E12">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>1261.2034747743264</v>
-      </c>
-      <c r="D13">
-        <v>1036.3494990915842</v>
-      </c>
-      <c r="E13">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14">
-        <v>5</v>
-      </c>
-      <c r="C14">
-        <v>888.85975735881163</v>
-      </c>
-      <c r="D14">
-        <v>1036.1252570136976</v>
-      </c>
-      <c r="E14">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>875.48745637488901</v>
-      </c>
-      <c r="D15">
-        <v>488.53178358312277</v>
-      </c>
-      <c r="E15">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="B16">
-        <v>7</v>
-      </c>
-      <c r="C16">
-        <v>495.782476538195</v>
-      </c>
-      <c r="D16">
-        <v>489.51792350975768</v>
-      </c>
-      <c r="E16">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17">
-        <v>8</v>
-      </c>
-      <c r="C17">
-        <v>506.55653425087291</v>
-      </c>
-      <c r="D17">
-        <v>1029.8142339811116</v>
-      </c>
-      <c r="E17">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>3</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>1501</v>
-      </c>
-      <c r="D18">
-        <v>878.00000000000011</v>
-      </c>
-      <c r="E18">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>3</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19">
-        <v>1489</v>
-      </c>
-      <c r="D19">
-        <v>341</v>
-      </c>
-      <c r="E19">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>3</v>
-      </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20">
-        <v>1120.4400268714517</v>
-      </c>
-      <c r="D20">
-        <v>337.01796391130733</v>
-      </c>
-      <c r="E20">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>3</v>
-      </c>
-      <c r="B21">
-        <v>4</v>
-      </c>
-      <c r="C21">
-        <v>1127.2251969457127</v>
-      </c>
-      <c r="D21">
-        <v>879.06141688646005</v>
-      </c>
-      <c r="E21">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>3</v>
-      </c>
-      <c r="B22">
-        <v>5</v>
-      </c>
-      <c r="C22">
-        <v>750.50109136046171</v>
-      </c>
-      <c r="D22">
-        <v>873.48663760499494</v>
-      </c>
-      <c r="E22">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>3</v>
-      </c>
-      <c r="B23">
-        <v>6</v>
-      </c>
-      <c r="C23">
-        <v>737.4743615261151</v>
-      </c>
-      <c r="D23">
-        <v>333</v>
-      </c>
-      <c r="E23">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24">
-        <v>7</v>
-      </c>
-      <c r="C24">
-        <v>360.05779300371512</v>
-      </c>
-      <c r="D24">
-        <v>336.31099366099261</v>
-      </c>
-      <c r="E24">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>3</v>
-      </c>
-      <c r="B25">
-        <v>8</v>
-      </c>
-      <c r="C25">
-        <v>370.82446642322049</v>
-      </c>
-      <c r="D25">
-        <v>872.11683665181329</v>
-      </c>
-      <c r="E25">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>4</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>1485.7148948701831</v>
-      </c>
-      <c r="D26">
-        <v>1016.6335969067704</v>
-      </c>
-      <c r="E26">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>4</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <v>1479.2353306905293</v>
-      </c>
-      <c r="D27">
-        <v>478.50236367984337</v>
-      </c>
-      <c r="E27">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>4</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
-      </c>
-      <c r="C28">
-        <v>1107.2219701040583</v>
-      </c>
-      <c r="D28">
-        <v>477.16738984616353</v>
-      </c>
-      <c r="E28">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>4</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29">
-        <v>1113.4112184328715</v>
-      </c>
-      <c r="D29">
-        <v>1017.5839006362315</v>
-      </c>
-      <c r="E29">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>4</v>
-      </c>
-      <c r="B30">
-        <v>5</v>
-      </c>
-      <c r="C30">
-        <v>739.47095031350148</v>
-      </c>
-      <c r="D30">
-        <v>1016</v>
-      </c>
-      <c r="E30">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>4</v>
-      </c>
-      <c r="B31">
-        <v>6</v>
-      </c>
-      <c r="C31">
-        <v>725.00373505082587</v>
-      </c>
-      <c r="D31">
-        <v>474.4840362551991</v>
-      </c>
-      <c r="E31">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>4</v>
-      </c>
-      <c r="B32">
-        <v>7</v>
-      </c>
-      <c r="C32">
-        <v>345</v>
-      </c>
-      <c r="D32">
-        <v>473</v>
-      </c>
-      <c r="E32">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>4</v>
-      </c>
-      <c r="B33">
-        <v>8</v>
-      </c>
-      <c r="C33">
-        <v>363.43228956640741</v>
-      </c>
-      <c r="D33">
-        <v>1009.2040069956981</v>
-      </c>
-      <c r="E33">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Soft X-ray/Four-View/fiberPositions.xlsx
+++ b/Soft X-ray/Four-View/fiberPositions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shinjirotakeda/Documents/GitHub/test-open/Soft X-ray/Four-View/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E152C26D-4AD9-1E42-8814-B48CAD33651E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5518C181-A4ED-6143-AB45-9714AB145648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1100" windowWidth="28800" windowHeight="16160" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="1100" windowWidth="28800" windowHeight="16160" firstSheet="4" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="230921" sheetId="4" r:id="rId1"/>
@@ -25,11 +25,13 @@
     <sheet name="240501_old" sheetId="10" r:id="rId10"/>
     <sheet name="240501_old2" sheetId="9" r:id="rId11"/>
     <sheet name="240501" sheetId="11" r:id="rId12"/>
-    <sheet name="240621" sheetId="13" r:id="rId17"/>
-    <sheet name="240622" sheetId="14" r:id="rId18"/>
-    <sheet name="240828" sheetId="15" r:id="rId19"/>
+    <sheet name="240621" sheetId="13" r:id="rId13"/>
+    <sheet name="240622" sheetId="14" r:id="rId14"/>
+    <sheet name="240828" sheetId="15" r:id="rId15"/>
+    <sheet name="250325_old" sheetId="16" r:id="rId16"/>
+    <sheet name="250328_old" sheetId="17" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="74" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="23">
   <si>
     <t>center_X</t>
     <phoneticPr fontId="1"/>
@@ -132,7 +134,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3">
     <font>
       <sz val="12"/>
@@ -166,7 +168,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -188,24 +190,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -375,7 +375,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -399,9 +399,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -425,7 +425,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -460,7 +460,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -478,7 +478,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -503,7 +503,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -519,15 +519,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="3" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="3.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -547,7 +547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
@@ -584,7 +584,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>1</v>
       </c>
@@ -621,7 +621,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>1</v>
       </c>
@@ -658,7 +658,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>1</v>
       </c>
@@ -695,7 +695,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>1</v>
       </c>
@@ -732,7 +732,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>1</v>
       </c>
@@ -769,7 +769,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>1</v>
       </c>
@@ -806,7 +806,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>1</v>
       </c>
@@ -843,7 +843,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>2</v>
       </c>
@@ -880,7 +880,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>2</v>
       </c>
@@ -917,7 +917,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>2</v>
       </c>
@@ -954,7 +954,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -991,7 +991,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:13">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:13">
       <c r="A18">
         <v>3</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:13">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:13">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:13">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:13">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:13">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:13">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:13">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:13">
       <c r="A26">
         <v>4</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:13">
       <c r="A27">
         <v>4</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:13">
       <c r="A28">
         <v>4</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:13">
       <c r="A29">
         <v>4</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:13">
       <c r="A30">
         <v>4</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:13">
       <c r="A31">
         <v>4</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:13">
       <c r="A32">
         <v>4</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:13">
       <c r="A33">
         <v>4</v>
       </c>
@@ -1738,16 +1738,16 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06735BCB-ED1E-904B-B816-90CA8290FBD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06735BCB-ED1E-904B-B816-90CA8290FBD5}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>3</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>3</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>4</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>4</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>4</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>4</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>4</v>
       </c>
@@ -2315,16 +2315,16 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>3</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>3</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>4</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>4</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>4</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>4</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>4</v>
       </c>
@@ -2892,16 +2892,16 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>3</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>3</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>3</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>3</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>3</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>3</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>3</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>3</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>4</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>4</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>4</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>4</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>4</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>4</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>4</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>4</v>
       </c>
@@ -3469,1746 +3469,2900 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="true"/>
-    <col min="2" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" customWidth="true"/>
-    <col min="4" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0">
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1623.2292720117171</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>318.02283380034714</v>
       </c>
-      <c r="E2" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0">
-        <v>2</v>
-      </c>
-      <c r="C3" s="0">
+      <c r="E2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1630</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>853</v>
       </c>
-      <c r="E3" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0">
-        <v>1</v>
-      </c>
-      <c r="B4" s="0">
-        <v>3</v>
-      </c>
-      <c r="C4" s="0">
+      <c r="E3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <v>1265.3901248978002</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>858.004657186401</v>
       </c>
-      <c r="E4" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>1</v>
-      </c>
-      <c r="B5" s="0">
-        <v>4</v>
-      </c>
-      <c r="C5" s="0">
+      <c r="E4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>1259.3298617001483</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>312.57633759001806</v>
       </c>
-      <c r="E5" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>1</v>
-      </c>
-      <c r="B6" s="0">
+      <c r="E5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>878.28953338071472</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>312.6477698349708</v>
       </c>
-      <c r="E6" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>1</v>
-      </c>
-      <c r="B7" s="0">
+      <c r="E6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7">
         <v>894.67516776544289</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>854.63303438425419</v>
       </c>
-      <c r="E7" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>1</v>
-      </c>
-      <c r="B8" s="0">
+      <c r="E7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C8">
         <v>511.00000000000006</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>850</v>
       </c>
-      <c r="E8" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>1</v>
-      </c>
-      <c r="B9" s="0">
+      <c r="E8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C9">
         <v>495.53392609582073</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>310.21151328870832</v>
       </c>
-      <c r="E9" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>2</v>
-      </c>
-      <c r="B10" s="0">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0">
+      <c r="E9">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>1602.5720858052957</v>
       </c>
-      <c r="D10" s="0">
+      <c r="D10">
         <v>455.00000000000006</v>
       </c>
-      <c r="E10" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0">
-        <v>2</v>
-      </c>
-      <c r="B11" s="0">
-        <v>2</v>
-      </c>
-      <c r="C11" s="0">
+      <c r="E10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
         <v>1611.6697320465623</v>
       </c>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>988.07147939259403</v>
       </c>
-      <c r="E11" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0">
-        <v>2</v>
-      </c>
-      <c r="B12" s="0">
-        <v>3</v>
-      </c>
-      <c r="C12" s="0">
+      <c r="E11">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <v>1244.3663165587568</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>993.84211118870417</v>
       </c>
-      <c r="E12" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0">
-        <v>2</v>
-      </c>
-      <c r="B13" s="0">
-        <v>4</v>
-      </c>
-      <c r="C13" s="0">
+      <c r="E12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
         <v>1239.4073597680974</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D13">
         <v>452.2096389680803</v>
       </c>
-      <c r="E13" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0">
-        <v>2</v>
-      </c>
-      <c r="B14" s="0">
+      <c r="E13">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14">
         <v>858</v>
       </c>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>452</v>
       </c>
-      <c r="E14" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0">
-        <v>2</v>
-      </c>
-      <c r="B15" s="0">
+      <c r="E14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
         <v>6</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>875.00660123453724</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>992.66237139821465</v>
       </c>
-      <c r="E15" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0">
-        <v>2</v>
-      </c>
-      <c r="B16" s="0">
+      <c r="E15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>491.41224563335277</v>
       </c>
-      <c r="D16" s="0">
+      <c r="D16">
         <v>991.18596534212418</v>
       </c>
-      <c r="E16" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0">
-        <v>2</v>
-      </c>
-      <c r="B17" s="0">
+      <c r="E16">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
         <v>8</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C17">
         <v>478.00000000000006</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>447.54026768194427</v>
       </c>
-      <c r="E17" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0">
-        <v>3</v>
-      </c>
-      <c r="B18" s="0">
-        <v>1</v>
-      </c>
-      <c r="C18" s="0">
+      <c r="E17">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
         <v>1473.1978278146719</v>
       </c>
-      <c r="D18" s="0">
+      <c r="D18">
         <v>310.19938864339537</v>
       </c>
-      <c r="E18" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0">
-        <v>3</v>
-      </c>
-      <c r="B19" s="0">
-        <v>2</v>
-      </c>
-      <c r="C19" s="0">
+      <c r="E18">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
         <v>1482.7441676226731</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D19">
         <v>848.07660330574492</v>
       </c>
-      <c r="E19" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0">
-        <v>3</v>
-      </c>
-      <c r="B20" s="0">
-        <v>3</v>
-      </c>
-      <c r="C20" s="0">
+      <c r="E19">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
         <v>1109.4778732563907</v>
       </c>
-      <c r="D20" s="0">
+      <c r="D20">
         <v>849.70594190979659</v>
       </c>
-      <c r="E20" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0">
-        <v>3</v>
-      </c>
-      <c r="B21" s="0">
-        <v>4</v>
-      </c>
-      <c r="C21" s="0">
+      <c r="E20">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
         <v>1101</v>
       </c>
-      <c r="D21" s="0">
+      <c r="D21">
         <v>307</v>
       </c>
-      <c r="E21" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0">
-        <v>3</v>
-      </c>
-      <c r="B22" s="0">
+      <c r="E21">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
         <v>5</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C22">
         <v>719.76067643648571</v>
       </c>
-      <c r="D22" s="0">
+      <c r="D22">
         <v>304.62199039186692</v>
       </c>
-      <c r="E22" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0">
-        <v>3</v>
-      </c>
-      <c r="B23" s="0">
+      <c r="E22">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
         <v>6</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C23">
         <v>733.65336961722619</v>
       </c>
-      <c r="D23" s="0">
+      <c r="D23">
         <v>843.98769856330478</v>
       </c>
-      <c r="E23" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0">
-        <v>3</v>
-      </c>
-      <c r="B24" s="0">
+      <c r="E23">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
         <v>7</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C24">
         <v>355</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D24">
         <v>840</v>
       </c>
-      <c r="E24" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0">
-        <v>3</v>
-      </c>
-      <c r="B25" s="0">
+      <c r="E24">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
         <v>8</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C25">
         <v>341</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D25">
         <v>303</v>
       </c>
-      <c r="E25" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0">
-        <v>4</v>
-      </c>
-      <c r="B26" s="0">
-        <v>1</v>
-      </c>
-      <c r="C26" s="0">
+      <c r="E25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
         <v>1470.5057035800305</v>
       </c>
-      <c r="D26" s="0">
+      <c r="D26">
         <v>446</v>
       </c>
-      <c r="E26" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0">
-        <v>4</v>
-      </c>
-      <c r="B27" s="0">
-        <v>2</v>
-      </c>
-      <c r="C27" s="0">
+      <c r="E26">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
         <v>1474</v>
       </c>
-      <c r="D27" s="0">
+      <c r="D27">
         <v>983.99999999999989</v>
       </c>
-      <c r="E27" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0">
-        <v>4</v>
-      </c>
-      <c r="B28" s="0">
-        <v>3</v>
-      </c>
-      <c r="C28" s="0">
+      <c r="E27">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
         <v>1103.4447738129099</v>
       </c>
-      <c r="D28" s="0">
+      <c r="D28">
         <v>985.83641054114321</v>
       </c>
-      <c r="E28" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0">
-        <v>4</v>
-      </c>
-      <c r="B29" s="0">
-        <v>4</v>
-      </c>
-      <c r="C29" s="0">
+      <c r="E28">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
         <v>1097</v>
       </c>
-      <c r="D29" s="0">
+      <c r="D29">
         <v>445.12107140231734</v>
       </c>
-      <c r="E29" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0">
-        <v>4</v>
-      </c>
-      <c r="B30" s="0">
+      <c r="E29">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
         <v>5</v>
       </c>
-      <c r="C30" s="0">
+      <c r="C30">
         <v>714.39773670552825</v>
       </c>
-      <c r="D30" s="0">
+      <c r="D30">
         <v>441.30329088212028</v>
       </c>
-      <c r="E30" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0">
-        <v>4</v>
-      </c>
-      <c r="B31" s="0">
+      <c r="E30">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
         <v>6</v>
       </c>
-      <c r="C31" s="0">
+      <c r="C31">
         <v>729.55746695772802</v>
       </c>
-      <c r="D31" s="0">
+      <c r="D31">
         <v>986.00000000000011</v>
       </c>
-      <c r="E31" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0">
-        <v>4</v>
-      </c>
-      <c r="B32" s="0">
+      <c r="E31">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C32" s="0">
+      <c r="C32">
         <v>352.64925385754344</v>
       </c>
-      <c r="D32" s="0">
+      <c r="D32">
         <v>984.31908196925087</v>
       </c>
-      <c r="E32" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0">
-        <v>4</v>
-      </c>
-      <c r="B33" s="0">
+      <c r="E32">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
         <v>8</v>
       </c>
-      <c r="C33" s="0">
+      <c r="C33">
         <v>336</v>
       </c>
-      <c r="D33" s="0">
+      <c r="D33">
         <v>442.99999999999994</v>
       </c>
-      <c r="E33" s="0">
+      <c r="E33">
         <v>71</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="true"/>
-    <col min="2" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" customWidth="true"/>
-    <col min="4" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0">
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1623.2292720117171</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>332.02283380034714</v>
       </c>
-      <c r="E2" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0">
-        <v>2</v>
-      </c>
-      <c r="C3" s="0">
+      <c r="E2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1630</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>867</v>
       </c>
-      <c r="E3" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0">
-        <v>1</v>
-      </c>
-      <c r="B4" s="0">
-        <v>3</v>
-      </c>
-      <c r="C4" s="0">
+      <c r="E3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <v>1265.3901248978002</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>872.004657186401</v>
       </c>
-      <c r="E4" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>1</v>
-      </c>
-      <c r="B5" s="0">
-        <v>4</v>
-      </c>
-      <c r="C5" s="0">
+      <c r="E4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>1259.3298617001483</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>326.57633759001806</v>
       </c>
-      <c r="E5" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>1</v>
-      </c>
-      <c r="B6" s="0">
+      <c r="E5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>878.28953338071472</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>326.6477698349708</v>
       </c>
-      <c r="E6" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>1</v>
-      </c>
-      <c r="B7" s="0">
+      <c r="E6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7">
         <v>894.67516776544289</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>868.63303438425419</v>
       </c>
-      <c r="E7" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>1</v>
-      </c>
-      <c r="B8" s="0">
+      <c r="E7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C8">
         <v>511.00000000000006</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>864</v>
       </c>
-      <c r="E8" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>1</v>
-      </c>
-      <c r="B9" s="0">
+      <c r="E8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C9">
         <v>495.53392609582073</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>324.21151328870832</v>
       </c>
-      <c r="E9" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>2</v>
-      </c>
-      <c r="B10" s="0">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0">
+      <c r="E9">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>1600.5720858052957</v>
       </c>
-      <c r="D10" s="0">
+      <c r="D10">
         <v>468.00000000000006</v>
       </c>
-      <c r="E10" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0">
-        <v>2</v>
-      </c>
-      <c r="B11" s="0">
-        <v>2</v>
-      </c>
-      <c r="C11" s="0">
+      <c r="E10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
         <v>1609.6697320465623</v>
       </c>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>1001.071479392594</v>
       </c>
-      <c r="E11" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0">
-        <v>2</v>
-      </c>
-      <c r="B12" s="0">
-        <v>3</v>
-      </c>
-      <c r="C12" s="0">
+      <c r="E11">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <v>1242.3663165587568</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>1006.8421111887042</v>
       </c>
-      <c r="E12" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0">
-        <v>2</v>
-      </c>
-      <c r="B13" s="0">
-        <v>4</v>
-      </c>
-      <c r="C13" s="0">
+      <c r="E12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
         <v>1237.4073597680974</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D13">
         <v>465.2096389680803</v>
       </c>
-      <c r="E13" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0">
-        <v>2</v>
-      </c>
-      <c r="B14" s="0">
+      <c r="E13">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14">
         <v>856</v>
       </c>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>465</v>
       </c>
-      <c r="E14" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0">
-        <v>2</v>
-      </c>
-      <c r="B15" s="0">
+      <c r="E14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
         <v>6</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>873.00660123453724</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>1005.6623713982146</v>
       </c>
-      <c r="E15" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0">
-        <v>2</v>
-      </c>
-      <c r="B16" s="0">
+      <c r="E15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>489.41224563335277</v>
       </c>
-      <c r="D16" s="0">
+      <c r="D16">
         <v>1004.1859653421242</v>
       </c>
-      <c r="E16" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0">
-        <v>2</v>
-      </c>
-      <c r="B17" s="0">
+      <c r="E16">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
         <v>8</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C17">
         <v>476.00000000000006</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>460.54026768194427</v>
       </c>
-      <c r="E17" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0">
-        <v>3</v>
-      </c>
-      <c r="B18" s="0">
-        <v>1</v>
-      </c>
-      <c r="C18" s="0">
+      <c r="E17">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
         <v>1471.1978278146719</v>
       </c>
-      <c r="D18" s="0">
+      <c r="D18">
         <v>323.19938864339537</v>
       </c>
-      <c r="E18" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0">
-        <v>3</v>
-      </c>
-      <c r="B19" s="0">
-        <v>2</v>
-      </c>
-      <c r="C19" s="0">
+      <c r="E18">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
         <v>1480.7441676226731</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D19">
         <v>861.07660330574492</v>
       </c>
-      <c r="E19" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0">
-        <v>3</v>
-      </c>
-      <c r="B20" s="0">
-        <v>3</v>
-      </c>
-      <c r="C20" s="0">
+      <c r="E19">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
         <v>1107.4778732563907</v>
       </c>
-      <c r="D20" s="0">
+      <c r="D20">
         <v>862.70594190979659</v>
       </c>
-      <c r="E20" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0">
-        <v>3</v>
-      </c>
-      <c r="B21" s="0">
-        <v>4</v>
-      </c>
-      <c r="C21" s="0">
+      <c r="E20">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
         <v>1099</v>
       </c>
-      <c r="D21" s="0">
+      <c r="D21">
         <v>320</v>
       </c>
-      <c r="E21" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0">
-        <v>3</v>
-      </c>
-      <c r="B22" s="0">
+      <c r="E21">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
         <v>5</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C22">
         <v>717.76067643648571</v>
       </c>
-      <c r="D22" s="0">
+      <c r="D22">
         <v>317.62199039186692</v>
       </c>
-      <c r="E22" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0">
-        <v>3</v>
-      </c>
-      <c r="B23" s="0">
+      <c r="E22">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
         <v>6</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C23">
         <v>731.65336961722619</v>
       </c>
-      <c r="D23" s="0">
+      <c r="D23">
         <v>856.98769856330478</v>
       </c>
-      <c r="E23" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0">
-        <v>3</v>
-      </c>
-      <c r="B24" s="0">
+      <c r="E23">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
         <v>7</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C24">
         <v>353</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D24">
         <v>853</v>
       </c>
-      <c r="E24" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0">
-        <v>3</v>
-      </c>
-      <c r="B25" s="0">
+      <c r="E24">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
         <v>8</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C25">
         <v>339</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D25">
         <v>316</v>
       </c>
-      <c r="E25" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0">
-        <v>4</v>
-      </c>
-      <c r="B26" s="0">
-        <v>1</v>
-      </c>
-      <c r="C26" s="0">
+      <c r="E25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
         <v>1468.5057035800305</v>
       </c>
-      <c r="D26" s="0">
+      <c r="D26">
         <v>459</v>
       </c>
-      <c r="E26" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0">
-        <v>4</v>
-      </c>
-      <c r="B27" s="0">
-        <v>2</v>
-      </c>
-      <c r="C27" s="0">
+      <c r="E26">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
         <v>1472</v>
       </c>
-      <c r="D27" s="0">
+      <c r="D27">
         <v>996.99999999999989</v>
       </c>
-      <c r="E27" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0">
-        <v>4</v>
-      </c>
-      <c r="B28" s="0">
-        <v>3</v>
-      </c>
-      <c r="C28" s="0">
+      <c r="E27">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
         <v>1101.4447738129099</v>
       </c>
-      <c r="D28" s="0">
+      <c r="D28">
         <v>998.83641054114321</v>
       </c>
-      <c r="E28" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0">
-        <v>4</v>
-      </c>
-      <c r="B29" s="0">
-        <v>4</v>
-      </c>
-      <c r="C29" s="0">
+      <c r="E28">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
         <v>1095</v>
       </c>
-      <c r="D29" s="0">
+      <c r="D29">
         <v>458.12107140231734</v>
       </c>
-      <c r="E29" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0">
-        <v>4</v>
-      </c>
-      <c r="B30" s="0">
+      <c r="E29">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
         <v>5</v>
       </c>
-      <c r="C30" s="0">
+      <c r="C30">
         <v>712.39773670552825</v>
       </c>
-      <c r="D30" s="0">
+      <c r="D30">
         <v>454.30329088212028</v>
       </c>
-      <c r="E30" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0">
-        <v>4</v>
-      </c>
-      <c r="B31" s="0">
+      <c r="E30">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
         <v>6</v>
       </c>
-      <c r="C31" s="0">
+      <c r="C31">
         <v>727.55746695772802</v>
       </c>
-      <c r="D31" s="0">
+      <c r="D31">
         <v>999.00000000000011</v>
       </c>
-      <c r="E31" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0">
-        <v>4</v>
-      </c>
-      <c r="B32" s="0">
+      <c r="E31">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C32" s="0">
+      <c r="C32">
         <v>350.64925385754344</v>
       </c>
-      <c r="D32" s="0">
+      <c r="D32">
         <v>997.31908196925087</v>
       </c>
-      <c r="E32" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0">
-        <v>4</v>
-      </c>
-      <c r="B33" s="0">
+      <c r="E32">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
         <v>8</v>
       </c>
-      <c r="C33" s="0">
+      <c r="C33">
         <v>334</v>
       </c>
-      <c r="D33" s="0">
+      <c r="D33">
         <v>455.99999999999994</v>
       </c>
-      <c r="E33" s="0">
+      <c r="E33">
         <v>71</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="true"/>
-    <col min="2" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" customWidth="true"/>
-    <col min="4" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0">
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1611.2292720117171</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>338.02283380034714</v>
       </c>
-      <c r="E2" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0">
-        <v>2</v>
-      </c>
-      <c r="C3" s="0">
+      <c r="E2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1618</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>873</v>
       </c>
-      <c r="E3" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0">
-        <v>1</v>
-      </c>
-      <c r="B4" s="0">
-        <v>3</v>
-      </c>
-      <c r="C4" s="0">
+      <c r="E3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <v>1253.3901248978002</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>878.004657186401</v>
       </c>
-      <c r="E4" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>1</v>
-      </c>
-      <c r="B5" s="0">
-        <v>4</v>
-      </c>
-      <c r="C5" s="0">
+      <c r="E4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>1247.3298617001483</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>332.57633759001806</v>
       </c>
-      <c r="E5" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>1</v>
-      </c>
-      <c r="B6" s="0">
+      <c r="E5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>866.28953338071472</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>332.6477698349708</v>
       </c>
-      <c r="E6" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>1</v>
-      </c>
-      <c r="B7" s="0">
+      <c r="E6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7">
         <v>882.67516776544289</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>874.63303438425419</v>
       </c>
-      <c r="E7" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>1</v>
-      </c>
-      <c r="B8" s="0">
+      <c r="E7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C8">
         <v>499.00000000000006</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>870</v>
       </c>
-      <c r="E8" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>1</v>
-      </c>
-      <c r="B9" s="0">
+      <c r="E8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C9">
         <v>483.53392609582073</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>330.21151328870832</v>
       </c>
-      <c r="E9" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>2</v>
-      </c>
-      <c r="B10" s="0">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0">
+      <c r="E9">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>1602.5720858052957</v>
       </c>
-      <c r="D10" s="0">
+      <c r="D10">
         <v>479.00000000000006</v>
       </c>
-      <c r="E10" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0">
-        <v>2</v>
-      </c>
-      <c r="B11" s="0">
-        <v>2</v>
-      </c>
-      <c r="C11" s="0">
+      <c r="E10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
         <v>1611.6697320465623</v>
       </c>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>1012.071479392594</v>
       </c>
-      <c r="E11" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0">
-        <v>2</v>
-      </c>
-      <c r="B12" s="0">
-        <v>3</v>
-      </c>
-      <c r="C12" s="0">
+      <c r="E11">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <v>1244.3663165587568</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>1017.8421111887042</v>
       </c>
-      <c r="E12" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0">
-        <v>2</v>
-      </c>
-      <c r="B13" s="0">
-        <v>4</v>
-      </c>
-      <c r="C13" s="0">
+      <c r="E12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
         <v>1239.4073597680974</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D13">
         <v>476.2096389680803</v>
       </c>
-      <c r="E13" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0">
-        <v>2</v>
-      </c>
-      <c r="B14" s="0">
+      <c r="E13">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14">
         <v>858</v>
       </c>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>476</v>
       </c>
-      <c r="E14" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0">
-        <v>2</v>
-      </c>
-      <c r="B15" s="0">
+      <c r="E14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
         <v>6</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>875.00660123453724</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>1016.6623713982146</v>
       </c>
-      <c r="E15" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0">
-        <v>2</v>
-      </c>
-      <c r="B16" s="0">
+      <c r="E15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>491.41224563335277</v>
       </c>
-      <c r="D16" s="0">
+      <c r="D16">
         <v>1015.1859653421242</v>
       </c>
-      <c r="E16" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0">
-        <v>2</v>
-      </c>
-      <c r="B17" s="0">
+      <c r="E16">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
         <v>8</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C17">
         <v>478.00000000000006</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>471.54026768194427</v>
       </c>
-      <c r="E17" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0">
-        <v>3</v>
-      </c>
-      <c r="B18" s="0">
-        <v>1</v>
-      </c>
-      <c r="C18" s="0">
+      <c r="E17">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
         <v>1473.1978278146719</v>
       </c>
-      <c r="D18" s="0">
+      <c r="D18">
         <v>334.19938864339537</v>
       </c>
-      <c r="E18" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0">
-        <v>3</v>
-      </c>
-      <c r="B19" s="0">
-        <v>2</v>
-      </c>
-      <c r="C19" s="0">
+      <c r="E18">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
         <v>1482.7441676226731</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D19">
         <v>872.07660330574492</v>
       </c>
-      <c r="E19" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0">
-        <v>3</v>
-      </c>
-      <c r="B20" s="0">
-        <v>3</v>
-      </c>
-      <c r="C20" s="0">
+      <c r="E19">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
         <v>1109.4778732563907</v>
       </c>
-      <c r="D20" s="0">
+      <c r="D20">
         <v>873.70594190979659</v>
       </c>
-      <c r="E20" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0">
-        <v>3</v>
-      </c>
-      <c r="B21" s="0">
-        <v>4</v>
-      </c>
-      <c r="C21" s="0">
+      <c r="E20">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
         <v>1101</v>
       </c>
-      <c r="D21" s="0">
+      <c r="D21">
         <v>331</v>
       </c>
-      <c r="E21" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0">
-        <v>3</v>
-      </c>
-      <c r="B22" s="0">
+      <c r="E21">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
         <v>5</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C22">
         <v>719.76067643648571</v>
       </c>
-      <c r="D22" s="0">
+      <c r="D22">
         <v>328.62199039186692</v>
       </c>
-      <c r="E22" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0">
-        <v>3</v>
-      </c>
-      <c r="B23" s="0">
+      <c r="E22">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
         <v>6</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C23">
         <v>733.65336961722619</v>
       </c>
-      <c r="D23" s="0">
+      <c r="D23">
         <v>867.98769856330478</v>
       </c>
-      <c r="E23" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0">
-        <v>3</v>
-      </c>
-      <c r="B24" s="0">
+      <c r="E23">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
         <v>7</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C24">
         <v>355</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D24">
         <v>864</v>
       </c>
-      <c r="E24" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0">
-        <v>3</v>
-      </c>
-      <c r="B25" s="0">
+      <c r="E24">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
         <v>8</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C25">
         <v>341</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D25">
         <v>327</v>
       </c>
-      <c r="E25" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0">
-        <v>4</v>
-      </c>
-      <c r="B26" s="0">
-        <v>1</v>
-      </c>
-      <c r="C26" s="0">
+      <c r="E25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
         <v>1470.5057035800305</v>
       </c>
-      <c r="D26" s="0">
+      <c r="D26">
         <v>470</v>
       </c>
-      <c r="E26" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0">
-        <v>4</v>
-      </c>
-      <c r="B27" s="0">
-        <v>2</v>
-      </c>
-      <c r="C27" s="0">
+      <c r="E26">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
         <v>1474</v>
       </c>
-      <c r="D27" s="0">
+      <c r="D27">
         <v>1007.9999999999999</v>
       </c>
-      <c r="E27" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0">
-        <v>4</v>
-      </c>
-      <c r="B28" s="0">
-        <v>3</v>
-      </c>
-      <c r="C28" s="0">
+      <c r="E27">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
         <v>1103.4447738129099</v>
       </c>
-      <c r="D28" s="0">
+      <c r="D28">
         <v>1009.8364105411432</v>
       </c>
-      <c r="E28" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0">
-        <v>4</v>
-      </c>
-      <c r="B29" s="0">
-        <v>4</v>
-      </c>
-      <c r="C29" s="0">
+      <c r="E28">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
         <v>1097</v>
       </c>
-      <c r="D29" s="0">
+      <c r="D29">
         <v>469.12107140231734</v>
       </c>
-      <c r="E29" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0">
-        <v>4</v>
-      </c>
-      <c r="B30" s="0">
+      <c r="E29">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
         <v>5</v>
       </c>
-      <c r="C30" s="0">
+      <c r="C30">
         <v>714.39773670552825</v>
       </c>
-      <c r="D30" s="0">
+      <c r="D30">
         <v>465.30329088212028</v>
       </c>
-      <c r="E30" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0">
-        <v>4</v>
-      </c>
-      <c r="B31" s="0">
+      <c r="E30">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
         <v>6</v>
       </c>
-      <c r="C31" s="0">
+      <c r="C31">
         <v>729.55746695772802</v>
       </c>
-      <c r="D31" s="0">
+      <c r="D31">
         <v>1010.0000000000001</v>
       </c>
-      <c r="E31" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0">
-        <v>4</v>
-      </c>
-      <c r="B32" s="0">
+      <c r="E31">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C32" s="0">
+      <c r="C32">
         <v>352.64925385754344</v>
       </c>
-      <c r="D32" s="0">
+      <c r="D32">
         <v>1008.3190819692509</v>
       </c>
-      <c r="E32" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0">
-        <v>4</v>
-      </c>
-      <c r="B33" s="0">
+      <c r="E32">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
         <v>8</v>
       </c>
-      <c r="C33" s="0">
+      <c r="C33">
         <v>336</v>
       </c>
-      <c r="D33" s="0">
+      <c r="D33">
         <v>466.99999999999994</v>
       </c>
-      <c r="E33" s="0">
+      <c r="E33">
         <v>71</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3B43FF-C5D2-924D-9F0C-7C90AD2365B0}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1623.2292720117171</v>
+      </c>
+      <c r="D2">
+        <v>343.02283380034714</v>
+      </c>
+      <c r="E2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1630</v>
+      </c>
+      <c r="D3">
+        <v>878</v>
+      </c>
+      <c r="E3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1265.3901248978002</v>
+      </c>
+      <c r="D4">
+        <v>883.004657186401</v>
+      </c>
+      <c r="E4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1259.3298617001483</v>
+      </c>
+      <c r="D5">
+        <v>337.57633759001806</v>
+      </c>
+      <c r="E5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>878.28953338071472</v>
+      </c>
+      <c r="D6">
+        <v>337.6477698349708</v>
+      </c>
+      <c r="E6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>894.67516776544289</v>
+      </c>
+      <c r="D7">
+        <v>879.63303438425419</v>
+      </c>
+      <c r="E7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>511.00000000000006</v>
+      </c>
+      <c r="D8">
+        <v>875</v>
+      </c>
+      <c r="E8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>495.53392609582073</v>
+      </c>
+      <c r="D9">
+        <v>335.21151328870832</v>
+      </c>
+      <c r="E9">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1612.5720858052957</v>
+      </c>
+      <c r="D10">
+        <v>493.00000000000006</v>
+      </c>
+      <c r="E10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1621.6697320465623</v>
+      </c>
+      <c r="D11">
+        <v>1026.071479392594</v>
+      </c>
+      <c r="E11">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1254.3663165587568</v>
+      </c>
+      <c r="D12">
+        <v>1031.8421111887042</v>
+      </c>
+      <c r="E12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1249.4073597680974</v>
+      </c>
+      <c r="D13">
+        <v>490.2096389680803</v>
+      </c>
+      <c r="E13">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>868</v>
+      </c>
+      <c r="D14">
+        <v>490</v>
+      </c>
+      <c r="E14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>885.00660123453724</v>
+      </c>
+      <c r="D15">
+        <v>1030.6623713982146</v>
+      </c>
+      <c r="E15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>501.41224563335277</v>
+      </c>
+      <c r="D16">
+        <v>1029.1859653421243</v>
+      </c>
+      <c r="E16">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>488.00000000000006</v>
+      </c>
+      <c r="D17">
+        <v>485.54026768194427</v>
+      </c>
+      <c r="E17">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1485.1978278146719</v>
+      </c>
+      <c r="D18">
+        <v>336.19938864339537</v>
+      </c>
+      <c r="E18">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1494.7441676226731</v>
+      </c>
+      <c r="D19">
+        <v>874.07660330574492</v>
+      </c>
+      <c r="E19">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1121.4778732563907</v>
+      </c>
+      <c r="D20">
+        <v>875.70594190979659</v>
+      </c>
+      <c r="E20">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1113</v>
+      </c>
+      <c r="D21">
+        <v>333</v>
+      </c>
+      <c r="E21">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>731.76067643648571</v>
+      </c>
+      <c r="D22">
+        <v>330.62199039186692</v>
+      </c>
+      <c r="E22">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>745.65336961722619</v>
+      </c>
+      <c r="D23">
+        <v>869.98769856330478</v>
+      </c>
+      <c r="E23">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>367</v>
+      </c>
+      <c r="D24">
+        <v>866</v>
+      </c>
+      <c r="E24">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>353</v>
+      </c>
+      <c r="D25">
+        <v>329</v>
+      </c>
+      <c r="E25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1470.5057035800305</v>
+      </c>
+      <c r="D26">
+        <v>477</v>
+      </c>
+      <c r="E26">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1474</v>
+      </c>
+      <c r="D27">
+        <v>1014.9999999999999</v>
+      </c>
+      <c r="E27">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1103.4447738129099</v>
+      </c>
+      <c r="D28">
+        <v>1016.8364105411432</v>
+      </c>
+      <c r="E28">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1097</v>
+      </c>
+      <c r="D29">
+        <v>476.12107140231734</v>
+      </c>
+      <c r="E29">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>714.39773670552825</v>
+      </c>
+      <c r="D30">
+        <v>472.30329088212028</v>
+      </c>
+      <c r="E30">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>729.55746695772802</v>
+      </c>
+      <c r="D31">
+        <v>1017.0000000000001</v>
+      </c>
+      <c r="E31">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>352.64925385754344</v>
+      </c>
+      <c r="D32">
+        <v>1015.3190819692509</v>
+      </c>
+      <c r="E32">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>336</v>
+      </c>
+      <c r="D33">
+        <v>473.99999999999994</v>
+      </c>
+      <c r="E33">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1623.2292720117171</v>
+      </c>
+      <c r="D2">
+        <v>346.02283380034714</v>
+      </c>
+      <c r="E2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1630</v>
+      </c>
+      <c r="D3">
+        <v>881</v>
+      </c>
+      <c r="E3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1265.3901248978002</v>
+      </c>
+      <c r="D4">
+        <v>886.004657186401</v>
+      </c>
+      <c r="E4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1259.3298617001483</v>
+      </c>
+      <c r="D5">
+        <v>340.57633759001806</v>
+      </c>
+      <c r="E5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>878.28953338071472</v>
+      </c>
+      <c r="D6">
+        <v>340.6477698349708</v>
+      </c>
+      <c r="E6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>894.67516776544289</v>
+      </c>
+      <c r="D7">
+        <v>882.63303438425419</v>
+      </c>
+      <c r="E7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>511.00000000000006</v>
+      </c>
+      <c r="D8">
+        <v>878</v>
+      </c>
+      <c r="E8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>495.53392609582073</v>
+      </c>
+      <c r="D9">
+        <v>338.21151328870832</v>
+      </c>
+      <c r="E9">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1614.5720858052957</v>
+      </c>
+      <c r="D10">
+        <v>487.00000000000006</v>
+      </c>
+      <c r="E10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1623.6697320465623</v>
+      </c>
+      <c r="D11">
+        <v>1020.071479392594</v>
+      </c>
+      <c r="E11">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1256.3663165587568</v>
+      </c>
+      <c r="D12">
+        <v>1025.8421111887042</v>
+      </c>
+      <c r="E12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1251.4073597680974</v>
+      </c>
+      <c r="D13">
+        <v>484.2096389680803</v>
+      </c>
+      <c r="E13">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>870</v>
+      </c>
+      <c r="D14">
+        <v>484</v>
+      </c>
+      <c r="E14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>887.00660123453724</v>
+      </c>
+      <c r="D15">
+        <v>1024.6623713982146</v>
+      </c>
+      <c r="E15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>503.41224563335277</v>
+      </c>
+      <c r="D16">
+        <v>1023.1859653421242</v>
+      </c>
+      <c r="E16">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>490.00000000000006</v>
+      </c>
+      <c r="D17">
+        <v>479.54026768194427</v>
+      </c>
+      <c r="E17">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1478.1978278146719</v>
+      </c>
+      <c r="D18">
+        <v>337.19938864339537</v>
+      </c>
+      <c r="E18">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1487.7441676226731</v>
+      </c>
+      <c r="D19">
+        <v>875.07660330574492</v>
+      </c>
+      <c r="E19">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1114.4778732563907</v>
+      </c>
+      <c r="D20">
+        <v>876.70594190979659</v>
+      </c>
+      <c r="E20">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1106</v>
+      </c>
+      <c r="D21">
+        <v>334</v>
+      </c>
+      <c r="E21">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>724.76067643648571</v>
+      </c>
+      <c r="D22">
+        <v>331.62199039186692</v>
+      </c>
+      <c r="E22">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>738.65336961722619</v>
+      </c>
+      <c r="D23">
+        <v>870.98769856330478</v>
+      </c>
+      <c r="E23">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>360</v>
+      </c>
+      <c r="D24">
+        <v>867</v>
+      </c>
+      <c r="E24">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>346</v>
+      </c>
+      <c r="D25">
+        <v>330</v>
+      </c>
+      <c r="E25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1471.5057035800305</v>
+      </c>
+      <c r="D26">
+        <v>473</v>
+      </c>
+      <c r="E26">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1475</v>
+      </c>
+      <c r="D27">
+        <v>1010.9999999999999</v>
+      </c>
+      <c r="E27">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1104.4447738129099</v>
+      </c>
+      <c r="D28">
+        <v>1012.8364105411432</v>
+      </c>
+      <c r="E28">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1098</v>
+      </c>
+      <c r="D29">
+        <v>472.12107140231734</v>
+      </c>
+      <c r="E29">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>715.39773670552825</v>
+      </c>
+      <c r="D30">
+        <v>468.30329088212028</v>
+      </c>
+      <c r="E30">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>730.55746695772802</v>
+      </c>
+      <c r="D31">
+        <v>1013.0000000000001</v>
+      </c>
+      <c r="E31">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>353.64925385754344</v>
+      </c>
+      <c r="D32">
+        <v>1011.3190819692509</v>
+      </c>
+      <c r="E32">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>337</v>
+      </c>
+      <c r="D33">
+        <v>469.99999999999994</v>
+      </c>
+      <c r="E33">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55619896-D09A-7746-A7AB-407CD32ABD7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55619896-D09A-7746-A7AB-407CD32ABD7F}">
   <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="3" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="3.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -5234,7 +6388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:29">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5316,7 +6470,7 @@
         <v>1030.8142339811116</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:29">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5398,7 +6552,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:29">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5480,7 +6634,7 @@
         <v>1005.2040069956981</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:29">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5562,7 +6716,7 @@
         <v>869.11683665181329</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:29">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5641,7 +6795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:29">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5672,7 +6826,7 @@
         <v>895.07874960000004</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:29">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5703,7 +6857,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:29">
       <c r="A9">
         <v>1</v>
       </c>
@@ -5734,7 +6888,7 @@
         <v>350.86695689999999</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:29">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5765,7 +6919,7 @@
         <v>516.2729018</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:29">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5796,7 +6950,7 @@
         <v>1054.6513580000001</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:29">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5827,7 +6981,7 @@
         <v>1057.3494989999999</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:29">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5858,7 +7012,7 @@
         <v>513.19384539999999</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:29">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5889,7 +7043,7 @@
         <v>509.53178359999998</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:29">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5920,7 +7074,7 @@
         <v>1047.1252569999999</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:29">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5951,7 +7105,7 @@
         <v>1040.8142339999999</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5982,7 +7136,7 @@
         <v>500.51792349999999</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>3</v>
       </c>
@@ -6013,7 +7167,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>3</v>
       </c>
@@ -6044,7 +7198,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>3</v>
       </c>
@@ -6075,7 +7229,7 @@
         <v>895.06141690000004</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>3</v>
       </c>
@@ -6106,7 +7260,7 @@
         <v>353.01796389999998</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>3</v>
       </c>
@@ -6137,7 +7291,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>3</v>
       </c>
@@ -6168,7 +7322,7 @@
         <v>889.48663759999999</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>3</v>
       </c>
@@ -6199,7 +7353,7 @@
         <v>888.11683670000002</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>3</v>
       </c>
@@ -6230,7 +7384,7 @@
         <v>352.31099369999998</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>4</v>
       </c>
@@ -6261,7 +7415,7 @@
         <v>490.50236369999999</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>4</v>
       </c>
@@ -6292,7 +7446,7 @@
         <v>1028.633597</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>4</v>
       </c>
@@ -6323,7 +7477,7 @@
         <v>1029.583901</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>4</v>
       </c>
@@ -6354,7 +7508,7 @@
         <v>489.16738980000002</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>4</v>
       </c>
@@ -6385,7 +7539,7 @@
         <v>486.48403630000001</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>4</v>
       </c>
@@ -6416,7 +7570,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>4</v>
       </c>
@@ -6447,7 +7601,7 @@
         <v>1021.204007</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>4</v>
       </c>
@@ -6485,14 +7639,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="16" width="12.7109375" customWidth="true"/>
+    <col min="1" max="16" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16">
       <c r="A1">
         <v>1632.2250068153903</v>
       </c>
@@ -6542,7 +7696,7 @@
         <v>1030.8142339811116</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1646.9999999999998</v>
       </c>
@@ -6592,7 +7746,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>1479.7148948701831</v>
       </c>
@@ -6642,7 +7796,7 @@
         <v>1005.2040069956981</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>1491</v>
       </c>
@@ -6700,11 +7854,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12331FAC-F287-564D-A828-85EA3FEE69F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12331FAC-F287-564D-A828-85EA3FEE69F0}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -6721,7 +7875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6752,7 +7906,7 @@
         <v>29.34225745781572</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6783,7 +7937,7 @@
         <v>840.99907164175033</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6814,7 +7968,7 @@
         <v>859.34225745781578</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6845,7 +7999,7 @@
         <v>314.34225745781572</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6876,7 +8030,7 @@
         <v>320.34137828619572</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6907,7 +8061,7 @@
         <v>863.34225745781578</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6938,7 +8092,7 @@
         <v>871.80117305920476</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>1</v>
       </c>
@@ -6969,7 +8123,7 @@
         <v>328.93127036364535</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>2</v>
       </c>
@@ -7000,7 +8154,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -7031,7 +8185,7 @@
         <v>999.47984336260345</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>2</v>
       </c>
@@ -7062,7 +8216,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>2</v>
       </c>
@@ -7093,7 +8247,7 @@
         <v>471.50098570018065</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>2</v>
       </c>
@@ -7124,7 +8278,7 @@
         <v>477.74724778007908</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>2</v>
       </c>
@@ -7155,7 +8309,7 @@
         <v>1021.0000000000001</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>2</v>
       </c>
@@ -7186,7 +8340,7 @@
         <v>1029.3219241389984</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7217,7 +8371,7 @@
         <v>488.84585525987632</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>3</v>
       </c>
@@ -7240,7 +8394,7 @@
         <v>279.48143931656074</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>3</v>
       </c>
@@ -7263,7 +8417,7 @@
         <v>813.23295593386445</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>3</v>
       </c>
@@ -7286,7 +8440,7 @@
         <v>829.28943124222167</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>3</v>
       </c>
@@ -7309,7 +8463,7 @@
         <v>282.76894231476359</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>3</v>
       </c>
@@ -7332,7 +8486,7 @@
         <v>291.00000000000006</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>3</v>
       </c>
@@ -7355,7 +8509,7 @@
         <v>831.51615876175674</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7378,7 +8532,7 @@
         <v>836.56843813389787</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7401,7 +8555,7 @@
         <v>300.52825243257473</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>4</v>
       </c>
@@ -7432,7 +8586,7 @@
         <v>28.14476265348992</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>4</v>
       </c>
@@ -7463,7 +8617,7 @@
         <v>987.80748757663412</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>4</v>
       </c>
@@ -7494,7 +8648,7 @@
         <v>998.63525095173111</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>4</v>
       </c>
@@ -7525,7 +8679,7 @@
         <v>453.14476265348998</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>4</v>
       </c>
@@ -7556,7 +8710,7 @@
         <v>462.61791541004521</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>4</v>
       </c>
@@ -7587,7 +8741,7 @@
         <v>1005.4059517454439</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>4</v>
       </c>
@@ -7618,7 +8772,7 @@
         <v>1011.1447626534898</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>4</v>
       </c>
@@ -7656,14 +8810,14 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A8B513D-DF9C-6D4B-8EB9-67E97D41F236}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A8B513D-DF9C-6D4B-8EB9-67E97D41F236}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -7680,7 +8834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7697,7 +8851,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7714,7 +8868,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -7731,7 +8885,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -7748,7 +8902,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -7765,7 +8919,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -7782,7 +8936,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
@@ -7799,7 +8953,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
@@ -7816,7 +8970,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>2</v>
       </c>
@@ -7833,7 +8987,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>2</v>
       </c>
@@ -7850,7 +9004,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>2</v>
       </c>
@@ -7867,7 +9021,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>2</v>
       </c>
@@ -7884,7 +9038,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2</v>
       </c>
@@ -7901,7 +9055,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2</v>
       </c>
@@ -7918,7 +9072,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
@@ -7935,7 +9089,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7952,7 +9106,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>3</v>
       </c>
@@ -7969,7 +9123,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>3</v>
       </c>
@@ -7986,7 +9140,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>3</v>
       </c>
@@ -8003,7 +9157,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>3</v>
       </c>
@@ -8020,7 +9174,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>3</v>
       </c>
@@ -8037,7 +9191,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>3</v>
       </c>
@@ -8054,7 +9208,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8071,7 +9225,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8088,7 +9242,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>4</v>
       </c>
@@ -8105,7 +9259,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>4</v>
       </c>
@@ -8122,7 +9276,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>4</v>
       </c>
@@ -8139,7 +9293,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>4</v>
       </c>
@@ -8156,7 +9310,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>4</v>
       </c>
@@ -8173,7 +9327,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>4</v>
       </c>
@@ -8190,7 +9344,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>4</v>
       </c>
@@ -8207,7 +9361,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>4</v>
       </c>
@@ -8231,16 +9385,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -8257,7 +9411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8274,7 +9428,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8291,7 +9445,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8308,7 +9462,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8325,7 +9479,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8342,7 +9496,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8359,7 +9513,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
@@ -8376,7 +9530,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
@@ -8393,7 +9547,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8410,7 +9564,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8427,7 +9581,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8444,7 +9598,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8461,7 +9615,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8478,7 +9632,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8495,7 +9649,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8512,7 +9666,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8529,7 +9683,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>3</v>
       </c>
@@ -8546,7 +9700,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>3</v>
       </c>
@@ -8563,7 +9717,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>3</v>
       </c>
@@ -8580,7 +9734,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>3</v>
       </c>
@@ -8597,7 +9751,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>3</v>
       </c>
@@ -8614,7 +9768,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>3</v>
       </c>
@@ -8631,7 +9785,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8648,7 +9802,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8665,7 +9819,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>4</v>
       </c>
@@ -8682,7 +9836,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>4</v>
       </c>
@@ -8699,7 +9853,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>4</v>
       </c>
@@ -8716,7 +9870,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>4</v>
       </c>
@@ -8733,7 +9887,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>4</v>
       </c>
@@ -8750,7 +9904,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>4</v>
       </c>
@@ -8767,7 +9921,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>4</v>
       </c>
@@ -8784,7 +9938,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>4</v>
       </c>
@@ -8808,16 +9962,16 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -8834,7 +9988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8851,7 +10005,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8868,7 +10022,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8885,7 +10039,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8902,7 +10056,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8919,7 +10073,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8936,7 +10090,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
@@ -8953,7 +10107,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
@@ -8970,7 +10124,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8987,7 +10141,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>2</v>
       </c>
@@ -9004,7 +10158,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>2</v>
       </c>
@@ -9021,7 +10175,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>2</v>
       </c>
@@ -9038,7 +10192,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2</v>
       </c>
@@ -9055,7 +10209,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2</v>
       </c>
@@ -9072,7 +10226,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
@@ -9089,7 +10243,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
@@ -9106,7 +10260,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>3</v>
       </c>
@@ -9123,7 +10277,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>3</v>
       </c>
@@ -9140,7 +10294,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>3</v>
       </c>
@@ -9157,7 +10311,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>3</v>
       </c>
@@ -9174,7 +10328,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>3</v>
       </c>
@@ -9191,7 +10345,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>3</v>
       </c>
@@ -9208,7 +10362,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>3</v>
       </c>
@@ -9225,7 +10379,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>3</v>
       </c>
@@ -9242,7 +10396,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>4</v>
       </c>
@@ -9259,7 +10413,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>4</v>
       </c>
@@ -9276,7 +10430,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>4</v>
       </c>
@@ -9293,7 +10447,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>4</v>
       </c>
@@ -9310,7 +10464,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>4</v>
       </c>
@@ -9327,7 +10481,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>4</v>
       </c>
@@ -9344,7 +10498,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>4</v>
       </c>
@@ -9361,7 +10515,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>4</v>
       </c>
@@ -9385,16 +10539,16 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B4C6AA-75FF-D04D-AEB0-D50F87D3190D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B4C6AA-75FF-D04D-AEB0-D50F87D3190D}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -9411,7 +10565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -9428,7 +10582,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -9445,7 +10599,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -9462,7 +10616,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -9479,7 +10633,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -9496,7 +10650,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -9513,7 +10667,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
@@ -9530,7 +10684,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
@@ -9547,7 +10701,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>2</v>
       </c>
@@ -9564,7 +10718,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>2</v>
       </c>
@@ -9581,7 +10735,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>2</v>
       </c>
@@ -9598,7 +10752,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>2</v>
       </c>
@@ -9615,7 +10769,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2</v>
       </c>
@@ -9632,7 +10786,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2</v>
       </c>
@@ -9649,7 +10803,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
@@ -9666,7 +10820,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
@@ -9683,7 +10837,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>3</v>
       </c>
@@ -9700,7 +10854,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>3</v>
       </c>
@@ -9717,7 +10871,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>3</v>
       </c>
@@ -9734,7 +10888,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>3</v>
       </c>
@@ -9751,7 +10905,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>3</v>
       </c>
@@ -9768,7 +10922,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>3</v>
       </c>
@@ -9785,7 +10939,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>3</v>
       </c>
@@ -9802,7 +10956,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>3</v>
       </c>
@@ -9819,7 +10973,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>4</v>
       </c>
@@ -9836,7 +10990,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>4</v>
       </c>
@@ -9853,7 +11007,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>4</v>
       </c>
@@ -9870,7 +11024,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>4</v>
       </c>
@@ -9887,7 +11041,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>4</v>
       </c>
@@ -9904,7 +11058,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>4</v>
       </c>
@@ -9921,7 +11075,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>4</v>
       </c>
@@ -9938,7 +11092,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>4</v>
       </c>
@@ -9962,16 +11116,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="1" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -9988,7 +11142,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -10005,7 +11159,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -10022,7 +11176,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -10039,7 +11193,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -10056,7 +11210,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -10073,7 +11227,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -10090,7 +11244,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
@@ -10107,7 +11261,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
@@ -10124,7 +11278,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>2</v>
       </c>
@@ -10141,7 +11295,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>2</v>
       </c>
@@ -10158,7 +11312,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>2</v>
       </c>
@@ -10175,7 +11329,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>2</v>
       </c>
@@ -10192,7 +11346,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>2</v>
       </c>
@@ -10209,7 +11363,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>2</v>
       </c>
@@ -10226,7 +11380,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>2</v>
       </c>
@@ -10243,7 +11397,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
@@ -10260,7 +11414,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>3</v>
       </c>
@@ -10277,7 +11431,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>3</v>
       </c>
@@ -10294,7 +11448,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>3</v>
       </c>
@@ -10311,7 +11465,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>3</v>
       </c>
@@ -10328,7 +11482,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>3</v>
       </c>
@@ -10345,7 +11499,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>3</v>
       </c>
@@ -10362,7 +11516,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>3</v>
       </c>
@@ -10379,7 +11533,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>3</v>
       </c>
@@ -10396,7 +11550,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>4</v>
       </c>
@@ -10413,7 +11567,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>4</v>
       </c>
@@ -10430,7 +11584,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>4</v>
       </c>
@@ -10447,7 +11601,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>4</v>
       </c>
@@ -10464,7 +11618,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>4</v>
       </c>
@@ -10481,7 +11635,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>4</v>
       </c>
@@ -10498,7 +11652,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>4</v>
       </c>
@@ -10515,7 +11669,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>4</v>
       </c>

--- a/Soft X-ray/Four-View/fiberPositions.xlsx
+++ b/Soft X-ray/Four-View/fiberPositions.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5518C181-A4ED-6143-AB45-9714AB145648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1100" windowWidth="28800" windowHeight="16160" firstSheet="4" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1100" windowWidth="28800" windowHeight="16160" firstSheet="4" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="230921" sheetId="4" r:id="rId1"/>
@@ -30,8 +30,13 @@
     <sheet name="240828" sheetId="15" r:id="rId15"/>
     <sheet name="250325_old" sheetId="16" r:id="rId16"/>
     <sheet name="250328_old" sheetId="17" r:id="rId17"/>
+    <sheet name="250325" sheetId="18" r:id="rId21"/>
+    <sheet name="250328" sheetId="19" r:id="rId22"/>
+    <sheet name="251109" sheetId="20" r:id="rId23"/>
+    <sheet name="251111" sheetId="21" r:id="rId24"/>
+    <sheet name="230830" sheetId="22" r:id="rId25"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -52,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="154" uniqueCount="23">
   <si>
     <t>center_X</t>
     <phoneticPr fontId="1"/>
@@ -134,7 +139,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="3">
     <font>
       <sz val="12"/>
@@ -168,7 +173,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -190,22 +195,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -224,7 +231,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -375,7 +382,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -399,9 +406,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -425,7 +432,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -460,7 +467,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -478,7 +485,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -503,7 +510,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -519,15 +526,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="3.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -547,7 +554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -584,7 +591,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -621,7 +628,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -658,7 +665,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -695,7 +702,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -732,7 +739,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -769,7 +776,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -806,7 +813,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -843,7 +850,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -880,7 +887,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -917,7 +924,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -954,7 +961,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -991,7 +998,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1028,7 +1035,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1065,7 +1072,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1102,7 +1109,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1139,7 +1146,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -1176,7 +1183,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1213,7 +1220,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1250,7 +1257,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1287,7 +1294,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1324,7 +1331,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1361,7 +1368,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1398,7 +1405,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1435,7 +1442,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -1472,7 +1479,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -1509,7 +1516,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -1546,7 +1553,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -1583,7 +1590,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -1620,7 +1627,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -1657,7 +1664,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -1694,7 +1701,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -1738,16 +1745,16 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06735BCB-ED1E-904B-B816-90CA8290FBD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06735BCB-ED1E-904B-B816-90CA8290FBD5}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1764,7 +1771,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1781,7 +1788,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1798,7 +1805,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1815,7 +1822,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1832,7 +1839,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1849,7 +1856,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1866,7 +1873,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1883,7 +1890,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1900,7 +1907,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1917,7 +1924,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1934,7 +1941,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1951,7 +1958,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1968,7 +1975,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1985,7 +1992,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2002,7 +2009,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2019,7 +2026,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2036,7 +2043,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -2053,7 +2060,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2070,7 +2077,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -2087,7 +2094,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2104,7 +2111,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2121,7 +2128,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2138,7 +2145,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2155,7 +2162,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2172,7 +2179,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -2189,7 +2196,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -2206,7 +2213,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -2223,7 +2230,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2240,7 +2247,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2257,7 +2264,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2274,7 +2281,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -2291,7 +2298,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -2315,16 +2322,16 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -2341,7 +2348,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2358,7 +2365,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2375,7 +2382,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2392,7 +2399,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2409,7 +2416,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2426,7 +2433,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2443,7 +2450,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2460,7 +2467,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -2477,7 +2484,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2494,7 +2501,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2511,7 +2518,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2528,7 +2535,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2545,7 +2552,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2562,7 +2569,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2579,7 +2586,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2596,7 +2603,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2613,7 +2620,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -2630,7 +2637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -2647,7 +2654,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -2664,7 +2671,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2681,7 +2688,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2698,7 +2705,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2715,7 +2722,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2732,7 +2739,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2749,7 +2756,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -2766,7 +2773,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -2783,7 +2790,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -2800,7 +2807,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -2817,7 +2824,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -2834,7 +2841,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2851,7 +2858,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -2868,7 +2875,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -2892,16 +2899,16 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -2918,7 +2925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2935,7 +2942,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2952,7 +2959,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2969,7 +2976,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2986,7 +2993,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3003,7 +3010,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3020,7 +3027,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3037,7 +3044,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -3054,7 +3061,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3071,7 +3078,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3088,7 +3095,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3105,7 +3112,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3122,7 +3129,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3139,7 +3146,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3156,7 +3163,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3173,7 +3180,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3190,7 +3197,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -3207,7 +3214,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -3224,7 +3231,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -3241,7 +3248,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -3258,7 +3265,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -3275,7 +3282,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -3292,7 +3299,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -3309,7 +3316,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -3326,7 +3333,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -3343,7 +3350,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -3360,7 +3367,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -3377,7 +3384,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -3394,7 +3401,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -3411,7 +3418,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -3428,7 +3435,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -3445,7 +3452,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -3469,16 +3476,16 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -3495,7 +3502,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3512,7 +3519,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3529,7 +3536,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3546,7 +3553,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3563,7 +3570,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3580,7 +3587,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3597,7 +3604,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3614,7 +3621,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -3631,7 +3638,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3648,7 +3655,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3665,7 +3672,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3682,7 +3689,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3699,7 +3706,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3716,7 +3723,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3733,7 +3740,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3750,7 +3757,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3767,7 +3774,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -3784,7 +3791,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -3801,7 +3808,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -3818,7 +3825,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -3835,7 +3842,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -3852,7 +3859,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -3869,7 +3876,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -3886,7 +3893,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -3903,7 +3910,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -3920,7 +3927,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -3937,7 +3944,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -3954,7 +3961,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -3971,7 +3978,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -3988,7 +3995,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -4005,7 +4012,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -4022,7 +4029,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -4046,573 +4053,575 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+    <col min="2" max="2" width="7.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
+    <row r="2">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0">
         <v>1623.2292720117171</v>
       </c>
-      <c r="D2">
-        <v>332.02283380034714</v>
-      </c>
-      <c r="E2">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
+      <c r="D2" s="0">
+        <v>330.02283380034714</v>
+      </c>
+      <c r="E2" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0">
+        <v>2</v>
+      </c>
+      <c r="C3" s="0">
         <v>1630</v>
       </c>
-      <c r="D3">
-        <v>867</v>
-      </c>
-      <c r="E3">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
+      <c r="D3" s="0">
+        <v>865</v>
+      </c>
+      <c r="E3" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0">
         <v>1265.3901248978002</v>
       </c>
-      <c r="D4">
-        <v>872.004657186401</v>
-      </c>
-      <c r="E4">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
+      <c r="D4" s="0">
+        <v>870.004657186401</v>
+      </c>
+      <c r="E4" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>1</v>
+      </c>
+      <c r="B5" s="0">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0">
         <v>1259.3298617001483</v>
       </c>
-      <c r="D5">
-        <v>326.57633759001806</v>
-      </c>
-      <c r="E5">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
+      <c r="D5" s="0">
+        <v>324.57633759001806</v>
+      </c>
+      <c r="E5" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>1</v>
+      </c>
+      <c r="B6" s="0">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <v>878.28953338071472</v>
       </c>
-      <c r="D6">
-        <v>326.6477698349708</v>
-      </c>
-      <c r="E6">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
+      <c r="D6" s="0">
+        <v>324.6477698349708</v>
+      </c>
+      <c r="E6" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>1</v>
+      </c>
+      <c r="B7" s="0">
         <v>6</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0">
         <v>894.67516776544289</v>
       </c>
-      <c r="D7">
-        <v>868.63303438425419</v>
-      </c>
-      <c r="E7">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
+      <c r="D7" s="0">
+        <v>866.63303438425419</v>
+      </c>
+      <c r="E7" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>1</v>
+      </c>
+      <c r="B8" s="0">
         <v>7</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>511.00000000000006</v>
       </c>
-      <c r="D8">
-        <v>864</v>
-      </c>
-      <c r="E8">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
+      <c r="D8" s="0">
+        <v>862</v>
+      </c>
+      <c r="E8" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>1</v>
+      </c>
+      <c r="B9" s="0">
         <v>8</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0">
         <v>495.53392609582073</v>
       </c>
-      <c r="D9">
-        <v>324.21151328870832</v>
-      </c>
-      <c r="E9">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
+      <c r="D9" s="0">
+        <v>322.21151328870832</v>
+      </c>
+      <c r="E9" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>2</v>
+      </c>
+      <c r="B10" s="0">
+        <v>1</v>
+      </c>
+      <c r="C10" s="0">
         <v>1600.5720858052957</v>
       </c>
-      <c r="D10">
-        <v>468.00000000000006</v>
-      </c>
-      <c r="E10">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
+      <c r="D10" s="0">
+        <v>476.00000000000006</v>
+      </c>
+      <c r="E10" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>2</v>
+      </c>
+      <c r="B11" s="0">
+        <v>2</v>
+      </c>
+      <c r="C11" s="0">
         <v>1609.6697320465623</v>
       </c>
-      <c r="D11">
-        <v>1001.071479392594</v>
-      </c>
-      <c r="E11">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12">
+      <c r="D11" s="0">
+        <v>1009.071479392594</v>
+      </c>
+      <c r="E11" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>2</v>
+      </c>
+      <c r="B12" s="0">
+        <v>3</v>
+      </c>
+      <c r="C12" s="0">
         <v>1242.3663165587568</v>
       </c>
-      <c r="D12">
-        <v>1006.8421111887042</v>
-      </c>
-      <c r="E12">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13">
+      <c r="D12" s="0">
+        <v>1014.8421111887042</v>
+      </c>
+      <c r="E12" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>2</v>
+      </c>
+      <c r="B13" s="0">
+        <v>4</v>
+      </c>
+      <c r="C13" s="0">
         <v>1237.4073597680974</v>
       </c>
-      <c r="D13">
-        <v>465.2096389680803</v>
-      </c>
-      <c r="E13">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14">
+      <c r="D13" s="0">
+        <v>473.2096389680803</v>
+      </c>
+      <c r="E13" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>2</v>
+      </c>
+      <c r="B14" s="0">
         <v>5</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="0">
         <v>856</v>
       </c>
-      <c r="D14">
-        <v>465</v>
-      </c>
-      <c r="E14">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15">
+      <c r="D14" s="0">
+        <v>473</v>
+      </c>
+      <c r="E14" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>2</v>
+      </c>
+      <c r="B15" s="0">
         <v>6</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="0">
         <v>873.00660123453724</v>
       </c>
-      <c r="D15">
-        <v>1005.6623713982146</v>
-      </c>
-      <c r="E15">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="B16">
+      <c r="D15" s="0">
+        <v>1013.6623713982146</v>
+      </c>
+      <c r="E15" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>2</v>
+      </c>
+      <c r="B16" s="0">
         <v>7</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="0">
         <v>489.41224563335277</v>
       </c>
-      <c r="D16">
-        <v>1004.1859653421242</v>
-      </c>
-      <c r="E16">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17">
+      <c r="D16" s="0">
+        <v>1012.1859653421242</v>
+      </c>
+      <c r="E16" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>2</v>
+      </c>
+      <c r="B17" s="0">
         <v>8</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="0">
         <v>476.00000000000006</v>
       </c>
-      <c r="D17">
-        <v>460.54026768194427</v>
-      </c>
-      <c r="E17">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>3</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
+      <c r="D17" s="0">
+        <v>468.54026768194427</v>
+      </c>
+      <c r="E17" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>3</v>
+      </c>
+      <c r="B18" s="0">
+        <v>1</v>
+      </c>
+      <c r="C18" s="0">
         <v>1471.1978278146719</v>
       </c>
-      <c r="D18">
-        <v>323.19938864339537</v>
-      </c>
-      <c r="E18">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>3</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19">
+      <c r="D18" s="0">
+        <v>311.19938864339537</v>
+      </c>
+      <c r="E18" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>3</v>
+      </c>
+      <c r="B19" s="0">
+        <v>2</v>
+      </c>
+      <c r="C19" s="0">
         <v>1480.7441676226731</v>
       </c>
-      <c r="D19">
-        <v>861.07660330574492</v>
-      </c>
-      <c r="E19">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>3</v>
-      </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20">
+      <c r="D19" s="0">
+        <v>849.07660330574492</v>
+      </c>
+      <c r="E19" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>3</v>
+      </c>
+      <c r="B20" s="0">
+        <v>3</v>
+      </c>
+      <c r="C20" s="0">
         <v>1107.4778732563907</v>
       </c>
-      <c r="D20">
-        <v>862.70594190979659</v>
-      </c>
-      <c r="E20">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>3</v>
-      </c>
-      <c r="B21">
-        <v>4</v>
-      </c>
-      <c r="C21">
+      <c r="D20" s="0">
+        <v>850.70594190979659</v>
+      </c>
+      <c r="E20" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>3</v>
+      </c>
+      <c r="B21" s="0">
+        <v>4</v>
+      </c>
+      <c r="C21" s="0">
         <v>1099</v>
       </c>
-      <c r="D21">
-        <v>320</v>
-      </c>
-      <c r="E21">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>3</v>
-      </c>
-      <c r="B22">
+      <c r="D21" s="0">
+        <v>308</v>
+      </c>
+      <c r="E21" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>3</v>
+      </c>
+      <c r="B22" s="0">
         <v>5</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="0">
         <v>717.76067643648571</v>
       </c>
-      <c r="D22">
-        <v>317.62199039186692</v>
-      </c>
-      <c r="E22">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>3</v>
-      </c>
-      <c r="B23">
+      <c r="D22" s="0">
+        <v>305.62199039186692</v>
+      </c>
+      <c r="E22" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>3</v>
+      </c>
+      <c r="B23" s="0">
         <v>6</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="0">
         <v>731.65336961722619</v>
       </c>
-      <c r="D23">
-        <v>856.98769856330478</v>
-      </c>
-      <c r="E23">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24">
+      <c r="D23" s="0">
+        <v>844.98769856330478</v>
+      </c>
+      <c r="E23" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>3</v>
+      </c>
+      <c r="B24" s="0">
         <v>7</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="0">
         <v>353</v>
       </c>
-      <c r="D24">
-        <v>853</v>
-      </c>
-      <c r="E24">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>3</v>
-      </c>
-      <c r="B25">
+      <c r="D24" s="0">
+        <v>841</v>
+      </c>
+      <c r="E24" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>3</v>
+      </c>
+      <c r="B25" s="0">
         <v>8</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="0">
         <v>339</v>
       </c>
-      <c r="D25">
-        <v>316</v>
-      </c>
-      <c r="E25">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>4</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>1468.5057035800305</v>
-      </c>
-      <c r="D26">
-        <v>459</v>
-      </c>
-      <c r="E26">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>4</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <v>1472</v>
-      </c>
-      <c r="D27">
-        <v>996.99999999999989</v>
-      </c>
-      <c r="E27">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>4</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
-      </c>
-      <c r="C28">
-        <v>1101.4447738129099</v>
-      </c>
-      <c r="D28">
-        <v>998.83641054114321</v>
-      </c>
-      <c r="E28">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>4</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29">
-        <v>1095</v>
-      </c>
-      <c r="D29">
-        <v>458.12107140231734</v>
-      </c>
-      <c r="E29">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>4</v>
-      </c>
-      <c r="B30">
+      <c r="D25" s="0">
+        <v>304</v>
+      </c>
+      <c r="E25" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>4</v>
+      </c>
+      <c r="B26" s="0">
+        <v>1</v>
+      </c>
+      <c r="C26" s="0">
+        <v>1467.5057035800305</v>
+      </c>
+      <c r="D26" s="0">
+        <v>457</v>
+      </c>
+      <c r="E26" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>4</v>
+      </c>
+      <c r="B27" s="0">
+        <v>2</v>
+      </c>
+      <c r="C27" s="0">
+        <v>1471</v>
+      </c>
+      <c r="D27" s="0">
+        <v>994.99999999999989</v>
+      </c>
+      <c r="E27" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>4</v>
+      </c>
+      <c r="B28" s="0">
+        <v>3</v>
+      </c>
+      <c r="C28" s="0">
+        <v>1100.4447738129099</v>
+      </c>
+      <c r="D28" s="0">
+        <v>996.83641054114321</v>
+      </c>
+      <c r="E28" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>4</v>
+      </c>
+      <c r="B29" s="0">
+        <v>4</v>
+      </c>
+      <c r="C29" s="0">
+        <v>1094</v>
+      </c>
+      <c r="D29" s="0">
+        <v>456.12107140231734</v>
+      </c>
+      <c r="E29" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>4</v>
+      </c>
+      <c r="B30" s="0">
         <v>5</v>
       </c>
-      <c r="C30">
-        <v>712.39773670552825</v>
-      </c>
-      <c r="D30">
-        <v>454.30329088212028</v>
-      </c>
-      <c r="E30">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>4</v>
-      </c>
-      <c r="B31">
+      <c r="C30" s="0">
+        <v>711.39773670552825</v>
+      </c>
+      <c r="D30" s="0">
+        <v>452.30329088212028</v>
+      </c>
+      <c r="E30" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>4</v>
+      </c>
+      <c r="B31" s="0">
         <v>6</v>
       </c>
-      <c r="C31">
-        <v>727.55746695772802</v>
-      </c>
-      <c r="D31">
-        <v>999.00000000000011</v>
-      </c>
-      <c r="E31">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>4</v>
-      </c>
-      <c r="B32">
+      <c r="C31" s="0">
+        <v>726.55746695772802</v>
+      </c>
+      <c r="D31" s="0">
+        <v>997.00000000000011</v>
+      </c>
+      <c r="E31" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>4</v>
+      </c>
+      <c r="B32" s="0">
         <v>7</v>
       </c>
-      <c r="C32">
-        <v>350.64925385754344</v>
-      </c>
-      <c r="D32">
-        <v>997.31908196925087</v>
-      </c>
-      <c r="E32">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>4</v>
-      </c>
-      <c r="B33">
+      <c r="C32" s="0">
+        <v>349.64925385754344</v>
+      </c>
+      <c r="D32" s="0">
+        <v>995.31908196925087</v>
+      </c>
+      <c r="E32" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>4</v>
+      </c>
+      <c r="B33" s="0">
         <v>8</v>
       </c>
-      <c r="C33">
-        <v>334</v>
-      </c>
-      <c r="D33">
-        <v>455.99999999999994</v>
-      </c>
-      <c r="E33">
+      <c r="C33" s="0">
+        <v>333</v>
+      </c>
+      <c r="D33" s="0">
+        <v>453.99999999999994</v>
+      </c>
+      <c r="E33" s="0">
         <v>71</v>
       </c>
     </row>
@@ -4623,16 +4632,16 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -4649,7 +4658,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4666,7 +4675,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4683,7 +4692,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4700,7 +4709,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4717,7 +4726,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4734,7 +4743,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4751,7 +4760,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4768,7 +4777,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4785,7 +4794,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -4802,7 +4811,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -4819,7 +4828,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -4836,7 +4845,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -4853,7 +4862,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -4870,7 +4879,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -4887,7 +4896,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -4904,7 +4913,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -4921,7 +4930,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -4938,7 +4947,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -4955,7 +4964,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -4972,7 +4981,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -4989,7 +4998,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -5006,7 +5015,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -5023,7 +5032,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -5040,7 +5049,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -5057,7 +5066,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -5074,7 +5083,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -5091,7 +5100,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -5108,7 +5117,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -5125,7 +5134,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -5142,7 +5151,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -5159,7 +5168,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -5176,7 +5185,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -5200,16 +5209,16 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3B43FF-C5D2-924D-9F0C-7C90AD2365B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3B43FF-C5D2-924D-9F0C-7C90AD2365B0}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -5226,7 +5235,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5243,7 +5252,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5260,7 +5269,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5277,7 +5286,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5294,7 +5303,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5311,7 +5320,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5328,7 +5337,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5345,7 +5354,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -5362,7 +5371,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5379,7 +5388,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5396,7 +5405,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5413,7 +5422,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5430,7 +5439,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5447,7 +5456,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5464,7 +5473,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5481,7 +5490,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5498,7 +5507,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -5515,7 +5524,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -5532,7 +5541,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -5549,7 +5558,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -5566,7 +5575,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -5583,7 +5592,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -5600,7 +5609,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -5617,7 +5626,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -5634,7 +5643,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -5651,7 +5660,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -5668,7 +5677,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -5685,7 +5694,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -5702,7 +5711,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -5719,7 +5728,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -5736,7 +5745,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -5753,7 +5762,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -5777,16 +5786,16 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -5803,7 +5812,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5820,7 +5829,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5837,7 +5846,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5854,7 +5863,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5871,7 +5880,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5888,7 +5897,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5905,7 +5914,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5922,7 +5931,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -5939,7 +5948,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5956,7 +5965,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5973,7 +5982,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5990,7 +5999,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6007,7 +6016,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6024,7 +6033,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -6041,7 +6050,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -6058,7 +6067,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -6075,7 +6084,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -6092,7 +6101,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -6109,7 +6118,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -6126,7 +6135,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -6143,7 +6152,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -6160,7 +6169,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -6177,7 +6186,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -6194,7 +6203,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -6211,7 +6220,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -6228,7 +6237,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -6245,7 +6254,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -6262,7 +6271,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -6279,7 +6288,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -6296,7 +6305,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -6313,7 +6322,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -6330,7 +6339,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -6353,16 +6362,1170 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" customWidth="true"/>
+    <col min="2" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1628.740003154807</v>
+      </c>
+      <c r="D2" s="0">
+        <v>343.0125247036006</v>
+      </c>
+      <c r="E2" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0">
+        <v>2</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1640</v>
+      </c>
+      <c r="D3" s="0">
+        <v>878.51776939116485</v>
+      </c>
+      <c r="E3" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0">
+        <v>1270.8478175628402</v>
+      </c>
+      <c r="D4" s="0">
+        <v>881.90461387263326</v>
+      </c>
+      <c r="E4" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>1</v>
+      </c>
+      <c r="B5" s="0">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0">
+        <v>1260.9999999999998</v>
+      </c>
+      <c r="D5" s="0">
+        <v>339</v>
+      </c>
+      <c r="E5" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>1</v>
+      </c>
+      <c r="B6" s="0">
+        <v>5</v>
+      </c>
+      <c r="C6" s="0">
+        <v>879.86084250484225</v>
+      </c>
+      <c r="D6" s="0">
+        <v>335.69214643529949</v>
+      </c>
+      <c r="E6" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>1</v>
+      </c>
+      <c r="B7" s="0">
+        <v>6</v>
+      </c>
+      <c r="C7" s="0">
+        <v>894.52421876117432</v>
+      </c>
+      <c r="D7" s="0">
+        <v>880.99999999999989</v>
+      </c>
+      <c r="E7" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>1</v>
+      </c>
+      <c r="B8" s="0">
+        <v>7</v>
+      </c>
+      <c r="C8" s="0">
+        <v>511.74891970656518</v>
+      </c>
+      <c r="D8" s="0">
+        <v>878.95013421079273</v>
+      </c>
+      <c r="E8" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>1</v>
+      </c>
+      <c r="B9" s="0">
+        <v>8</v>
+      </c>
+      <c r="C9" s="0">
+        <v>500.96584159356468</v>
+      </c>
+      <c r="D9" s="0">
+        <v>338.22958188004088</v>
+      </c>
+      <c r="E9" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>2</v>
+      </c>
+      <c r="B10" s="0">
+        <v>1</v>
+      </c>
+      <c r="C10" s="0">
+        <v>1617.4754154701334</v>
+      </c>
+      <c r="D10" s="0">
+        <v>493.49959138629725</v>
+      </c>
+      <c r="E10" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>2</v>
+      </c>
+      <c r="B11" s="0">
+        <v>2</v>
+      </c>
+      <c r="C11" s="0">
+        <v>1622.6898017241776</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1029.7785862262986</v>
+      </c>
+      <c r="E11" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>2</v>
+      </c>
+      <c r="B12" s="0">
+        <v>3</v>
+      </c>
+      <c r="C12" s="0">
+        <v>1253.5027933210117</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1034</v>
+      </c>
+      <c r="E12" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>2</v>
+      </c>
+      <c r="B13" s="0">
+        <v>4</v>
+      </c>
+      <c r="C13" s="0">
+        <v>1249.3158145262933</v>
+      </c>
+      <c r="D13" s="0">
+        <v>489.58588495307123</v>
+      </c>
+      <c r="E13" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>2</v>
+      </c>
+      <c r="B14" s="0">
+        <v>5</v>
+      </c>
+      <c r="C14" s="0">
+        <v>864.94671150906493</v>
+      </c>
+      <c r="D14" s="0">
+        <v>485.98499825494321</v>
+      </c>
+      <c r="E14" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>2</v>
+      </c>
+      <c r="B15" s="0">
+        <v>6</v>
+      </c>
+      <c r="C15" s="0">
+        <v>881.51181174358658</v>
+      </c>
+      <c r="D15" s="0">
+        <v>1032.499253404862</v>
+      </c>
+      <c r="E15" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>2</v>
+      </c>
+      <c r="B16" s="0">
+        <v>7</v>
+      </c>
+      <c r="C16" s="0">
+        <v>500</v>
+      </c>
+      <c r="D16" s="0">
+        <v>1029</v>
+      </c>
+      <c r="E16" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>2</v>
+      </c>
+      <c r="B17" s="0">
+        <v>8</v>
+      </c>
+      <c r="C17" s="0">
+        <v>487.20212825465023</v>
+      </c>
+      <c r="D17" s="0">
+        <v>487.81124895322654</v>
+      </c>
+      <c r="E17" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>3</v>
+      </c>
+      <c r="B18" s="0">
+        <v>1</v>
+      </c>
+      <c r="C18" s="0">
+        <v>1474.5306868592531</v>
+      </c>
+      <c r="D18" s="0">
+        <v>326.99999999999994</v>
+      </c>
+      <c r="E18" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>3</v>
+      </c>
+      <c r="B19" s="0">
+        <v>2</v>
+      </c>
+      <c r="C19" s="0">
+        <v>1487.5446336336893</v>
+      </c>
+      <c r="D19" s="0">
+        <v>864.0298918650434</v>
+      </c>
+      <c r="E19" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>3</v>
+      </c>
+      <c r="B20" s="0">
+        <v>3</v>
+      </c>
+      <c r="C20" s="0">
+        <v>1113.5091530813968</v>
+      </c>
+      <c r="D20" s="0">
+        <v>867.00000000000011</v>
+      </c>
+      <c r="E20" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>3</v>
+      </c>
+      <c r="B21" s="0">
+        <v>4</v>
+      </c>
+      <c r="C21" s="0">
+        <v>1102.6845041587553</v>
+      </c>
+      <c r="D21" s="0">
+        <v>323.17892908370311</v>
+      </c>
+      <c r="E21" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>3</v>
+      </c>
+      <c r="B22" s="0">
+        <v>5</v>
+      </c>
+      <c r="C22" s="0">
+        <v>720.01701066515921</v>
+      </c>
+      <c r="D22" s="0">
+        <v>321.26465366599678</v>
+      </c>
+      <c r="E22" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>3</v>
+      </c>
+      <c r="B23" s="0">
+        <v>6</v>
+      </c>
+      <c r="C23" s="0">
+        <v>734.4110185410824</v>
+      </c>
+      <c r="D23" s="0">
+        <v>863.30924555334536</v>
+      </c>
+      <c r="E23" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>3</v>
+      </c>
+      <c r="B24" s="0">
+        <v>7</v>
+      </c>
+      <c r="C24" s="0">
+        <v>355.45688417687649</v>
+      </c>
+      <c r="D24" s="0">
+        <v>861</v>
+      </c>
+      <c r="E24" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>3</v>
+      </c>
+      <c r="B25" s="0">
+        <v>8</v>
+      </c>
+      <c r="C25" s="0">
+        <v>343.49148056390328</v>
+      </c>
+      <c r="D25" s="0">
+        <v>322</v>
+      </c>
+      <c r="E25" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>4</v>
+      </c>
+      <c r="B26" s="0">
+        <v>1</v>
+      </c>
+      <c r="C26" s="0">
+        <v>1468.0682926045956</v>
+      </c>
+      <c r="D26" s="0">
+        <v>481</v>
+      </c>
+      <c r="E26" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>4</v>
+      </c>
+      <c r="B27" s="0">
+        <v>2</v>
+      </c>
+      <c r="C27" s="0">
+        <v>1472.6870774041925</v>
+      </c>
+      <c r="D27" s="0">
+        <v>1017.9862622663102</v>
+      </c>
+      <c r="E27" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>4</v>
+      </c>
+      <c r="B28" s="0">
+        <v>3</v>
+      </c>
+      <c r="C28" s="0">
+        <v>1101.9944670644577</v>
+      </c>
+      <c r="D28" s="0">
+        <v>1020.7574914771931</v>
+      </c>
+      <c r="E28" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>4</v>
+      </c>
+      <c r="B29" s="0">
+        <v>4</v>
+      </c>
+      <c r="C29" s="0">
+        <v>1093</v>
+      </c>
+      <c r="D29" s="0">
+        <v>475</v>
+      </c>
+      <c r="E29" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>4</v>
+      </c>
+      <c r="B30" s="0">
+        <v>5</v>
+      </c>
+      <c r="C30" s="0">
+        <v>708.51938140841287</v>
+      </c>
+      <c r="D30" s="0">
+        <v>475.48912023749961</v>
+      </c>
+      <c r="E30" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>4</v>
+      </c>
+      <c r="B31" s="0">
+        <v>6</v>
+      </c>
+      <c r="C31" s="0">
+        <v>729.50379431098156</v>
+      </c>
+      <c r="D31" s="0">
+        <v>1021</v>
+      </c>
+      <c r="E31" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>4</v>
+      </c>
+      <c r="B32" s="0">
+        <v>7</v>
+      </c>
+      <c r="C32" s="0">
+        <v>347.66249779080601</v>
+      </c>
+      <c r="D32" s="0">
+        <v>1016.3111176733956</v>
+      </c>
+      <c r="E32" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>4</v>
+      </c>
+      <c r="B33" s="0">
+        <v>8</v>
+      </c>
+      <c r="C33" s="0">
+        <v>330.49601411293042</v>
+      </c>
+      <c r="D33" s="0">
+        <v>475.00506142951207</v>
+      </c>
+      <c r="E33" s="0">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" customWidth="true"/>
+    <col min="2" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1617.740003154807</v>
+      </c>
+      <c r="D2" s="0">
+        <v>340.0125247036006</v>
+      </c>
+      <c r="E2" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0">
+        <v>2</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1629</v>
+      </c>
+      <c r="D3" s="0">
+        <v>875.51776939116485</v>
+      </c>
+      <c r="E3" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0">
+        <v>1259.8478175628402</v>
+      </c>
+      <c r="D4" s="0">
+        <v>878.90461387263326</v>
+      </c>
+      <c r="E4" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>1</v>
+      </c>
+      <c r="B5" s="0">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0">
+        <v>1249.9999999999998</v>
+      </c>
+      <c r="D5" s="0">
+        <v>336</v>
+      </c>
+      <c r="E5" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>1</v>
+      </c>
+      <c r="B6" s="0">
+        <v>5</v>
+      </c>
+      <c r="C6" s="0">
+        <v>868.86084250484225</v>
+      </c>
+      <c r="D6" s="0">
+        <v>332.69214643529949</v>
+      </c>
+      <c r="E6" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>1</v>
+      </c>
+      <c r="B7" s="0">
+        <v>6</v>
+      </c>
+      <c r="C7" s="0">
+        <v>883.52421876117432</v>
+      </c>
+      <c r="D7" s="0">
+        <v>877.99999999999989</v>
+      </c>
+      <c r="E7" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>1</v>
+      </c>
+      <c r="B8" s="0">
+        <v>7</v>
+      </c>
+      <c r="C8" s="0">
+        <v>500.74891970656518</v>
+      </c>
+      <c r="D8" s="0">
+        <v>875.95013421079273</v>
+      </c>
+      <c r="E8" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>1</v>
+      </c>
+      <c r="B9" s="0">
+        <v>8</v>
+      </c>
+      <c r="C9" s="0">
+        <v>489.96584159356468</v>
+      </c>
+      <c r="D9" s="0">
+        <v>335.22958188004088</v>
+      </c>
+      <c r="E9" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>2</v>
+      </c>
+      <c r="B10" s="0">
+        <v>1</v>
+      </c>
+      <c r="C10" s="0">
+        <v>1615.4754154701334</v>
+      </c>
+      <c r="D10" s="0">
+        <v>483.49959138629725</v>
+      </c>
+      <c r="E10" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>2</v>
+      </c>
+      <c r="B11" s="0">
+        <v>2</v>
+      </c>
+      <c r="C11" s="0">
+        <v>1620.6898017241776</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1019.7785862262986</v>
+      </c>
+      <c r="E11" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>2</v>
+      </c>
+      <c r="B12" s="0">
+        <v>3</v>
+      </c>
+      <c r="C12" s="0">
+        <v>1251.5027933210117</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1024</v>
+      </c>
+      <c r="E12" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>2</v>
+      </c>
+      <c r="B13" s="0">
+        <v>4</v>
+      </c>
+      <c r="C13" s="0">
+        <v>1247.3158145262933</v>
+      </c>
+      <c r="D13" s="0">
+        <v>479.58588495307123</v>
+      </c>
+      <c r="E13" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>2</v>
+      </c>
+      <c r="B14" s="0">
+        <v>5</v>
+      </c>
+      <c r="C14" s="0">
+        <v>862.94671150906493</v>
+      </c>
+      <c r="D14" s="0">
+        <v>475.98499825494321</v>
+      </c>
+      <c r="E14" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>2</v>
+      </c>
+      <c r="B15" s="0">
+        <v>6</v>
+      </c>
+      <c r="C15" s="0">
+        <v>879.51181174358658</v>
+      </c>
+      <c r="D15" s="0">
+        <v>1022.4992534048619</v>
+      </c>
+      <c r="E15" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>2</v>
+      </c>
+      <c r="B16" s="0">
+        <v>7</v>
+      </c>
+      <c r="C16" s="0">
+        <v>498</v>
+      </c>
+      <c r="D16" s="0">
+        <v>1019</v>
+      </c>
+      <c r="E16" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>2</v>
+      </c>
+      <c r="B17" s="0">
+        <v>8</v>
+      </c>
+      <c r="C17" s="0">
+        <v>485.20212825465023</v>
+      </c>
+      <c r="D17" s="0">
+        <v>477.81124895322654</v>
+      </c>
+      <c r="E17" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>3</v>
+      </c>
+      <c r="B18" s="0">
+        <v>1</v>
+      </c>
+      <c r="C18" s="0">
+        <v>1473.5306868592531</v>
+      </c>
+      <c r="D18" s="0">
+        <v>330.99999999999994</v>
+      </c>
+      <c r="E18" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>3</v>
+      </c>
+      <c r="B19" s="0">
+        <v>2</v>
+      </c>
+      <c r="C19" s="0">
+        <v>1486.5446336336893</v>
+      </c>
+      <c r="D19" s="0">
+        <v>868.0298918650434</v>
+      </c>
+      <c r="E19" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>3</v>
+      </c>
+      <c r="B20" s="0">
+        <v>3</v>
+      </c>
+      <c r="C20" s="0">
+        <v>1112.5091530813968</v>
+      </c>
+      <c r="D20" s="0">
+        <v>871.00000000000011</v>
+      </c>
+      <c r="E20" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>3</v>
+      </c>
+      <c r="B21" s="0">
+        <v>4</v>
+      </c>
+      <c r="C21" s="0">
+        <v>1101.6845041587553</v>
+      </c>
+      <c r="D21" s="0">
+        <v>327.17892908370311</v>
+      </c>
+      <c r="E21" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>3</v>
+      </c>
+      <c r="B22" s="0">
+        <v>5</v>
+      </c>
+      <c r="C22" s="0">
+        <v>719.01701066515921</v>
+      </c>
+      <c r="D22" s="0">
+        <v>325.26465366599678</v>
+      </c>
+      <c r="E22" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>3</v>
+      </c>
+      <c r="B23" s="0">
+        <v>6</v>
+      </c>
+      <c r="C23" s="0">
+        <v>733.4110185410824</v>
+      </c>
+      <c r="D23" s="0">
+        <v>867.30924555334536</v>
+      </c>
+      <c r="E23" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>3</v>
+      </c>
+      <c r="B24" s="0">
+        <v>7</v>
+      </c>
+      <c r="C24" s="0">
+        <v>354.45688417687649</v>
+      </c>
+      <c r="D24" s="0">
+        <v>865</v>
+      </c>
+      <c r="E24" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>3</v>
+      </c>
+      <c r="B25" s="0">
+        <v>8</v>
+      </c>
+      <c r="C25" s="0">
+        <v>342.49148056390328</v>
+      </c>
+      <c r="D25" s="0">
+        <v>326</v>
+      </c>
+      <c r="E25" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>4</v>
+      </c>
+      <c r="B26" s="0">
+        <v>1</v>
+      </c>
+      <c r="C26" s="0">
+        <v>1473.0682926045956</v>
+      </c>
+      <c r="D26" s="0">
+        <v>477</v>
+      </c>
+      <c r="E26" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>4</v>
+      </c>
+      <c r="B27" s="0">
+        <v>2</v>
+      </c>
+      <c r="C27" s="0">
+        <v>1477.6870774041925</v>
+      </c>
+      <c r="D27" s="0">
+        <v>1013.9862622663102</v>
+      </c>
+      <c r="E27" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>4</v>
+      </c>
+      <c r="B28" s="0">
+        <v>3</v>
+      </c>
+      <c r="C28" s="0">
+        <v>1106.9944670644577</v>
+      </c>
+      <c r="D28" s="0">
+        <v>1016.7574914771931</v>
+      </c>
+      <c r="E28" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>4</v>
+      </c>
+      <c r="B29" s="0">
+        <v>4</v>
+      </c>
+      <c r="C29" s="0">
+        <v>1098</v>
+      </c>
+      <c r="D29" s="0">
+        <v>471</v>
+      </c>
+      <c r="E29" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>4</v>
+      </c>
+      <c r="B30" s="0">
+        <v>5</v>
+      </c>
+      <c r="C30" s="0">
+        <v>713.51938140841287</v>
+      </c>
+      <c r="D30" s="0">
+        <v>471.48912023749961</v>
+      </c>
+      <c r="E30" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>4</v>
+      </c>
+      <c r="B31" s="0">
+        <v>6</v>
+      </c>
+      <c r="C31" s="0">
+        <v>734.50379431098156</v>
+      </c>
+      <c r="D31" s="0">
+        <v>1017</v>
+      </c>
+      <c r="E31" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>4</v>
+      </c>
+      <c r="B32" s="0">
+        <v>7</v>
+      </c>
+      <c r="C32" s="0">
+        <v>352.66249779080601</v>
+      </c>
+      <c r="D32" s="0">
+        <v>1012.3111176733956</v>
+      </c>
+      <c r="E32" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>4</v>
+      </c>
+      <c r="B33" s="0">
+        <v>8</v>
+      </c>
+      <c r="C33" s="0">
+        <v>335.49601411293042</v>
+      </c>
+      <c r="D33" s="0">
+        <v>471.00506142951207</v>
+      </c>
+      <c r="E33" s="0">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55619896-D09A-7746-A7AB-407CD32ABD7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55619896-D09A-7746-A7AB-407CD32ABD7F}">
   <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="3.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -6388,7 +7551,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6470,7 +7633,7 @@
         <v>1030.8142339811116</v>
       </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6552,7 +7715,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6634,7 +7797,7 @@
         <v>1005.2040069956981</v>
       </c>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6716,7 +7879,7 @@
         <v>869.11683665181329</v>
       </c>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6795,7 +7958,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6826,7 +7989,7 @@
         <v>895.07874960000004</v>
       </c>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6857,7 +8020,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="9" spans="1:29">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -6888,7 +8051,7 @@
         <v>350.86695689999999</v>
       </c>
     </row>
-    <row r="10" spans="1:29">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -6919,7 +8082,7 @@
         <v>516.2729018</v>
       </c>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6950,7 +8113,7 @@
         <v>1054.6513580000001</v>
       </c>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6981,7 +8144,7 @@
         <v>1057.3494989999999</v>
       </c>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -7012,7 +8175,7 @@
         <v>513.19384539999999</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -7043,7 +8206,7 @@
         <v>509.53178359999998</v>
       </c>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -7074,7 +8237,7 @@
         <v>1047.1252569999999</v>
       </c>
     </row>
-    <row r="16" spans="1:29">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -7105,7 +8268,7 @@
         <v>1040.8142339999999</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7136,7 +8299,7 @@
         <v>500.51792349999999</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -7167,7 +8330,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -7198,7 +8361,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -7229,7 +8392,7 @@
         <v>895.06141690000004</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -7260,7 +8423,7 @@
         <v>353.01796389999998</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -7291,7 +8454,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -7322,7 +8485,7 @@
         <v>889.48663759999999</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7353,7 +8516,7 @@
         <v>888.11683670000002</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7384,7 +8547,7 @@
         <v>352.31099369999998</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -7415,7 +8578,7 @@
         <v>490.50236369999999</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -7446,7 +8609,7 @@
         <v>1028.633597</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -7477,7 +8640,7 @@
         <v>1029.583901</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -7508,7 +8671,7 @@
         <v>489.16738980000002</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -7539,7 +8702,7 @@
         <v>486.48403630000001</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -7570,7 +8733,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -7601,7 +8764,7 @@
         <v>1021.204007</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -7638,15 +8801,1474 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" customWidth="true"/>
+    <col min="2" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1695</v>
+      </c>
+      <c r="D2" s="0">
+        <v>265</v>
+      </c>
+      <c r="E2" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0">
+        <v>2</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1704.9917745739383</v>
+      </c>
+      <c r="D3" s="0">
+        <v>801</v>
+      </c>
+      <c r="E3" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0">
+        <v>1338.5026868544157</v>
+      </c>
+      <c r="D4" s="0">
+        <v>806</v>
+      </c>
+      <c r="E4" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>1</v>
+      </c>
+      <c r="B5" s="0">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0">
+        <v>1327</v>
+      </c>
+      <c r="D5" s="0">
+        <v>262.5228635742792</v>
+      </c>
+      <c r="E5" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>1</v>
+      </c>
+      <c r="B6" s="0">
+        <v>5</v>
+      </c>
+      <c r="C6" s="0">
+        <v>946.99999999999989</v>
+      </c>
+      <c r="D6" s="0">
+        <v>260</v>
+      </c>
+      <c r="E6" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>1</v>
+      </c>
+      <c r="B7" s="0">
+        <v>6</v>
+      </c>
+      <c r="C7" s="0">
+        <v>965.73436213713285</v>
+      </c>
+      <c r="D7" s="0">
+        <v>807.36169114028905</v>
+      </c>
+      <c r="E7" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>1</v>
+      </c>
+      <c r="B8" s="0">
+        <v>7</v>
+      </c>
+      <c r="C8" s="0">
+        <v>583</v>
+      </c>
+      <c r="D8" s="0">
+        <v>806</v>
+      </c>
+      <c r="E8" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>1</v>
+      </c>
+      <c r="B9" s="0">
+        <v>8</v>
+      </c>
+      <c r="C9" s="0">
+        <v>569</v>
+      </c>
+      <c r="D9" s="0">
+        <v>263</v>
+      </c>
+      <c r="E9" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>2</v>
+      </c>
+      <c r="B10" s="0">
+        <v>1</v>
+      </c>
+      <c r="C10" s="0">
+        <v>1692.4744644894422</v>
+      </c>
+      <c r="D10" s="0">
+        <v>409.00000000000006</v>
+      </c>
+      <c r="E10" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>2</v>
+      </c>
+      <c r="B11" s="0">
+        <v>2</v>
+      </c>
+      <c r="C11" s="0">
+        <v>1699</v>
+      </c>
+      <c r="D11" s="0">
+        <v>945</v>
+      </c>
+      <c r="E11" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>2</v>
+      </c>
+      <c r="B12" s="0">
+        <v>3</v>
+      </c>
+      <c r="C12" s="0">
+        <v>1332.9999999999998</v>
+      </c>
+      <c r="D12" s="0">
+        <v>949.49154609272216</v>
+      </c>
+      <c r="E12" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>2</v>
+      </c>
+      <c r="B13" s="0">
+        <v>4</v>
+      </c>
+      <c r="C13" s="0">
+        <v>1325.5042809132685</v>
+      </c>
+      <c r="D13" s="0">
+        <v>405.99999999999994</v>
+      </c>
+      <c r="E13" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>2</v>
+      </c>
+      <c r="B14" s="0">
+        <v>5</v>
+      </c>
+      <c r="C14" s="0">
+        <v>941.42420632351775</v>
+      </c>
+      <c r="D14" s="0">
+        <v>403.99999999999994</v>
+      </c>
+      <c r="E14" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>2</v>
+      </c>
+      <c r="B15" s="0">
+        <v>6</v>
+      </c>
+      <c r="C15" s="0">
+        <v>960</v>
+      </c>
+      <c r="D15" s="0">
+        <v>950</v>
+      </c>
+      <c r="E15" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>2</v>
+      </c>
+      <c r="B16" s="0">
+        <v>7</v>
+      </c>
+      <c r="C16" s="0">
+        <v>578.79880651185431</v>
+      </c>
+      <c r="D16" s="0">
+        <v>947.57565299721614</v>
+      </c>
+      <c r="E16" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>2</v>
+      </c>
+      <c r="B17" s="0">
+        <v>8</v>
+      </c>
+      <c r="C17" s="0">
+        <v>562.49174180250736</v>
+      </c>
+      <c r="D17" s="0">
+        <v>406.48809251374257</v>
+      </c>
+      <c r="E17" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>3</v>
+      </c>
+      <c r="B18" s="0">
+        <v>1</v>
+      </c>
+      <c r="C18" s="0">
+        <v>1550.9999999999998</v>
+      </c>
+      <c r="D18" s="0">
+        <v>254.52238737668117</v>
+      </c>
+      <c r="E18" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>3</v>
+      </c>
+      <c r="B19" s="0">
+        <v>2</v>
+      </c>
+      <c r="C19" s="0">
+        <v>1564</v>
+      </c>
+      <c r="D19" s="0">
+        <v>792.99999999999989</v>
+      </c>
+      <c r="E19" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>3</v>
+      </c>
+      <c r="B20" s="0">
+        <v>3</v>
+      </c>
+      <c r="C20" s="0">
+        <v>1191.468376153884</v>
+      </c>
+      <c r="D20" s="0">
+        <v>798</v>
+      </c>
+      <c r="E20" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>3</v>
+      </c>
+      <c r="B21" s="0">
+        <v>4</v>
+      </c>
+      <c r="C21" s="0">
+        <v>1179</v>
+      </c>
+      <c r="D21" s="0">
+        <v>252</v>
+      </c>
+      <c r="E21" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>3</v>
+      </c>
+      <c r="B22" s="0">
+        <v>5</v>
+      </c>
+      <c r="C22" s="0">
+        <v>799</v>
+      </c>
+      <c r="D22" s="0">
+        <v>253</v>
+      </c>
+      <c r="E22" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>3</v>
+      </c>
+      <c r="B23" s="0">
+        <v>6</v>
+      </c>
+      <c r="C23" s="0">
+        <v>816</v>
+      </c>
+      <c r="D23" s="0">
+        <v>795.45214729968905</v>
+      </c>
+      <c r="E23" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>3</v>
+      </c>
+      <c r="B24" s="0">
+        <v>7</v>
+      </c>
+      <c r="C24" s="0">
+        <v>437</v>
+      </c>
+      <c r="D24" s="0">
+        <v>795</v>
+      </c>
+      <c r="E24" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>3</v>
+      </c>
+      <c r="B25" s="0">
+        <v>8</v>
+      </c>
+      <c r="C25" s="0">
+        <v>422</v>
+      </c>
+      <c r="D25" s="0">
+        <v>255.00000000000003</v>
+      </c>
+      <c r="E25" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>4</v>
+      </c>
+      <c r="B26" s="0">
+        <v>1</v>
+      </c>
+      <c r="C26" s="0">
+        <v>1549.5100088758986</v>
+      </c>
+      <c r="D26" s="0">
+        <v>402</v>
+      </c>
+      <c r="E26" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>4</v>
+      </c>
+      <c r="B27" s="0">
+        <v>2</v>
+      </c>
+      <c r="C27" s="0">
+        <v>1555.486582044831</v>
+      </c>
+      <c r="D27" s="0">
+        <v>939</v>
+      </c>
+      <c r="E27" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>4</v>
+      </c>
+      <c r="B28" s="0">
+        <v>3</v>
+      </c>
+      <c r="C28" s="0">
+        <v>1186</v>
+      </c>
+      <c r="D28" s="0">
+        <v>944</v>
+      </c>
+      <c r="E28" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>4</v>
+      </c>
+      <c r="B29" s="0">
+        <v>4</v>
+      </c>
+      <c r="C29" s="0">
+        <v>1177</v>
+      </c>
+      <c r="D29" s="0">
+        <v>399.473464652188</v>
+      </c>
+      <c r="E29" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>4</v>
+      </c>
+      <c r="B30" s="0">
+        <v>5</v>
+      </c>
+      <c r="C30" s="0">
+        <v>793.50819995609561</v>
+      </c>
+      <c r="D30" s="0">
+        <v>398.52525486410917</v>
+      </c>
+      <c r="E30" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>4</v>
+      </c>
+      <c r="B31" s="0">
+        <v>6</v>
+      </c>
+      <c r="C31" s="0">
+        <v>814</v>
+      </c>
+      <c r="D31" s="0">
+        <v>944</v>
+      </c>
+      <c r="E31" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>4</v>
+      </c>
+      <c r="B32" s="0">
+        <v>7</v>
+      </c>
+      <c r="C32" s="0">
+        <v>433</v>
+      </c>
+      <c r="D32" s="0">
+        <v>940</v>
+      </c>
+      <c r="E32" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>4</v>
+      </c>
+      <c r="B33" s="0">
+        <v>8</v>
+      </c>
+      <c r="C33" s="0">
+        <v>414.45006015033368</v>
+      </c>
+      <c r="D33" s="0">
+        <v>400</v>
+      </c>
+      <c r="E33" s="0">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" customWidth="true"/>
+    <col min="2" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1700</v>
+      </c>
+      <c r="D2" s="0">
+        <v>276</v>
+      </c>
+      <c r="E2" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0">
+        <v>2</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1709.9917745739383</v>
+      </c>
+      <c r="D3" s="0">
+        <v>812</v>
+      </c>
+      <c r="E3" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0">
+        <v>1343.5026868544157</v>
+      </c>
+      <c r="D4" s="0">
+        <v>817</v>
+      </c>
+      <c r="E4" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>1</v>
+      </c>
+      <c r="B5" s="0">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0">
+        <v>1332</v>
+      </c>
+      <c r="D5" s="0">
+        <v>273.5228635742792</v>
+      </c>
+      <c r="E5" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>1</v>
+      </c>
+      <c r="B6" s="0">
+        <v>5</v>
+      </c>
+      <c r="C6" s="0">
+        <v>951.99999999999989</v>
+      </c>
+      <c r="D6" s="0">
+        <v>271</v>
+      </c>
+      <c r="E6" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>1</v>
+      </c>
+      <c r="B7" s="0">
+        <v>6</v>
+      </c>
+      <c r="C7" s="0">
+        <v>970.73436213713285</v>
+      </c>
+      <c r="D7" s="0">
+        <v>818.36169114028905</v>
+      </c>
+      <c r="E7" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>1</v>
+      </c>
+      <c r="B8" s="0">
+        <v>7</v>
+      </c>
+      <c r="C8" s="0">
+        <v>588</v>
+      </c>
+      <c r="D8" s="0">
+        <v>817</v>
+      </c>
+      <c r="E8" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>1</v>
+      </c>
+      <c r="B9" s="0">
+        <v>8</v>
+      </c>
+      <c r="C9" s="0">
+        <v>574</v>
+      </c>
+      <c r="D9" s="0">
+        <v>274</v>
+      </c>
+      <c r="E9" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>2</v>
+      </c>
+      <c r="B10" s="0">
+        <v>1</v>
+      </c>
+      <c r="C10" s="0">
+        <v>1697.4744644894422</v>
+      </c>
+      <c r="D10" s="0">
+        <v>420.00000000000006</v>
+      </c>
+      <c r="E10" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>2</v>
+      </c>
+      <c r="B11" s="0">
+        <v>2</v>
+      </c>
+      <c r="C11" s="0">
+        <v>1704</v>
+      </c>
+      <c r="D11" s="0">
+        <v>956</v>
+      </c>
+      <c r="E11" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>2</v>
+      </c>
+      <c r="B12" s="0">
+        <v>3</v>
+      </c>
+      <c r="C12" s="0">
+        <v>1337.9999999999998</v>
+      </c>
+      <c r="D12" s="0">
+        <v>960.49154609272216</v>
+      </c>
+      <c r="E12" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>2</v>
+      </c>
+      <c r="B13" s="0">
+        <v>4</v>
+      </c>
+      <c r="C13" s="0">
+        <v>1330.5042809132685</v>
+      </c>
+      <c r="D13" s="0">
+        <v>416.99999999999994</v>
+      </c>
+      <c r="E13" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>2</v>
+      </c>
+      <c r="B14" s="0">
+        <v>5</v>
+      </c>
+      <c r="C14" s="0">
+        <v>946.42420632351775</v>
+      </c>
+      <c r="D14" s="0">
+        <v>414.99999999999994</v>
+      </c>
+      <c r="E14" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>2</v>
+      </c>
+      <c r="B15" s="0">
+        <v>6</v>
+      </c>
+      <c r="C15" s="0">
+        <v>965</v>
+      </c>
+      <c r="D15" s="0">
+        <v>961</v>
+      </c>
+      <c r="E15" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>2</v>
+      </c>
+      <c r="B16" s="0">
+        <v>7</v>
+      </c>
+      <c r="C16" s="0">
+        <v>583.79880651185431</v>
+      </c>
+      <c r="D16" s="0">
+        <v>958.57565299721614</v>
+      </c>
+      <c r="E16" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>2</v>
+      </c>
+      <c r="B17" s="0">
+        <v>8</v>
+      </c>
+      <c r="C17" s="0">
+        <v>567.49174180250736</v>
+      </c>
+      <c r="D17" s="0">
+        <v>417.48809251374257</v>
+      </c>
+      <c r="E17" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>3</v>
+      </c>
+      <c r="B18" s="0">
+        <v>1</v>
+      </c>
+      <c r="C18" s="0">
+        <v>1555.9999999999998</v>
+      </c>
+      <c r="D18" s="0">
+        <v>265.52238737668119</v>
+      </c>
+      <c r="E18" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>3</v>
+      </c>
+      <c r="B19" s="0">
+        <v>2</v>
+      </c>
+      <c r="C19" s="0">
+        <v>1569</v>
+      </c>
+      <c r="D19" s="0">
+        <v>803.99999999999989</v>
+      </c>
+      <c r="E19" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>3</v>
+      </c>
+      <c r="B20" s="0">
+        <v>3</v>
+      </c>
+      <c r="C20" s="0">
+        <v>1196.468376153884</v>
+      </c>
+      <c r="D20" s="0">
+        <v>809</v>
+      </c>
+      <c r="E20" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>3</v>
+      </c>
+      <c r="B21" s="0">
+        <v>4</v>
+      </c>
+      <c r="C21" s="0">
+        <v>1184</v>
+      </c>
+      <c r="D21" s="0">
+        <v>263</v>
+      </c>
+      <c r="E21" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>3</v>
+      </c>
+      <c r="B22" s="0">
+        <v>5</v>
+      </c>
+      <c r="C22" s="0">
+        <v>804</v>
+      </c>
+      <c r="D22" s="0">
+        <v>264</v>
+      </c>
+      <c r="E22" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>3</v>
+      </c>
+      <c r="B23" s="0">
+        <v>6</v>
+      </c>
+      <c r="C23" s="0">
+        <v>821</v>
+      </c>
+      <c r="D23" s="0">
+        <v>806.45214729968905</v>
+      </c>
+      <c r="E23" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>3</v>
+      </c>
+      <c r="B24" s="0">
+        <v>7</v>
+      </c>
+      <c r="C24" s="0">
+        <v>442</v>
+      </c>
+      <c r="D24" s="0">
+        <v>806</v>
+      </c>
+      <c r="E24" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>3</v>
+      </c>
+      <c r="B25" s="0">
+        <v>8</v>
+      </c>
+      <c r="C25" s="0">
+        <v>427</v>
+      </c>
+      <c r="D25" s="0">
+        <v>266</v>
+      </c>
+      <c r="E25" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>4</v>
+      </c>
+      <c r="B26" s="0">
+        <v>1</v>
+      </c>
+      <c r="C26" s="0">
+        <v>1554.5100088758986</v>
+      </c>
+      <c r="D26" s="0">
+        <v>413</v>
+      </c>
+      <c r="E26" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>4</v>
+      </c>
+      <c r="B27" s="0">
+        <v>2</v>
+      </c>
+      <c r="C27" s="0">
+        <v>1560.486582044831</v>
+      </c>
+      <c r="D27" s="0">
+        <v>950</v>
+      </c>
+      <c r="E27" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>4</v>
+      </c>
+      <c r="B28" s="0">
+        <v>3</v>
+      </c>
+      <c r="C28" s="0">
+        <v>1191</v>
+      </c>
+      <c r="D28" s="0">
+        <v>955</v>
+      </c>
+      <c r="E28" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>4</v>
+      </c>
+      <c r="B29" s="0">
+        <v>4</v>
+      </c>
+      <c r="C29" s="0">
+        <v>1182</v>
+      </c>
+      <c r="D29" s="0">
+        <v>410.473464652188</v>
+      </c>
+      <c r="E29" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>4</v>
+      </c>
+      <c r="B30" s="0">
+        <v>5</v>
+      </c>
+      <c r="C30" s="0">
+        <v>798.50819995609561</v>
+      </c>
+      <c r="D30" s="0">
+        <v>409.52525486410917</v>
+      </c>
+      <c r="E30" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>4</v>
+      </c>
+      <c r="B31" s="0">
+        <v>6</v>
+      </c>
+      <c r="C31" s="0">
+        <v>819</v>
+      </c>
+      <c r="D31" s="0">
+        <v>955</v>
+      </c>
+      <c r="E31" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>4</v>
+      </c>
+      <c r="B32" s="0">
+        <v>7</v>
+      </c>
+      <c r="C32" s="0">
+        <v>438</v>
+      </c>
+      <c r="D32" s="0">
+        <v>951</v>
+      </c>
+      <c r="E32" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>4</v>
+      </c>
+      <c r="B33" s="0">
+        <v>8</v>
+      </c>
+      <c r="C33" s="0">
+        <v>419.45006015033368</v>
+      </c>
+      <c r="D33" s="0">
+        <v>411</v>
+      </c>
+      <c r="E33" s="0">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" customWidth="true"/>
+    <col min="2" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1274.5497069661656</v>
+      </c>
+      <c r="D2" s="0">
+        <v>347</v>
+      </c>
+      <c r="E2" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0">
+        <v>2</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1282.9374013812564</v>
+      </c>
+      <c r="D3" s="0">
+        <v>890.23676204022513</v>
+      </c>
+      <c r="E3" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>1</v>
+      </c>
+      <c r="B4" s="0">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0">
+        <v>741</v>
+      </c>
+      <c r="D4" s="0">
+        <v>886</v>
+      </c>
+      <c r="E4" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>1</v>
+      </c>
+      <c r="B5" s="0">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0">
+        <v>730.99999999999989</v>
+      </c>
+      <c r="D5" s="0">
+        <v>344</v>
+      </c>
+      <c r="E5" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>2</v>
+      </c>
+      <c r="B6" s="0">
+        <v>1</v>
+      </c>
+      <c r="C6" s="0">
+        <v>1263.3749427579257</v>
+      </c>
+      <c r="D6" s="0">
+        <v>488.85164744853807</v>
+      </c>
+      <c r="E6" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>2</v>
+      </c>
+      <c r="B7" s="0">
+        <v>2</v>
+      </c>
+      <c r="C7" s="0">
+        <v>1273.9999999999998</v>
+      </c>
+      <c r="D7" s="0">
+        <v>1028.5871314552232</v>
+      </c>
+      <c r="E7" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>2</v>
+      </c>
+      <c r="B8" s="0">
+        <v>3</v>
+      </c>
+      <c r="C8" s="0">
+        <v>732.98989667639148</v>
+      </c>
+      <c r="D8" s="0">
+        <v>1028</v>
+      </c>
+      <c r="E8" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>2</v>
+      </c>
+      <c r="B9" s="0">
+        <v>4</v>
+      </c>
+      <c r="C9" s="0">
+        <v>727.97720214232947</v>
+      </c>
+      <c r="D9" s="0">
+        <v>482.97125875018503</v>
+      </c>
+      <c r="E9" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>3</v>
+      </c>
+      <c r="B10" s="0">
+        <v>1</v>
+      </c>
+      <c r="C10" s="0">
+        <v>1129.2529574871867</v>
+      </c>
+      <c r="D10" s="0">
+        <v>343.26889872489846</v>
+      </c>
+      <c r="E10" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>3</v>
+      </c>
+      <c r="B11" s="0">
+        <v>2</v>
+      </c>
+      <c r="C11" s="0">
+        <v>1141.4456685905477</v>
+      </c>
+      <c r="D11" s="0">
+        <v>887.52201113999195</v>
+      </c>
+      <c r="E11" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>3</v>
+      </c>
+      <c r="B12" s="0">
+        <v>3</v>
+      </c>
+      <c r="C12" s="0">
+        <v>598.00000000000011</v>
+      </c>
+      <c r="D12" s="0">
+        <v>886.5235340926057</v>
+      </c>
+      <c r="E12" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>3</v>
+      </c>
+      <c r="B13" s="0">
+        <v>4</v>
+      </c>
+      <c r="C13" s="0">
+        <v>591.0367201156231</v>
+      </c>
+      <c r="D13" s="0">
+        <v>340.31508819348767</v>
+      </c>
+      <c r="E13" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>4</v>
+      </c>
+      <c r="B14" s="0">
+        <v>1</v>
+      </c>
+      <c r="C14" s="0">
+        <v>1124.9248065927791</v>
+      </c>
+      <c r="D14" s="0">
+        <v>482.26081184409622</v>
+      </c>
+      <c r="E14" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>4</v>
+      </c>
+      <c r="B15" s="0">
+        <v>2</v>
+      </c>
+      <c r="C15" s="0">
+        <v>1136</v>
+      </c>
+      <c r="D15" s="0">
+        <v>1023.9765358885199</v>
+      </c>
+      <c r="E15" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>4</v>
+      </c>
+      <c r="B16" s="0">
+        <v>3</v>
+      </c>
+      <c r="C16" s="0">
+        <v>593.05633789363412</v>
+      </c>
+      <c r="D16" s="0">
+        <v>1020</v>
+      </c>
+      <c r="E16" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>4</v>
+      </c>
+      <c r="B17" s="0">
+        <v>4</v>
+      </c>
+      <c r="C17" s="0">
+        <v>585.00723719099699</v>
+      </c>
+      <c r="D17" s="0">
+        <v>478.03312688324678</v>
+      </c>
+      <c r="E17" s="0">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="16" width="12.7109375" customWidth="1"/>
+    <col min="1" max="16" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1">
       <c r="A1">
         <v>1632.2250068153903</v>
       </c>
@@ -7696,7 +10318,7 @@
         <v>1030.8142339811116</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2">
       <c r="A2">
         <v>1646.9999999999998</v>
       </c>
@@ -7746,7 +10368,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3">
       <c r="A3">
         <v>1479.7148948701831</v>
       </c>
@@ -7796,7 +10418,7 @@
         <v>1005.2040069956981</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4">
       <c r="A4">
         <v>1491</v>
       </c>
@@ -7854,11 +10476,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12331FAC-F287-564D-A828-85EA3FEE69F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12331FAC-F287-564D-A828-85EA3FEE69F0}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -7875,7 +10497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7906,7 +10528,7 @@
         <v>29.34225745781572</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7937,7 +10559,7 @@
         <v>840.99907164175033</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -7968,7 +10590,7 @@
         <v>859.34225745781578</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -7999,7 +10621,7 @@
         <v>314.34225745781572</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8030,7 +10652,7 @@
         <v>320.34137828619572</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8061,7 +10683,7 @@
         <v>863.34225745781578</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -8092,7 +10714,7 @@
         <v>871.80117305920476</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -8123,7 +10745,7 @@
         <v>328.93127036364535</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8154,7 +10776,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8185,7 +10807,7 @@
         <v>999.47984336260345</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8216,7 +10838,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8247,7 +10869,7 @@
         <v>471.50098570018065</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8278,7 +10900,7 @@
         <v>477.74724778007908</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8309,7 +10931,7 @@
         <v>1021.0000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8340,7 +10962,7 @@
         <v>1029.3219241389984</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8371,7 +10993,7 @@
         <v>488.84585525987632</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -8394,7 +11016,7 @@
         <v>279.48143931656074</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -8417,7 +11039,7 @@
         <v>813.23295593386445</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -8440,7 +11062,7 @@
         <v>829.28943124222167</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -8463,7 +11085,7 @@
         <v>282.76894231476359</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -8486,7 +11108,7 @@
         <v>291.00000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -8509,7 +11131,7 @@
         <v>831.51615876175674</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8532,7 +11154,7 @@
         <v>836.56843813389787</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8555,7 +11177,7 @@
         <v>300.52825243257473</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -8586,7 +11208,7 @@
         <v>28.14476265348992</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -8617,7 +11239,7 @@
         <v>987.80748757663412</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -8648,7 +11270,7 @@
         <v>998.63525095173111</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -8679,7 +11301,7 @@
         <v>453.14476265348998</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -8710,7 +11332,7 @@
         <v>462.61791541004521</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -8741,7 +11363,7 @@
         <v>1005.4059517454439</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -8772,7 +11394,7 @@
         <v>1011.1447626534898</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -8810,14 +11432,14 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A8B513D-DF9C-6D4B-8EB9-67E97D41F236}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A8B513D-DF9C-6D4B-8EB9-67E97D41F236}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -8834,7 +11456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8851,7 +11473,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8868,7 +11490,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8885,7 +11507,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8902,7 +11524,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8919,7 +11541,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8936,7 +11558,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -8953,7 +11575,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -8970,7 +11592,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8987,7 +11609,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -9004,7 +11626,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -9021,7 +11643,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -9038,7 +11660,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -9055,7 +11677,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -9072,7 +11694,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -9089,7 +11711,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -9106,7 +11728,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -9123,7 +11745,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -9140,7 +11762,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -9157,7 +11779,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -9174,7 +11796,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -9191,7 +11813,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -9208,7 +11830,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -9225,7 +11847,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -9242,7 +11864,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -9259,7 +11881,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -9276,7 +11898,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -9293,7 +11915,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -9310,7 +11932,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -9327,7 +11949,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -9344,7 +11966,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -9361,7 +11983,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -9385,16 +12007,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -9411,7 +12033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -9428,7 +12050,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -9445,7 +12067,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -9462,7 +12084,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -9479,7 +12101,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -9496,7 +12118,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -9513,7 +12135,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -9530,7 +12152,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -9547,7 +12169,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -9564,7 +12186,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -9581,7 +12203,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -9598,7 +12220,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -9615,7 +12237,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -9632,7 +12254,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -9649,7 +12271,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -9666,7 +12288,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -9683,7 +12305,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -9700,7 +12322,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -9717,7 +12339,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -9734,7 +12356,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -9751,7 +12373,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -9768,7 +12390,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -9785,7 +12407,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -9802,7 +12424,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -9819,7 +12441,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -9836,7 +12458,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -9853,7 +12475,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -9870,7 +12492,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -9887,7 +12509,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -9904,7 +12526,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -9921,7 +12543,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -9938,7 +12560,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -9962,16 +12584,16 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -9988,7 +12610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -10005,7 +12627,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -10022,7 +12644,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -10039,7 +12661,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -10056,7 +12678,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -10073,7 +12695,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -10090,7 +12712,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -10107,7 +12729,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -10124,7 +12746,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -10141,7 +12763,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -10158,7 +12780,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -10175,7 +12797,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -10192,7 +12814,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -10209,7 +12831,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -10226,7 +12848,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -10243,7 +12865,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -10260,7 +12882,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -10277,7 +12899,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -10294,7 +12916,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -10311,7 +12933,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -10328,7 +12950,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -10345,7 +12967,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -10362,7 +12984,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -10379,7 +13001,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -10396,7 +13018,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -10413,7 +13035,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -10430,7 +13052,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -10447,7 +13069,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -10464,7 +13086,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -10481,7 +13103,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -10498,7 +13120,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -10515,7 +13137,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -10539,16 +13161,16 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B4C6AA-75FF-D04D-AEB0-D50F87D3190D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B4C6AA-75FF-D04D-AEB0-D50F87D3190D}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -10565,7 +13187,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -10582,7 +13204,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -10599,7 +13221,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -10616,7 +13238,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -10633,7 +13255,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -10650,7 +13272,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -10667,7 +13289,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -10684,7 +13306,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -10701,7 +13323,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -10718,7 +13340,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -10735,7 +13357,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -10752,7 +13374,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -10769,7 +13391,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -10786,7 +13408,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -10803,7 +13425,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -10820,7 +13442,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -10837,7 +13459,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -10854,7 +13476,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -10871,7 +13493,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -10888,7 +13510,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -10905,7 +13527,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -10922,7 +13544,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -10939,7 +13561,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -10956,7 +13578,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -10973,7 +13595,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -10990,7 +13612,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -11007,7 +13629,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -11024,7 +13646,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -11041,7 +13663,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -11058,7 +13680,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -11075,7 +13697,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -11092,7 +13714,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>
@@ -11116,16 +13738,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="1" max="2" width="7.7109375" customWidth="true"/>
+    <col min="3" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -11142,7 +13764,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -11159,7 +13781,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -11176,7 +13798,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -11193,7 +13815,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -11210,7 +13832,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -11227,7 +13849,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -11244,7 +13866,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -11261,7 +13883,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
@@ -11278,7 +13900,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
@@ -11295,7 +13917,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="A11">
         <v>2</v>
       </c>
@@ -11312,7 +13934,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -11329,7 +13951,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13">
       <c r="A13">
         <v>2</v>
       </c>
@@ -11346,7 +13968,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14">
       <c r="A14">
         <v>2</v>
       </c>
@@ -11363,7 +13985,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15">
       <c r="A15">
         <v>2</v>
       </c>
@@ -11380,7 +14002,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16">
       <c r="A16">
         <v>2</v>
       </c>
@@ -11397,7 +14019,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17">
       <c r="A17">
         <v>2</v>
       </c>
@@ -11414,7 +14036,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18">
       <c r="A18">
         <v>3</v>
       </c>
@@ -11431,7 +14053,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19">
       <c r="A19">
         <v>3</v>
       </c>
@@ -11448,7 +14070,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20">
       <c r="A20">
         <v>3</v>
       </c>
@@ -11465,7 +14087,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21">
       <c r="A21">
         <v>3</v>
       </c>
@@ -11482,7 +14104,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22">
       <c r="A22">
         <v>3</v>
       </c>
@@ -11499,7 +14121,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23">
       <c r="A23">
         <v>3</v>
       </c>
@@ -11516,7 +14138,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24">
       <c r="A24">
         <v>3</v>
       </c>
@@ -11533,7 +14155,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25">
       <c r="A25">
         <v>3</v>
       </c>
@@ -11550,7 +14172,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26">
       <c r="A26">
         <v>4</v>
       </c>
@@ -11567,7 +14189,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27">
       <c r="A27">
         <v>4</v>
       </c>
@@ -11584,7 +14206,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28">
       <c r="A28">
         <v>4</v>
       </c>
@@ -11601,7 +14223,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29">
       <c r="A29">
         <v>4</v>
       </c>
@@ -11618,7 +14240,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30">
       <c r="A30">
         <v>4</v>
       </c>
@@ -11635,7 +14257,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31">
       <c r="A31">
         <v>4</v>
       </c>
@@ -11652,7 +14274,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32">
       <c r="A32">
         <v>4</v>
       </c>
@@ -11669,7 +14291,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33">
       <c r="A33">
         <v>4</v>
       </c>

--- a/Soft X-ray/Four-View/fiberPositions.xlsx
+++ b/Soft X-ray/Four-View/fiberPositions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shohgookazaki/Documents/GitHub/test-open/Soft X-ray/Four-View/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F822E21-4F95-784B-A154-43E7FBDAE471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53C10E9-DA44-0947-956A-6982BD896909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19120" firstSheet="7" activeTab="23"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19120" firstSheet="8" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="230429" sheetId="16" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="250125" sheetId="26" r:id="rId22"/>
     <sheet name="250205" sheetId="25" r:id="rId23"/>
     <sheet name="250206" sheetId="27" r:id="rId24"/>
+    <sheet name="251220" sheetId="28" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="123" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="133" uniqueCount="23">
   <si>
     <t>center_X</t>
     <phoneticPr fontId="1"/>
@@ -9489,6 +9490,583 @@
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="true"/>
+    <col min="2" max="2" width="7.1640625" customWidth="true"/>
+    <col min="3" max="4" width="13.33203125" customWidth="true"/>
+    <col min="5" max="5" width="5.5" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1620.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>912.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1611.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>377.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1245</v>
+      </c>
+      <c r="D4">
+        <v>372</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1252.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>915.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>880.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>915.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>864.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>369.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>485.83493585304365</v>
+      </c>
+      <c r="D8">
+        <v>368.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>493.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>913</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1485.3846762361873</v>
+      </c>
+      <c r="D10">
+        <v>898.182620379632</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1474.7054596333444</v>
+      </c>
+      <c r="D11">
+        <v>357.98346611431509</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1102.5063568822814</v>
+      </c>
+      <c r="D12">
+        <v>357.46121207422669</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1111.5494197876064</v>
+      </c>
+      <c r="D13">
+        <v>897</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>735.37055943669645</v>
+      </c>
+      <c r="D14">
+        <v>898.87694241073473</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>720</v>
+      </c>
+      <c r="D15">
+        <v>356</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>343.59998908096031</v>
+      </c>
+      <c r="D16">
+        <v>356.18836282597613</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>353.52787151824356</v>
+      </c>
+      <c r="D17">
+        <v>894.00000000000011</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1625.8746535296575</v>
+      </c>
+      <c r="D18">
+        <v>1106.0845244489574</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1622.9734582162946</v>
+      </c>
+      <c r="D19">
+        <v>570</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1253.9999999999998</v>
+      </c>
+      <c r="D20">
+        <v>567</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1258.3493827116019</v>
+      </c>
+      <c r="D21">
+        <v>1112.3012493082249</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>886.52484896262547</v>
+      </c>
+      <c r="D22">
+        <v>1113.5206728589721</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>871.4076645902577</v>
+      </c>
+      <c r="D23">
+        <v>563.7948190298614</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>489.46508385439239</v>
+      </c>
+      <c r="D24">
+        <v>566.4455764172319</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>503.99999999999994</v>
+      </c>
+      <c r="D25">
+        <v>1106.0980695012088</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1484</v>
+      </c>
+      <c r="D26">
+        <v>1040</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1482.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>499.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1101</v>
+      </c>
+      <c r="D28">
+        <v>496.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1114.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>1038.2580222016863</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>735.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>1035.2802447597348</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>722.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>493.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>340.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>493.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>360.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>1032.3292348100124</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FE0AEC6-4CFB-454E-AD0F-7A26F660C484}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
     <col min="1" max="1" width="8.28515625" customWidth="true"/>
     <col min="2" max="2" width="7.140625" customWidth="true"/>
     <col min="3" max="3" width="13.28515625" customWidth="true"/>
@@ -9521,10 +10099,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="0">
-        <v>1620.7425030099457</v>
+        <v>1707.7425030099457</v>
       </c>
       <c r="D2" s="0">
-        <v>912.02871194456884</v>
+        <v>872.02871194456884</v>
       </c>
       <c r="E2" s="0">
         <v>65</v>
@@ -9538,10 +10116,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="0">
-        <v>1611.4061483041658</v>
+        <v>1698.4061483041658</v>
       </c>
       <c r="D3" s="0">
-        <v>377.32671346786896</v>
+        <v>337.32671346786896</v>
       </c>
       <c r="E3" s="0">
         <v>65</v>
@@ -9555,10 +10133,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="0">
-        <v>1245</v>
+        <v>1332</v>
       </c>
       <c r="D4" s="0">
-        <v>372</v>
+        <v>332</v>
       </c>
       <c r="E4" s="0">
         <v>65</v>
@@ -9572,10 +10150,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="0">
-        <v>1252.520209029972</v>
+        <v>1339.520209029972</v>
       </c>
       <c r="D5" s="0">
-        <v>915.01460290365162</v>
+        <v>875.01460290365162</v>
       </c>
       <c r="E5" s="0">
         <v>65</v>
@@ -9589,10 +10167,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="0">
-        <v>880.62459762139895</v>
+        <v>967.62459762139895</v>
       </c>
       <c r="D6" s="0">
-        <v>915.04376388709545</v>
+        <v>875.04376388709545</v>
       </c>
       <c r="E6" s="0">
         <v>65</v>
@@ -9606,10 +10184,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="0">
-        <v>864.28458590452396</v>
+        <v>951.28458590452396</v>
       </c>
       <c r="D7" s="0">
-        <v>369.24413555490423</v>
+        <v>329.24413555490423</v>
       </c>
       <c r="E7" s="0">
         <v>65</v>
@@ -9623,10 +10201,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="0">
-        <v>485.83493585304365</v>
+        <v>572.83493585304359</v>
       </c>
       <c r="D8" s="0">
-        <v>368.79972769377798</v>
+        <v>328.79972769377798</v>
       </c>
       <c r="E8" s="0">
         <v>65</v>
@@ -9640,10 +10218,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="0">
-        <v>493.0101420458949</v>
+        <v>580.0101420458949</v>
       </c>
       <c r="D9" s="0">
-        <v>913</v>
+        <v>873</v>
       </c>
       <c r="E9" s="0">
         <v>65</v>
@@ -9657,10 +10235,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="0">
-        <v>1485.3846762361873</v>
+        <v>1703.8746535296575</v>
       </c>
       <c r="D10" s="0">
-        <v>898.182620379632</v>
+        <v>1005.0845244489574</v>
       </c>
       <c r="E10" s="0">
         <v>65</v>
@@ -9674,10 +10252,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="0">
-        <v>1474.7054596333444</v>
+        <v>1700.9734582162946</v>
       </c>
       <c r="D11" s="0">
-        <v>357.98346611431509</v>
+        <v>469</v>
       </c>
       <c r="E11" s="0">
         <v>65</v>
@@ -9691,10 +10269,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="0">
-        <v>1102.5063568822814</v>
+        <v>1331.9999999999998</v>
       </c>
       <c r="D12" s="0">
-        <v>357.46121207422669</v>
+        <v>466</v>
       </c>
       <c r="E12" s="0">
         <v>65</v>
@@ -9708,10 +10286,10 @@
         <v>4</v>
       </c>
       <c r="C13" s="0">
-        <v>1111.5494197876064</v>
+        <v>1336.3493827116019</v>
       </c>
       <c r="D13" s="0">
-        <v>897</v>
+        <v>1011.3012493082249</v>
       </c>
       <c r="E13" s="0">
         <v>65</v>
@@ -9725,10 +10303,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="0">
-        <v>735.37055943669645</v>
+        <v>964.52484896262547</v>
       </c>
       <c r="D14" s="0">
-        <v>898.87694241073473</v>
+        <v>1012.5206728589721</v>
       </c>
       <c r="E14" s="0">
         <v>65</v>
@@ -9742,10 +10320,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="0">
-        <v>720</v>
+        <v>949.4076645902577</v>
       </c>
       <c r="D15" s="0">
-        <v>356</v>
+        <v>462.7948190298614</v>
       </c>
       <c r="E15" s="0">
         <v>65</v>
@@ -9759,10 +10337,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="0">
-        <v>343.59998908096031</v>
+        <v>567.46508385439233</v>
       </c>
       <c r="D16" s="0">
-        <v>356.18836282597613</v>
+        <v>465.4455764172319</v>
       </c>
       <c r="E16" s="0">
         <v>65</v>
@@ -9776,10 +10354,10 @@
         <v>8</v>
       </c>
       <c r="C17" s="0">
-        <v>353.52787151824356</v>
+        <v>582</v>
       </c>
       <c r="D17" s="0">
-        <v>894.00000000000011</v>
+        <v>1005.0980695012088</v>
       </c>
       <c r="E17" s="0">
         <v>65</v>
@@ -9793,10 +10371,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="0">
-        <v>1625.8746535296575</v>
+        <v>1561.3846762361873</v>
       </c>
       <c r="D18" s="0">
-        <v>1106.0845244489574</v>
+        <v>863.182620379632</v>
       </c>
       <c r="E18" s="0">
         <v>65</v>
@@ -9810,10 +10388,10 @@
         <v>2</v>
       </c>
       <c r="C19" s="0">
-        <v>1622.9734582162946</v>
+        <v>1550.7054596333444</v>
       </c>
       <c r="D19" s="0">
-        <v>570</v>
+        <v>322.98346611431509</v>
       </c>
       <c r="E19" s="0">
         <v>65</v>
@@ -9827,10 +10405,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="0">
-        <v>1253.9999999999998</v>
+        <v>1178.5063568822814</v>
       </c>
       <c r="D20" s="0">
-        <v>567</v>
+        <v>322.46121207422669</v>
       </c>
       <c r="E20" s="0">
         <v>65</v>
@@ -9844,10 +10422,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="0">
-        <v>1258.3493827116019</v>
+        <v>1187.5494197876064</v>
       </c>
       <c r="D21" s="0">
-        <v>1112.3012493082249</v>
+        <v>862</v>
       </c>
       <c r="E21" s="0">
         <v>65</v>
@@ -9861,10 +10439,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="0">
-        <v>886.52484896262547</v>
+        <v>811.37055943669645</v>
       </c>
       <c r="D22" s="0">
-        <v>1113.5206728589721</v>
+        <v>863.87694241073473</v>
       </c>
       <c r="E22" s="0">
         <v>65</v>
@@ -9878,10 +10456,10 @@
         <v>6</v>
       </c>
       <c r="C23" s="0">
-        <v>871.4076645902577</v>
+        <v>796</v>
       </c>
       <c r="D23" s="0">
-        <v>563.7948190298614</v>
+        <v>321</v>
       </c>
       <c r="E23" s="0">
         <v>65</v>
@@ -9895,10 +10473,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="0">
-        <v>489.46508385439239</v>
+        <v>419.59998908096031</v>
       </c>
       <c r="D24" s="0">
-        <v>566.4455764172319</v>
+        <v>321.18836282597613</v>
       </c>
       <c r="E24" s="0">
         <v>65</v>
@@ -9912,10 +10490,10 @@
         <v>8</v>
       </c>
       <c r="C25" s="0">
-        <v>503.99999999999994</v>
+        <v>429.52787151824356</v>
       </c>
       <c r="D25" s="0">
-        <v>1106.0980695012088</v>
+        <v>859.00000000000011</v>
       </c>
       <c r="E25" s="0">
         <v>65</v>
@@ -9929,10 +10507,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="0">
-        <v>1484</v>
+        <v>1555</v>
       </c>
       <c r="D26" s="0">
-        <v>1040</v>
+        <v>1003</v>
       </c>
       <c r="E26" s="0">
         <v>65</v>
@@ -9946,10 +10524,10 @@
         <v>2</v>
       </c>
       <c r="C27" s="0">
-        <v>1482.3355062255928</v>
+        <v>1553.3355062255928</v>
       </c>
       <c r="D27" s="0">
-        <v>499.68324673024046</v>
+        <v>462.68324673024046</v>
       </c>
       <c r="E27" s="0">
         <v>65</v>
@@ -9963,10 +10541,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="0">
-        <v>1101</v>
+        <v>1172</v>
       </c>
       <c r="D28" s="0">
-        <v>496.06282172105097</v>
+        <v>459.06282172105097</v>
       </c>
       <c r="E28" s="0">
         <v>65</v>
@@ -9980,10 +10558,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="0">
-        <v>1114.0510306101908</v>
+        <v>1185.0510306101908</v>
       </c>
       <c r="D29" s="0">
-        <v>1038.2580222016863</v>
+        <v>1001.2580222016863</v>
       </c>
       <c r="E29" s="0">
         <v>65</v>
@@ -9997,10 +10575,10 @@
         <v>5</v>
       </c>
       <c r="C30" s="0">
-        <v>735.28422113454724</v>
+        <v>806.28422113454724</v>
       </c>
       <c r="D30" s="0">
-        <v>1035.2802447597348</v>
+        <v>998.28024475973484</v>
       </c>
       <c r="E30" s="0">
         <v>65</v>
@@ -10014,10 +10592,10 @@
         <v>6</v>
       </c>
       <c r="C31" s="0">
-        <v>722.43600904846016</v>
+        <v>793.43600904846016</v>
       </c>
       <c r="D31" s="0">
-        <v>493.80569376586431</v>
+        <v>456.80569376586431</v>
       </c>
       <c r="E31" s="0">
         <v>65</v>
@@ -10031,10 +10609,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="0">
-        <v>340.48909359995025</v>
+        <v>411.48909359995025</v>
       </c>
       <c r="D32" s="0">
-        <v>493.47228629221291</v>
+        <v>456.47228629221291</v>
       </c>
       <c r="E32" s="0">
         <v>65</v>
@@ -10048,10 +10626,10 @@
         <v>8</v>
       </c>
       <c r="C33" s="0">
-        <v>360.68442286943787</v>
+        <v>431.68442286943787</v>
       </c>
       <c r="D33" s="0">
-        <v>1032.3292348100124</v>
+        <v>995.32923481001239</v>
       </c>
       <c r="E33" s="0">
         <v>65</v>

--- a/Soft X-ray/Four-View/fiberPositions.xlsx
+++ b/Soft X-ray/Four-View/fiberPositions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shohgookazaki/Documents/GitHub/test-open/Soft X-ray/Four-View/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F680E3-6F2E-A549-A23A-2FF3518D610E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EC2505-5A7C-454D-9D1B-695FADDB6D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18920" firstSheet="12" activeTab="30"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18920" firstSheet="20" activeTab="36"/>
   </bookViews>
   <sheets>
     <sheet name="230429" sheetId="16" r:id="rId1"/>
@@ -44,6 +44,14 @@
     <sheet name="260218" sheetId="32" r:id="rId29"/>
     <sheet name="260219" sheetId="33" r:id="rId30"/>
     <sheet name="260220" sheetId="34" r:id="rId31"/>
+    <sheet name="260226" sheetId="35" r:id="rId32"/>
+    <sheet name="260309" sheetId="36" r:id="rId33"/>
+    <sheet name="260311" sheetId="37" r:id="rId34"/>
+    <sheet name="260317" sheetId="38" r:id="rId35"/>
+    <sheet name="260318" sheetId="39" r:id="rId36"/>
+    <sheet name="260325" sheetId="40" r:id="rId37"/>
+    <sheet name="260326" sheetId="41" r:id="rId38"/>
+    <sheet name="260331" sheetId="42" r:id="rId39"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
@@ -66,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="178" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="238" uniqueCount="23">
   <si>
     <t>center_X</t>
     <phoneticPr fontId="1"/>
@@ -11800,575 +11808,574 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE6E7C1-1524-DA49-8ED4-26509AE0C30A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE6E7C1-1524-DA49-8ED4-26509AE0C30A}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" customWidth="true"/>
-    <col min="2" max="2" width="7.140625" customWidth="true"/>
-    <col min="3" max="3" width="13.28515625" customWidth="true"/>
-    <col min="5" max="5" width="5.42578125" customWidth="true"/>
-    <col min="4" max="4" width="13.28515625" customWidth="true"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
-      <c r="A2" s="0">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1709.7425030099457</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>860.02871194456884</v>
       </c>
-      <c r="E2" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
-      <c r="A3" s="0">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0">
-        <v>2</v>
-      </c>
-      <c r="C3" s="0">
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1700.4061483041658</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>325.32671346786896</v>
       </c>
-      <c r="E3" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
-      <c r="A4" s="0">
-        <v>1</v>
-      </c>
-      <c r="B4" s="0">
-        <v>3</v>
-      </c>
-      <c r="C4" s="0">
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <v>1334</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>320</v>
       </c>
-      <c r="E4" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
-      <c r="A5" s="0">
-        <v>1</v>
-      </c>
-      <c r="B5" s="0">
-        <v>4</v>
-      </c>
-      <c r="C5" s="0">
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>1341.520209029972</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>863.01460290365162</v>
       </c>
-      <c r="E5" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
-      <c r="A6" s="0">
-        <v>1</v>
-      </c>
-      <c r="B6" s="0">
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>969.62459762139895</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>863.04376388709545</v>
       </c>
-      <c r="E6" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
-      <c r="A7" s="0">
-        <v>1</v>
-      </c>
-      <c r="B7" s="0">
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7">
         <v>953.28458590452396</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>317.24413555490423</v>
       </c>
-      <c r="E7" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
-      <c r="A8" s="0">
-        <v>1</v>
-      </c>
-      <c r="B8" s="0">
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C8">
         <v>574.83493585304359</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>316.79972769377798</v>
       </c>
-      <c r="E8" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
-      <c r="A9" s="0">
-        <v>1</v>
-      </c>
-      <c r="B9" s="0">
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C9">
         <v>582.0101420458949</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>861</v>
       </c>
-      <c r="E9" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
-      <c r="A10" s="0">
-        <v>2</v>
-      </c>
-      <c r="B10" s="0">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0">
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>1703.8746535296575</v>
       </c>
-      <c r="D10" s="0">
+      <c r="D10">
         <v>1001.0845244489574</v>
       </c>
-      <c r="E10" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
-      <c r="A11" s="0">
-        <v>2</v>
-      </c>
-      <c r="B11" s="0">
-        <v>2</v>
-      </c>
-      <c r="C11" s="0">
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
         <v>1700.9734582162946</v>
       </c>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>465</v>
       </c>
-      <c r="E11" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
-      <c r="A12" s="0">
-        <v>2</v>
-      </c>
-      <c r="B12" s="0">
-        <v>3</v>
-      </c>
-      <c r="C12" s="0">
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <v>1331.9999999999998</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>462</v>
       </c>
-      <c r="E12" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
-      <c r="A13" s="0">
-        <v>2</v>
-      </c>
-      <c r="B13" s="0">
-        <v>4</v>
-      </c>
-      <c r="C13" s="0">
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
         <v>1336.3493827116019</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D13">
         <v>1007.3012493082249</v>
       </c>
-      <c r="E13" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
-      <c r="A14" s="0">
-        <v>2</v>
-      </c>
-      <c r="B14" s="0">
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14">
         <v>964.52484896262547</v>
       </c>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>1008.5206728589721</v>
       </c>
-      <c r="E14" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="0">
-        <v>2</v>
-      </c>
-      <c r="B15" s="0">
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
         <v>6</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>949.4076645902577</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>458.7948190298614</v>
       </c>
-      <c r="E15" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="0">
-        <v>2</v>
-      </c>
-      <c r="B16" s="0">
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>567.46508385439233</v>
       </c>
-      <c r="D16" s="0">
-        <v>461.44557641723191</v>
-      </c>
-      <c r="E16" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="0">
-        <v>2</v>
-      </c>
-      <c r="B17" s="0">
+      <c r="D16">
+        <v>461.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
         <v>8</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C17">
         <v>582</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>1001.0980695012088</v>
       </c>
-      <c r="E17" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="0">
-        <v>3</v>
-      </c>
-      <c r="B18" s="0">
-        <v>1</v>
-      </c>
-      <c r="C18" s="0">
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
         <v>1561.3846762361873</v>
       </c>
-      <c r="D18" s="0">
+      <c r="D18">
         <v>858.182620379632</v>
       </c>
-      <c r="E18" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
-      <c r="A19" s="0">
-        <v>3</v>
-      </c>
-      <c r="B19" s="0">
-        <v>2</v>
-      </c>
-      <c r="C19" s="0">
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
         <v>1550.7054596333444</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D19">
         <v>317.98346611431509</v>
       </c>
-      <c r="E19" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="0">
-        <v>3</v>
-      </c>
-      <c r="B20" s="0">
-        <v>3</v>
-      </c>
-      <c r="C20" s="0">
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
         <v>1178.5063568822814</v>
       </c>
-      <c r="D20" s="0">
+      <c r="D20">
         <v>317.46121207422669</v>
       </c>
-      <c r="E20" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
-      <c r="A21" s="0">
-        <v>3</v>
-      </c>
-      <c r="B21" s="0">
-        <v>4</v>
-      </c>
-      <c r="C21" s="0">
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
         <v>1187.5494197876064</v>
       </c>
-      <c r="D21" s="0">
+      <c r="D21">
         <v>857</v>
       </c>
-      <c r="E21" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
-      <c r="A22" s="0">
-        <v>3</v>
-      </c>
-      <c r="B22" s="0">
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
         <v>5</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C22">
         <v>811.37055943669645</v>
       </c>
-      <c r="D22" s="0">
+      <c r="D22">
         <v>858.87694241073473</v>
       </c>
-      <c r="E22" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
-      <c r="A23" s="0">
-        <v>3</v>
-      </c>
-      <c r="B23" s="0">
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
         <v>6</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C23">
         <v>796</v>
       </c>
-      <c r="D23" s="0">
+      <c r="D23">
         <v>316</v>
       </c>
-      <c r="E23" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
-      <c r="A24" s="0">
-        <v>3</v>
-      </c>
-      <c r="B24" s="0">
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
         <v>7</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C24">
         <v>419.59998908096031</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D24">
         <v>316.18836282597613</v>
       </c>
-      <c r="E24" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
-      <c r="A25" s="0">
-        <v>3</v>
-      </c>
-      <c r="B25" s="0">
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
         <v>8</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C25">
         <v>429.52787151824356</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D25">
         <v>854.00000000000011</v>
       </c>
-      <c r="E25" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
-      <c r="A26" s="0">
-        <v>4</v>
-      </c>
-      <c r="B26" s="0">
-        <v>1</v>
-      </c>
-      <c r="C26" s="0">
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
         <v>1564</v>
       </c>
-      <c r="D26" s="0">
+      <c r="D26">
         <v>989</v>
       </c>
-      <c r="E26" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
-      <c r="A27" s="0">
-        <v>4</v>
-      </c>
-      <c r="B27" s="0">
-        <v>2</v>
-      </c>
-      <c r="C27" s="0">
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
         <v>1562.3355062255928</v>
       </c>
-      <c r="D27" s="0">
+      <c r="D27">
         <v>448.68324673024046</v>
       </c>
-      <c r="E27" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
-      <c r="A28" s="0">
-        <v>4</v>
-      </c>
-      <c r="B28" s="0">
-        <v>3</v>
-      </c>
-      <c r="C28" s="0">
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
         <v>1181</v>
       </c>
-      <c r="D28" s="0">
+      <c r="D28">
         <v>445.06282172105097</v>
       </c>
-      <c r="E28" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
-      <c r="A29" s="0">
-        <v>4</v>
-      </c>
-      <c r="B29" s="0">
-        <v>4</v>
-      </c>
-      <c r="C29" s="0">
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
         <v>1194.0510306101908</v>
       </c>
-      <c r="D29" s="0">
-        <v>987.25802220168635</v>
-      </c>
-      <c r="E29" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="0">
-        <v>4</v>
-      </c>
-      <c r="B30" s="0">
+      <c r="D29">
+        <v>987.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
         <v>5</v>
       </c>
-      <c r="C30" s="0">
+      <c r="C30">
         <v>815.28422113454724</v>
       </c>
-      <c r="D30" s="0">
+      <c r="D30">
         <v>984.28024475973484</v>
       </c>
-      <c r="E30" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
-      <c r="A31" s="0">
-        <v>4</v>
-      </c>
-      <c r="B31" s="0">
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
         <v>6</v>
       </c>
-      <c r="C31" s="0">
+      <c r="C31">
         <v>802.43600904846016</v>
       </c>
-      <c r="D31" s="0">
+      <c r="D31">
         <v>442.80569376586431</v>
       </c>
-      <c r="E31" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
-      <c r="A32" s="0">
-        <v>4</v>
-      </c>
-      <c r="B32" s="0">
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C32" s="0">
+      <c r="C32">
         <v>420.48909359995025</v>
       </c>
-      <c r="D32" s="0">
+      <c r="D32">
         <v>442.47228629221291</v>
       </c>
-      <c r="E32" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
-      <c r="A33" s="0">
-        <v>4</v>
-      </c>
-      <c r="B33" s="0">
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
         <v>8</v>
       </c>
-      <c r="C33" s="0">
+      <c r="C33">
         <v>440.68442286943787</v>
       </c>
-      <c r="D33" s="0">
-        <v>981.3292348100124</v>
-      </c>
-      <c r="E33" s="0">
+      <c r="D33">
+        <v>981.32923481001239</v>
+      </c>
+      <c r="E33">
         <v>65</v>
       </c>
     </row>
@@ -12378,575 +12385,574 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9DC520A-2572-7C4A-AF73-48A5E2C26EAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9DC520A-2572-7C4A-AF73-48A5E2C26EAA}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" customWidth="true"/>
-    <col min="2" max="2" width="7.140625" customWidth="true"/>
-    <col min="3" max="3" width="13.28515625" customWidth="true"/>
-    <col min="5" max="5" width="5.42578125" customWidth="true"/>
-    <col min="4" max="4" width="13.28515625" customWidth="true"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
-      <c r="A2" s="0">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>1708.7425030099457</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>856.02871194456884</v>
       </c>
-      <c r="E2" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
-      <c r="A3" s="0">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0">
-        <v>2</v>
-      </c>
-      <c r="C3" s="0">
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1699.4061483041658</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>321.32671346786896</v>
       </c>
-      <c r="E3" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
-      <c r="A4" s="0">
-        <v>1</v>
-      </c>
-      <c r="B4" s="0">
-        <v>3</v>
-      </c>
-      <c r="C4" s="0">
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <v>1333</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>316</v>
       </c>
-      <c r="E4" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
-      <c r="A5" s="0">
-        <v>1</v>
-      </c>
-      <c r="B5" s="0">
-        <v>4</v>
-      </c>
-      <c r="C5" s="0">
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>1340.520209029972</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>859.01460290365162</v>
       </c>
-      <c r="E5" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
-      <c r="A6" s="0">
-        <v>1</v>
-      </c>
-      <c r="B6" s="0">
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>968.62459762139895</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>859.04376388709545</v>
       </c>
-      <c r="E6" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
-      <c r="A7" s="0">
-        <v>1</v>
-      </c>
-      <c r="B7" s="0">
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7">
         <v>952.28458590452396</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>313.24413555490423</v>
       </c>
-      <c r="E7" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
-      <c r="A8" s="0">
-        <v>1</v>
-      </c>
-      <c r="B8" s="0">
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C8">
         <v>573.83493585304359</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>312.79972769377798</v>
       </c>
-      <c r="E8" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
-      <c r="A9" s="0">
-        <v>1</v>
-      </c>
-      <c r="B9" s="0">
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C9">
         <v>581.0101420458949</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>857</v>
       </c>
-      <c r="E9" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
-      <c r="A10" s="0">
-        <v>2</v>
-      </c>
-      <c r="B10" s="0">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0">
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>1703.8746535296575</v>
       </c>
-      <c r="D10" s="0">
+      <c r="D10">
         <v>997.08452444895738</v>
       </c>
-      <c r="E10" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
-      <c r="A11" s="0">
-        <v>2</v>
-      </c>
-      <c r="B11" s="0">
-        <v>2</v>
-      </c>
-      <c r="C11" s="0">
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
         <v>1700.9734582162946</v>
       </c>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>461</v>
       </c>
-      <c r="E11" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
-      <c r="A12" s="0">
-        <v>2</v>
-      </c>
-      <c r="B12" s="0">
-        <v>3</v>
-      </c>
-      <c r="C12" s="0">
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <v>1331.9999999999998</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>458</v>
       </c>
-      <c r="E12" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
-      <c r="A13" s="0">
-        <v>2</v>
-      </c>
-      <c r="B13" s="0">
-        <v>4</v>
-      </c>
-      <c r="C13" s="0">
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
         <v>1336.3493827116019</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D13">
         <v>1003.3012493082249</v>
       </c>
-      <c r="E13" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
-      <c r="A14" s="0">
-        <v>2</v>
-      </c>
-      <c r="B14" s="0">
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14">
         <v>964.52484896262547</v>
       </c>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>1004.5206728589721</v>
       </c>
-      <c r="E14" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="0">
-        <v>2</v>
-      </c>
-      <c r="B15" s="0">
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
         <v>6</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>949.4076645902577</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>454.7948190298614</v>
       </c>
-      <c r="E15" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="0">
-        <v>2</v>
-      </c>
-      <c r="B16" s="0">
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
         <v>7</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>567.46508385439233</v>
       </c>
-      <c r="D16" s="0">
-        <v>457.44557641723191</v>
-      </c>
-      <c r="E16" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="0">
-        <v>2</v>
-      </c>
-      <c r="B17" s="0">
+      <c r="D16">
+        <v>457.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
         <v>8</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C17">
         <v>582</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>997.09806950120878</v>
       </c>
-      <c r="E17" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="0">
-        <v>3</v>
-      </c>
-      <c r="B18" s="0">
-        <v>1</v>
-      </c>
-      <c r="C18" s="0">
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
         <v>1549.3846762361873</v>
       </c>
-      <c r="D18" s="0">
+      <c r="D18">
         <v>832.182620379632</v>
       </c>
-      <c r="E18" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
-      <c r="A19" s="0">
-        <v>3</v>
-      </c>
-      <c r="B19" s="0">
-        <v>2</v>
-      </c>
-      <c r="C19" s="0">
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
         <v>1538.7054596333444</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D19">
         <v>291.98346611431509</v>
       </c>
-      <c r="E19" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="0">
-        <v>3</v>
-      </c>
-      <c r="B20" s="0">
-        <v>3</v>
-      </c>
-      <c r="C20" s="0">
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
         <v>1166.5063568822814</v>
       </c>
-      <c r="D20" s="0">
+      <c r="D20">
         <v>291.46121207422669</v>
       </c>
-      <c r="E20" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
-      <c r="A21" s="0">
-        <v>3</v>
-      </c>
-      <c r="B21" s="0">
-        <v>4</v>
-      </c>
-      <c r="C21" s="0">
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
         <v>1175.5494197876064</v>
       </c>
-      <c r="D21" s="0">
+      <c r="D21">
         <v>831</v>
       </c>
-      <c r="E21" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
-      <c r="A22" s="0">
-        <v>3</v>
-      </c>
-      <c r="B22" s="0">
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
         <v>5</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C22">
         <v>799.37055943669645</v>
       </c>
-      <c r="D22" s="0">
+      <c r="D22">
         <v>832.87694241073473</v>
       </c>
-      <c r="E22" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
-      <c r="A23" s="0">
-        <v>3</v>
-      </c>
-      <c r="B23" s="0">
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
         <v>6</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C23">
         <v>784</v>
       </c>
-      <c r="D23" s="0">
+      <c r="D23">
         <v>290</v>
       </c>
-      <c r="E23" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
-      <c r="A24" s="0">
-        <v>3</v>
-      </c>
-      <c r="B24" s="0">
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
         <v>7</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C24">
         <v>407.59998908096031</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D24">
         <v>290.18836282597613</v>
       </c>
-      <c r="E24" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
-      <c r="A25" s="0">
-        <v>3</v>
-      </c>
-      <c r="B25" s="0">
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
         <v>8</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C25">
         <v>417.52787151824356</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D25">
         <v>828.00000000000011</v>
       </c>
-      <c r="E25" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
-      <c r="A26" s="0">
-        <v>4</v>
-      </c>
-      <c r="B26" s="0">
-        <v>1</v>
-      </c>
-      <c r="C26" s="0">
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
         <v>1552</v>
       </c>
-      <c r="D26" s="0">
+      <c r="D26">
         <v>983</v>
       </c>
-      <c r="E26" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
-      <c r="A27" s="0">
-        <v>4</v>
-      </c>
-      <c r="B27" s="0">
-        <v>2</v>
-      </c>
-      <c r="C27" s="0">
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
         <v>1550.3355062255928</v>
       </c>
-      <c r="D27" s="0">
+      <c r="D27">
         <v>442.68324673024046</v>
       </c>
-      <c r="E27" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
-      <c r="A28" s="0">
-        <v>4</v>
-      </c>
-      <c r="B28" s="0">
-        <v>3</v>
-      </c>
-      <c r="C28" s="0">
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
         <v>1169</v>
       </c>
-      <c r="D28" s="0">
+      <c r="D28">
         <v>439.06282172105097</v>
       </c>
-      <c r="E28" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
-      <c r="A29" s="0">
-        <v>4</v>
-      </c>
-      <c r="B29" s="0">
-        <v>4</v>
-      </c>
-      <c r="C29" s="0">
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
         <v>1182.0510306101908</v>
       </c>
-      <c r="D29" s="0">
-        <v>981.25802220168635</v>
-      </c>
-      <c r="E29" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="0">
-        <v>4</v>
-      </c>
-      <c r="B30" s="0">
+      <c r="D29">
+        <v>981.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
         <v>5</v>
       </c>
-      <c r="C30" s="0">
+      <c r="C30">
         <v>803.28422113454724</v>
       </c>
-      <c r="D30" s="0">
+      <c r="D30">
         <v>978.28024475973484</v>
       </c>
-      <c r="E30" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
-      <c r="A31" s="0">
-        <v>4</v>
-      </c>
-      <c r="B31" s="0">
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
         <v>6</v>
       </c>
-      <c r="C31" s="0">
+      <c r="C31">
         <v>790.43600904846016</v>
       </c>
-      <c r="D31" s="0">
+      <c r="D31">
         <v>436.80569376586431</v>
       </c>
-      <c r="E31" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.2">
-      <c r="A32" s="0">
-        <v>4</v>
-      </c>
-      <c r="B32" s="0">
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C32" s="0">
+      <c r="C32">
         <v>408.48909359995025</v>
       </c>
-      <c r="D32" s="0">
+      <c r="D32">
         <v>436.47228629221291</v>
       </c>
-      <c r="E32" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.2">
-      <c r="A33" s="0">
-        <v>4</v>
-      </c>
-      <c r="B33" s="0">
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
         <v>8</v>
       </c>
-      <c r="C33" s="0">
+      <c r="C33">
         <v>428.68442286943787</v>
       </c>
-      <c r="D33" s="0">
-        <v>975.3292348100124</v>
-      </c>
-      <c r="E33" s="0">
+      <c r="D33">
+        <v>975.32923481001239</v>
+      </c>
+      <c r="E33">
         <v>65</v>
       </c>
     </row>
@@ -13533,7 +13539,4046 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C10DDB25-AF0C-8145-8F65-7A81F2AD1F00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C10DDB25-AF0C-8145-8F65-7A81F2AD1F00}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1710.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>865.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1701.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>330.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1335</v>
+      </c>
+      <c r="D4">
+        <v>325</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1342.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>868.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>970.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>868.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>954.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>322.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>575.83493585304359</v>
+      </c>
+      <c r="D8">
+        <v>321.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>583.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>866</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1703.8746535296575</v>
+      </c>
+      <c r="D10">
+        <v>1006.0845244489574</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1700.9734582162946</v>
+      </c>
+      <c r="D11">
+        <v>470</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1331.9999999999998</v>
+      </c>
+      <c r="D12">
+        <v>467</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1336.3493827116019</v>
+      </c>
+      <c r="D13">
+        <v>1012.3012493082249</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>964.52484896262547</v>
+      </c>
+      <c r="D14">
+        <v>1013.5206728589721</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>949.4076645902577</v>
+      </c>
+      <c r="D15">
+        <v>463.7948190298614</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>567.46508385439233</v>
+      </c>
+      <c r="D16">
+        <v>466.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>582</v>
+      </c>
+      <c r="D17">
+        <v>1006.0980695012088</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1561.3846762361873</v>
+      </c>
+      <c r="D18">
+        <v>850.182620379632</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1550.7054596333444</v>
+      </c>
+      <c r="D19">
+        <v>309.98346611431509</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1178.5063568822814</v>
+      </c>
+      <c r="D20">
+        <v>309.46121207422669</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1187.5494197876064</v>
+      </c>
+      <c r="D21">
+        <v>849</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>811.37055943669645</v>
+      </c>
+      <c r="D22">
+        <v>850.87694241073473</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>796</v>
+      </c>
+      <c r="D23">
+        <v>308</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>419.59998908096031</v>
+      </c>
+      <c r="D24">
+        <v>308.18836282597613</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>429.52787151824356</v>
+      </c>
+      <c r="D25">
+        <v>846.00000000000011</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1555</v>
+      </c>
+      <c r="D26">
+        <v>993</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1553.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>452.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1172</v>
+      </c>
+      <c r="D28">
+        <v>449.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1185.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>991.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>806.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>988.28024475973484</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>793.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>446.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>411.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>446.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>431.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>985.32923481001239</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3762F5-3A42-1A45-977B-E61EF4F43B9D}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1709.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>858.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1700.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>323.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1334</v>
+      </c>
+      <c r="D4">
+        <v>318</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1341.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>861.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>969.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>861.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>953.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>315.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>574.83493585304359</v>
+      </c>
+      <c r="D8">
+        <v>314.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>582.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>859</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1701.8746535296575</v>
+      </c>
+      <c r="D10">
+        <v>996.08452444895738</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1698.9734582162946</v>
+      </c>
+      <c r="D11">
+        <v>460</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1329.9999999999998</v>
+      </c>
+      <c r="D12">
+        <v>457</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1334.3493827116019</v>
+      </c>
+      <c r="D13">
+        <v>1002.3012493082249</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>962.52484896262547</v>
+      </c>
+      <c r="D14">
+        <v>1003.5206728589721</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>947.4076645902577</v>
+      </c>
+      <c r="D15">
+        <v>453.7948190298614</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>565.46508385439233</v>
+      </c>
+      <c r="D16">
+        <v>456.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>580</v>
+      </c>
+      <c r="D17">
+        <v>996.09806950120878</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1557.3846762361873</v>
+      </c>
+      <c r="D18">
+        <v>842.182620379632</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1546.7054596333444</v>
+      </c>
+      <c r="D19">
+        <v>301.98346611431509</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1174.5063568822814</v>
+      </c>
+      <c r="D20">
+        <v>301.46121207422669</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1183.5494197876064</v>
+      </c>
+      <c r="D21">
+        <v>841</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>807.37055943669645</v>
+      </c>
+      <c r="D22">
+        <v>842.87694241073473</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>792</v>
+      </c>
+      <c r="D23">
+        <v>300</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>415.59998908096031</v>
+      </c>
+      <c r="D24">
+        <v>300.18836282597613</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>425.52787151824356</v>
+      </c>
+      <c r="D25">
+        <v>838.00000000000011</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1553</v>
+      </c>
+      <c r="D26">
+        <v>993</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1551.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>452.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1170</v>
+      </c>
+      <c r="D28">
+        <v>449.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1183.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>991.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>804.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>988.28024475973484</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>791.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>446.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>409.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>446.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>429.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>985.32923481001239</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9F95D3-5ADE-714F-8156-75EBF89DAD2E}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1709.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>868.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1700.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>333.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1334</v>
+      </c>
+      <c r="D4">
+        <v>328</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1341.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>871.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>969.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>871.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>953.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>325.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>574.83493585304359</v>
+      </c>
+      <c r="D8">
+        <v>324.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>582.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>869</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1701.8746535296575</v>
+      </c>
+      <c r="D10">
+        <v>1010.0845244489574</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1698.9734582162946</v>
+      </c>
+      <c r="D11">
+        <v>474</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1329.9999999999998</v>
+      </c>
+      <c r="D12">
+        <v>471</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1334.3493827116019</v>
+      </c>
+      <c r="D13">
+        <v>1016.3012493082249</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>962.52484896262547</v>
+      </c>
+      <c r="D14">
+        <v>1017.5206728589721</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>947.4076645902577</v>
+      </c>
+      <c r="D15">
+        <v>467.7948190298614</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>565.46508385439233</v>
+      </c>
+      <c r="D16">
+        <v>470.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>580</v>
+      </c>
+      <c r="D17">
+        <v>1010.0980695012088</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1557.3846762361873</v>
+      </c>
+      <c r="D18">
+        <v>855.182620379632</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1546.7054596333444</v>
+      </c>
+      <c r="D19">
+        <v>314.98346611431509</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1174.5063568822814</v>
+      </c>
+      <c r="D20">
+        <v>314.46121207422669</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1183.5494197876064</v>
+      </c>
+      <c r="D21">
+        <v>854</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>807.37055943669645</v>
+      </c>
+      <c r="D22">
+        <v>855.87694241073473</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>792</v>
+      </c>
+      <c r="D23">
+        <v>313</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>415.59998908096031</v>
+      </c>
+      <c r="D24">
+        <v>313.18836282597613</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>425.52787151824356</v>
+      </c>
+      <c r="D25">
+        <v>851.00000000000011</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1553</v>
+      </c>
+      <c r="D26">
+        <v>993</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1551.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>452.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1170</v>
+      </c>
+      <c r="D28">
+        <v>449.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1183.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>991.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>804.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>988.28024475973484</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>791.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>446.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>409.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>446.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>429.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>985.32923481001239</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D226DA5-9779-DA4D-9B32-DE369CEE8095}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1709.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>868.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1700.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>333.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1334</v>
+      </c>
+      <c r="D4">
+        <v>328</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1341.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>871.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>969.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>871.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>953.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>325.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>574.83493585304359</v>
+      </c>
+      <c r="D8">
+        <v>324.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>582.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>869</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1701.8746535296575</v>
+      </c>
+      <c r="D10">
+        <v>1010.0845244489574</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1698.9734582162946</v>
+      </c>
+      <c r="D11">
+        <v>474</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1329.9999999999998</v>
+      </c>
+      <c r="D12">
+        <v>471</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1334.3493827116019</v>
+      </c>
+      <c r="D13">
+        <v>1016.3012493082249</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>962.52484896262547</v>
+      </c>
+      <c r="D14">
+        <v>1017.5206728589721</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>947.4076645902577</v>
+      </c>
+      <c r="D15">
+        <v>467.7948190298614</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>565.46508385439233</v>
+      </c>
+      <c r="D16">
+        <v>470.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>580</v>
+      </c>
+      <c r="D17">
+        <v>1010.0980695012088</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1557.3846762361873</v>
+      </c>
+      <c r="D18">
+        <v>855.182620379632</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1546.7054596333444</v>
+      </c>
+      <c r="D19">
+        <v>314.98346611431509</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1174.5063568822814</v>
+      </c>
+      <c r="D20">
+        <v>314.46121207422669</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1183.5494197876064</v>
+      </c>
+      <c r="D21">
+        <v>854</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>807.37055943669645</v>
+      </c>
+      <c r="D22">
+        <v>855.87694241073473</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>792</v>
+      </c>
+      <c r="D23">
+        <v>313</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>415.59998908096031</v>
+      </c>
+      <c r="D24">
+        <v>313.18836282597613</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>425.52787151824356</v>
+      </c>
+      <c r="D25">
+        <v>851.00000000000011</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1553</v>
+      </c>
+      <c r="D26">
+        <v>993</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1551.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>452.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1170</v>
+      </c>
+      <c r="D28">
+        <v>449.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1183.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>991.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>804.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>988.28024475973484</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>791.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>446.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>409.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>446.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>429.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>985.32923481001239</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7747300-B6E9-AE4F-B080-F6AEE57C78D6}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1709.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>868.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1700.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>333.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1334</v>
+      </c>
+      <c r="D4">
+        <v>328</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1341.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>871.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>969.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>871.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>953.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>325.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>574.83493585304359</v>
+      </c>
+      <c r="D8">
+        <v>324.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>582.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>869</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1701.8746535296575</v>
+      </c>
+      <c r="D10">
+        <v>1010.0845244489574</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1698.9734582162946</v>
+      </c>
+      <c r="D11">
+        <v>474</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1329.9999999999998</v>
+      </c>
+      <c r="D12">
+        <v>471</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1334.3493827116019</v>
+      </c>
+      <c r="D13">
+        <v>1016.3012493082249</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>962.52484896262547</v>
+      </c>
+      <c r="D14">
+        <v>1017.5206728589721</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>947.4076645902577</v>
+      </c>
+      <c r="D15">
+        <v>467.7948190298614</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>565.46508385439233</v>
+      </c>
+      <c r="D16">
+        <v>470.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>580</v>
+      </c>
+      <c r="D17">
+        <v>1010.0980695012088</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1557.3846762361873</v>
+      </c>
+      <c r="D18">
+        <v>855.182620379632</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1546.7054596333444</v>
+      </c>
+      <c r="D19">
+        <v>314.98346611431509</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1174.5063568822814</v>
+      </c>
+      <c r="D20">
+        <v>314.46121207422669</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1183.5494197876064</v>
+      </c>
+      <c r="D21">
+        <v>854</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>807.37055943669645</v>
+      </c>
+      <c r="D22">
+        <v>855.87694241073473</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>792</v>
+      </c>
+      <c r="D23">
+        <v>313</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>415.59998908096031</v>
+      </c>
+      <c r="D24">
+        <v>313.18836282597613</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>425.52787151824356</v>
+      </c>
+      <c r="D25">
+        <v>851.00000000000011</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1553</v>
+      </c>
+      <c r="D26">
+        <v>993</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1551.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>452.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1170</v>
+      </c>
+      <c r="D28">
+        <v>449.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1183.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>991.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>804.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>988.28024475973484</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>791.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>446.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>409.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>446.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>429.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>985.32923481001239</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFDDB1FA-E0F7-A243-A534-650EA217BF3A}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1709.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>868.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1700.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>333.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1334</v>
+      </c>
+      <c r="D4">
+        <v>328</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1341.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>871.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>969.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>871.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>953.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>325.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>574.83493585304359</v>
+      </c>
+      <c r="D8">
+        <v>324.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>582.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>869</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1701.8746535296575</v>
+      </c>
+      <c r="D10">
+        <v>1010.0845244489574</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1698.9734582162946</v>
+      </c>
+      <c r="D11">
+        <v>474</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1329.9999999999998</v>
+      </c>
+      <c r="D12">
+        <v>471</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1334.3493827116019</v>
+      </c>
+      <c r="D13">
+        <v>1016.3012493082249</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>962.52484896262547</v>
+      </c>
+      <c r="D14">
+        <v>1017.5206728589721</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>947.4076645902577</v>
+      </c>
+      <c r="D15">
+        <v>467.7948190298614</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>565.46508385439233</v>
+      </c>
+      <c r="D16">
+        <v>470.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>580</v>
+      </c>
+      <c r="D17">
+        <v>1010.0980695012088</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1557.3846762361873</v>
+      </c>
+      <c r="D18">
+        <v>855.182620379632</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1546.7054596333444</v>
+      </c>
+      <c r="D19">
+        <v>314.98346611431509</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1174.5063568822814</v>
+      </c>
+      <c r="D20">
+        <v>314.46121207422669</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1183.5494197876064</v>
+      </c>
+      <c r="D21">
+        <v>854</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>807.37055943669645</v>
+      </c>
+      <c r="D22">
+        <v>855.87694241073473</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>792</v>
+      </c>
+      <c r="D23">
+        <v>313</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>415.59998908096031</v>
+      </c>
+      <c r="D24">
+        <v>313.18836282597613</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>425.52787151824356</v>
+      </c>
+      <c r="D25">
+        <v>851.00000000000011</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1553</v>
+      </c>
+      <c r="D26">
+        <v>993</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1551.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>452.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1170</v>
+      </c>
+      <c r="D28">
+        <v>449.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1183.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>991.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>804.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>988.28024475973484</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>791.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>446.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>409.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>446.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>429.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>985.32923481001239</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{021B0B65-BC3B-1D48-B26E-9B79F00E2B9B}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1709.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>868.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1700.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>333.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1334</v>
+      </c>
+      <c r="D4">
+        <v>328</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1341.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>871.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>969.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>871.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>953.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>325.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>574.83493585304359</v>
+      </c>
+      <c r="D8">
+        <v>324.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>582.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>869</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1701.8746535296575</v>
+      </c>
+      <c r="D10">
+        <v>1010.0845244489574</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1698.9734582162946</v>
+      </c>
+      <c r="D11">
+        <v>474</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1329.9999999999998</v>
+      </c>
+      <c r="D12">
+        <v>471</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1334.3493827116019</v>
+      </c>
+      <c r="D13">
+        <v>1016.3012493082249</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>962.52484896262547</v>
+      </c>
+      <c r="D14">
+        <v>1017.5206728589721</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>947.4076645902577</v>
+      </c>
+      <c r="D15">
+        <v>467.7948190298614</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>565.46508385439233</v>
+      </c>
+      <c r="D16">
+        <v>470.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>580</v>
+      </c>
+      <c r="D17">
+        <v>1010.0980695012088</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1557.3846762361873</v>
+      </c>
+      <c r="D18">
+        <v>855.182620379632</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1546.7054596333444</v>
+      </c>
+      <c r="D19">
+        <v>314.98346611431509</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1174.5063568822814</v>
+      </c>
+      <c r="D20">
+        <v>314.46121207422669</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1183.5494197876064</v>
+      </c>
+      <c r="D21">
+        <v>854</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>807.37055943669645</v>
+      </c>
+      <c r="D22">
+        <v>855.87694241073473</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>792</v>
+      </c>
+      <c r="D23">
+        <v>313</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>415.59998908096031</v>
+      </c>
+      <c r="D24">
+        <v>313.18836282597613</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>425.52787151824356</v>
+      </c>
+      <c r="D25">
+        <v>851.00000000000011</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1553</v>
+      </c>
+      <c r="D26">
+        <v>993</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1551.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>452.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1170</v>
+      </c>
+      <c r="D28">
+        <v>449.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1183.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>991.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>804.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>988.28024475973484</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>791.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>446.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>409.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>446.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>429.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>985.32923481001239</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B23506-DAD4-7041-B918-D3529AC8BB67}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -13569,10 +17614,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="0">
-        <v>1710.7425030099457</v>
+        <v>1556</v>
       </c>
       <c r="D2" s="0">
-        <v>865.02871194456884</v>
+        <v>998</v>
       </c>
       <c r="E2" s="0">
         <v>65</v>
@@ -13586,10 +17631,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="0">
-        <v>1701.4061483041658</v>
+        <v>1554.3355062255928</v>
       </c>
       <c r="D3" s="0">
-        <v>330.32671346786896</v>
+        <v>457.68324673024046</v>
       </c>
       <c r="E3" s="0">
         <v>65</v>
@@ -13603,10 +17648,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="0">
-        <v>1335</v>
+        <v>1173</v>
       </c>
       <c r="D4" s="0">
-        <v>325</v>
+        <v>454.06282172105097</v>
       </c>
       <c r="E4" s="0">
         <v>65</v>
@@ -13620,10 +17665,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="0">
-        <v>1342.520209029972</v>
+        <v>1186.0510306101908</v>
       </c>
       <c r="D5" s="0">
-        <v>868.01460290365162</v>
+        <v>996.25802220168635</v>
       </c>
       <c r="E5" s="0">
         <v>65</v>
@@ -13637,10 +17682,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="0">
-        <v>970.62459762139895</v>
+        <v>807.28422113454724</v>
       </c>
       <c r="D6" s="0">
-        <v>868.04376388709545</v>
+        <v>993.28024475973484</v>
       </c>
       <c r="E6" s="0">
         <v>65</v>
@@ -13654,10 +17699,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="0">
-        <v>954.28458590452396</v>
+        <v>794.43600904846016</v>
       </c>
       <c r="D7" s="0">
-        <v>322.24413555490423</v>
+        <v>451.80569376586431</v>
       </c>
       <c r="E7" s="0">
         <v>65</v>
@@ -13671,10 +17716,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="0">
-        <v>575.83493585304359</v>
+        <v>412.48909359995025</v>
       </c>
       <c r="D8" s="0">
-        <v>321.79972769377798</v>
+        <v>451.47228629221291</v>
       </c>
       <c r="E8" s="0">
         <v>65</v>
@@ -13688,10 +17733,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="0">
-        <v>583.0101420458949</v>
+        <v>432.68442286943787</v>
       </c>
       <c r="D9" s="0">
-        <v>866</v>
+        <v>990.3292348100124</v>
       </c>
       <c r="E9" s="0">
         <v>65</v>
@@ -13705,10 +17750,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="0">
-        <v>1703.8746535296575</v>
+        <v>1699.8746535296575</v>
       </c>
       <c r="D10" s="0">
-        <v>1006.0845244489574</v>
+        <v>995.08452444895738</v>
       </c>
       <c r="E10" s="0">
         <v>65</v>
@@ -13722,10 +17767,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="0">
-        <v>1700.9734582162946</v>
+        <v>1696.9734582162946</v>
       </c>
       <c r="D11" s="0">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="E11" s="0">
         <v>65</v>
@@ -13739,10 +17784,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="0">
-        <v>1331.9999999999998</v>
+        <v>1327.9999999999998</v>
       </c>
       <c r="D12" s="0">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="E12" s="0">
         <v>65</v>
@@ -13756,10 +17801,10 @@
         <v>4</v>
       </c>
       <c r="C13" s="0">
-        <v>1336.3493827116019</v>
+        <v>1332.3493827116019</v>
       </c>
       <c r="D13" s="0">
-        <v>1012.3012493082249</v>
+        <v>1001.3012493082249</v>
       </c>
       <c r="E13" s="0">
         <v>65</v>
@@ -13773,10 +17818,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="0">
-        <v>964.52484896262547</v>
+        <v>960.52484896262547</v>
       </c>
       <c r="D14" s="0">
-        <v>1013.5206728589721</v>
+        <v>1002.5206728589721</v>
       </c>
       <c r="E14" s="0">
         <v>65</v>
@@ -13790,10 +17835,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="0">
-        <v>949.4076645902577</v>
+        <v>945.4076645902577</v>
       </c>
       <c r="D15" s="0">
-        <v>463.7948190298614</v>
+        <v>452.7948190298614</v>
       </c>
       <c r="E15" s="0">
         <v>65</v>
@@ -13807,10 +17852,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="0">
-        <v>567.46508385439233</v>
+        <v>563.46508385439233</v>
       </c>
       <c r="D16" s="0">
-        <v>466.44557641723191</v>
+        <v>455.44557641723191</v>
       </c>
       <c r="E16" s="0">
         <v>65</v>
@@ -13824,10 +17869,10 @@
         <v>8</v>
       </c>
       <c r="C17" s="0">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D17" s="0">
-        <v>1006.0980695012088</v>
+        <v>995.09806950120878</v>
       </c>
       <c r="E17" s="0">
         <v>65</v>
@@ -13841,10 +17886,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="0">
-        <v>1561.3846762361873</v>
+        <v>1560.3846762361873</v>
       </c>
       <c r="D18" s="0">
-        <v>850.182620379632</v>
+        <v>842.182620379632</v>
       </c>
       <c r="E18" s="0">
         <v>65</v>
@@ -13858,10 +17903,10 @@
         <v>2</v>
       </c>
       <c r="C19" s="0">
-        <v>1550.7054596333444</v>
+        <v>1549.7054596333444</v>
       </c>
       <c r="D19" s="0">
-        <v>309.98346611431509</v>
+        <v>301.98346611431509</v>
       </c>
       <c r="E19" s="0">
         <v>65</v>
@@ -13875,10 +17920,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="0">
-        <v>1178.5063568822814</v>
+        <v>1177.5063568822814</v>
       </c>
       <c r="D20" s="0">
-        <v>309.46121207422669</v>
+        <v>301.46121207422669</v>
       </c>
       <c r="E20" s="0">
         <v>65</v>
@@ -13892,10 +17937,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="0">
-        <v>1187.5494197876064</v>
+        <v>1186.5494197876064</v>
       </c>
       <c r="D21" s="0">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="E21" s="0">
         <v>65</v>
@@ -13909,10 +17954,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="0">
-        <v>811.37055943669645</v>
+        <v>810.37055943669645</v>
       </c>
       <c r="D22" s="0">
-        <v>850.87694241073473</v>
+        <v>842.87694241073473</v>
       </c>
       <c r="E22" s="0">
         <v>65</v>
@@ -13926,10 +17971,10 @@
         <v>6</v>
       </c>
       <c r="C23" s="0">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D23" s="0">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E23" s="0">
         <v>65</v>
@@ -13943,10 +17988,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="0">
-        <v>419.59998908096031</v>
+        <v>418.59998908096031</v>
       </c>
       <c r="D24" s="0">
-        <v>308.18836282597613</v>
+        <v>300.18836282597613</v>
       </c>
       <c r="E24" s="0">
         <v>65</v>
@@ -13960,10 +18005,10 @@
         <v>8</v>
       </c>
       <c r="C25" s="0">
-        <v>429.52787151824356</v>
+        <v>428.52787151824356</v>
       </c>
       <c r="D25" s="0">
-        <v>846.00000000000011</v>
+        <v>838.00000000000011</v>
       </c>
       <c r="E25" s="0">
         <v>65</v>
@@ -13977,10 +18022,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="0">
-        <v>1555</v>
+        <v>1705.7425030099457</v>
       </c>
       <c r="D26" s="0">
-        <v>993</v>
+        <v>854.02871194456884</v>
       </c>
       <c r="E26" s="0">
         <v>65</v>
@@ -13994,10 +18039,10 @@
         <v>2</v>
       </c>
       <c r="C27" s="0">
-        <v>1553.3355062255928</v>
+        <v>1696.4061483041658</v>
       </c>
       <c r="D27" s="0">
-        <v>452.68324673024046</v>
+        <v>319.32671346786896</v>
       </c>
       <c r="E27" s="0">
         <v>65</v>
@@ -14011,10 +18056,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="0">
-        <v>1172</v>
+        <v>1330</v>
       </c>
       <c r="D28" s="0">
-        <v>449.06282172105097</v>
+        <v>314</v>
       </c>
       <c r="E28" s="0">
         <v>65</v>
@@ -14028,10 +18073,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="0">
-        <v>1185.0510306101908</v>
+        <v>1337.520209029972</v>
       </c>
       <c r="D29" s="0">
-        <v>991.25802220168635</v>
+        <v>857.01460290365162</v>
       </c>
       <c r="E29" s="0">
         <v>65</v>
@@ -14045,10 +18090,10 @@
         <v>5</v>
       </c>
       <c r="C30" s="0">
-        <v>806.28422113454724</v>
+        <v>965.62459762139895</v>
       </c>
       <c r="D30" s="0">
-        <v>988.28024475973484</v>
+        <v>857.04376388709545</v>
       </c>
       <c r="E30" s="0">
         <v>65</v>
@@ -14062,10 +18107,10 @@
         <v>6</v>
       </c>
       <c r="C31" s="0">
-        <v>793.43600904846016</v>
+        <v>949.28458590452396</v>
       </c>
       <c r="D31" s="0">
-        <v>446.80569376586431</v>
+        <v>311.24413555490423</v>
       </c>
       <c r="E31" s="0">
         <v>65</v>
@@ -14079,10 +18124,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="0">
-        <v>411.48909359995025</v>
+        <v>570.83493585304359</v>
       </c>
       <c r="D32" s="0">
-        <v>446.47228629221291</v>
+        <v>310.79972769377798</v>
       </c>
       <c r="E32" s="0">
         <v>65</v>
@@ -14096,10 +18141,10 @@
         <v>8</v>
       </c>
       <c r="C33" s="0">
-        <v>431.68442286943787</v>
+        <v>578.0101420458949</v>
       </c>
       <c r="D33" s="0">
-        <v>985.3292348100124</v>
+        <v>855</v>
       </c>
       <c r="E33" s="0">
         <v>65</v>
@@ -14110,8 +18155,585 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3762F5-3A42-1A45-977B-E61EF4F43B9D}">
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59420751-9065-0949-A4BF-D6E5C59A0E13}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1709.7425030099457</v>
+      </c>
+      <c r="D2">
+        <v>868.02871194456884</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1700.4061483041658</v>
+      </c>
+      <c r="D3">
+        <v>333.32671346786896</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1334</v>
+      </c>
+      <c r="D4">
+        <v>328</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1341.520209029972</v>
+      </c>
+      <c r="D5">
+        <v>871.01460290365162</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>969.62459762139895</v>
+      </c>
+      <c r="D6">
+        <v>871.04376388709545</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>953.28458590452396</v>
+      </c>
+      <c r="D7">
+        <v>325.24413555490423</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>574.83493585304359</v>
+      </c>
+      <c r="D8">
+        <v>324.79972769377798</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>582.0101420458949</v>
+      </c>
+      <c r="D9">
+        <v>869</v>
+      </c>
+      <c r="E9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1701.8746535296575</v>
+      </c>
+      <c r="D10">
+        <v>1010.0845244489574</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>1698.9734582162946</v>
+      </c>
+      <c r="D11">
+        <v>474</v>
+      </c>
+      <c r="E11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>1329.9999999999998</v>
+      </c>
+      <c r="D12">
+        <v>471</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>1334.3493827116019</v>
+      </c>
+      <c r="D13">
+        <v>1016.3012493082249</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>962.52484896262547</v>
+      </c>
+      <c r="D14">
+        <v>1017.5206728589721</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>947.4076645902577</v>
+      </c>
+      <c r="D15">
+        <v>467.7948190298614</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>565.46508385439233</v>
+      </c>
+      <c r="D16">
+        <v>470.4455764172319</v>
+      </c>
+      <c r="E16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>580</v>
+      </c>
+      <c r="D17">
+        <v>1010.0980695012088</v>
+      </c>
+      <c r="E17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1557.3846762361873</v>
+      </c>
+      <c r="D18">
+        <v>855.182620379632</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1546.7054596333444</v>
+      </c>
+      <c r="D19">
+        <v>314.98346611431509</v>
+      </c>
+      <c r="E19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1174.5063568822814</v>
+      </c>
+      <c r="D20">
+        <v>314.46121207422669</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1183.5494197876064</v>
+      </c>
+      <c r="D21">
+        <v>854</v>
+      </c>
+      <c r="E21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>807.37055943669645</v>
+      </c>
+      <c r="D22">
+        <v>855.87694241073473</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>792</v>
+      </c>
+      <c r="D23">
+        <v>313</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>415.59998908096031</v>
+      </c>
+      <c r="D24">
+        <v>313.18836282597613</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>425.52787151824356</v>
+      </c>
+      <c r="D25">
+        <v>851.00000000000011</v>
+      </c>
+      <c r="E25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1553</v>
+      </c>
+      <c r="D26">
+        <v>993</v>
+      </c>
+      <c r="E26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1551.3355062255928</v>
+      </c>
+      <c r="D27">
+        <v>452.68324673024046</v>
+      </c>
+      <c r="E27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>1170</v>
+      </c>
+      <c r="D28">
+        <v>449.06282172105097</v>
+      </c>
+      <c r="E28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1183.0510306101908</v>
+      </c>
+      <c r="D29">
+        <v>991.25802220168634</v>
+      </c>
+      <c r="E29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>804.28422113454724</v>
+      </c>
+      <c r="D30">
+        <v>988.28024475973484</v>
+      </c>
+      <c r="E30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>791.43600904846016</v>
+      </c>
+      <c r="D31">
+        <v>446.80569376586431</v>
+      </c>
+      <c r="E31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>409.48909359995025</v>
+      </c>
+      <c r="D32">
+        <v>446.47228629221291</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>429.68442286943787</v>
+      </c>
+      <c r="D33">
+        <v>985.32923481001239</v>
+      </c>
+      <c r="E33">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A2CD3C4-E7FD-774F-8AE8-57C6E0420AB1}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -14150,7 +18772,7 @@
         <v>1709.7425030099457</v>
       </c>
       <c r="D2" s="0">
-        <v>858.02871194456884</v>
+        <v>875.02871194456884</v>
       </c>
       <c r="E2" s="0">
         <v>65</v>
@@ -14167,7 +18789,7 @@
         <v>1700.4061483041658</v>
       </c>
       <c r="D3" s="0">
-        <v>323.32671346786896</v>
+        <v>340.32671346786896</v>
       </c>
       <c r="E3" s="0">
         <v>65</v>
@@ -14184,7 +18806,7 @@
         <v>1334</v>
       </c>
       <c r="D4" s="0">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="E4" s="0">
         <v>65</v>
@@ -14201,7 +18823,7 @@
         <v>1341.520209029972</v>
       </c>
       <c r="D5" s="0">
-        <v>861.01460290365162</v>
+        <v>878.01460290365162</v>
       </c>
       <c r="E5" s="0">
         <v>65</v>
@@ -14218,7 +18840,7 @@
         <v>969.62459762139895</v>
       </c>
       <c r="D6" s="0">
-        <v>861.04376388709545</v>
+        <v>878.04376388709545</v>
       </c>
       <c r="E6" s="0">
         <v>65</v>
@@ -14235,7 +18857,7 @@
         <v>953.28458590452396</v>
       </c>
       <c r="D7" s="0">
-        <v>315.24413555490423</v>
+        <v>332.24413555490423</v>
       </c>
       <c r="E7" s="0">
         <v>65</v>
@@ -14252,7 +18874,7 @@
         <v>574.83493585304359</v>
       </c>
       <c r="D8" s="0">
-        <v>314.79972769377798</v>
+        <v>331.79972769377798</v>
       </c>
       <c r="E8" s="0">
         <v>65</v>
@@ -14269,7 +18891,7 @@
         <v>582.0101420458949</v>
       </c>
       <c r="D9" s="0">
-        <v>859</v>
+        <v>876</v>
       </c>
       <c r="E9" s="0">
         <v>65</v>
@@ -14286,7 +18908,7 @@
         <v>1701.8746535296575</v>
       </c>
       <c r="D10" s="0">
-        <v>996.08452444895738</v>
+        <v>1010.0845244489574</v>
       </c>
       <c r="E10" s="0">
         <v>65</v>
@@ -14303,7 +18925,7 @@
         <v>1698.9734582162946</v>
       </c>
       <c r="D11" s="0">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="E11" s="0">
         <v>65</v>
@@ -14320,7 +18942,7 @@
         <v>1329.9999999999998</v>
       </c>
       <c r="D12" s="0">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="E12" s="0">
         <v>65</v>
@@ -14337,7 +18959,7 @@
         <v>1334.3493827116019</v>
       </c>
       <c r="D13" s="0">
-        <v>1002.3012493082249</v>
+        <v>1016.3012493082249</v>
       </c>
       <c r="E13" s="0">
         <v>65</v>
@@ -14354,7 +18976,7 @@
         <v>962.52484896262547</v>
       </c>
       <c r="D14" s="0">
-        <v>1003.5206728589721</v>
+        <v>1017.5206728589721</v>
       </c>
       <c r="E14" s="0">
         <v>65</v>
@@ -14371,7 +18993,7 @@
         <v>947.4076645902577</v>
       </c>
       <c r="D15" s="0">
-        <v>453.7948190298614</v>
+        <v>467.7948190298614</v>
       </c>
       <c r="E15" s="0">
         <v>65</v>
@@ -14388,7 +19010,7 @@
         <v>565.46508385439233</v>
       </c>
       <c r="D16" s="0">
-        <v>456.44557641723191</v>
+        <v>470.44557641723191</v>
       </c>
       <c r="E16" s="0">
         <v>65</v>
@@ -14405,7 +19027,7 @@
         <v>580</v>
       </c>
       <c r="D17" s="0">
-        <v>996.09806950120878</v>
+        <v>1010.0980695012088</v>
       </c>
       <c r="E17" s="0">
         <v>65</v>
@@ -14422,7 +19044,7 @@
         <v>1557.3846762361873</v>
       </c>
       <c r="D18" s="0">
-        <v>842.182620379632</v>
+        <v>855.182620379632</v>
       </c>
       <c r="E18" s="0">
         <v>65</v>
@@ -14439,7 +19061,7 @@
         <v>1546.7054596333444</v>
       </c>
       <c r="D19" s="0">
-        <v>301.98346611431509</v>
+        <v>314.98346611431509</v>
       </c>
       <c r="E19" s="0">
         <v>65</v>
@@ -14456,7 +19078,7 @@
         <v>1174.5063568822814</v>
       </c>
       <c r="D20" s="0">
-        <v>301.46121207422669</v>
+        <v>314.46121207422669</v>
       </c>
       <c r="E20" s="0">
         <v>65</v>
@@ -14473,7 +19095,7 @@
         <v>1183.5494197876064</v>
       </c>
       <c r="D21" s="0">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="E21" s="0">
         <v>65</v>
@@ -14490,7 +19112,7 @@
         <v>807.37055943669645</v>
       </c>
       <c r="D22" s="0">
-        <v>842.87694241073473</v>
+        <v>855.87694241073473</v>
       </c>
       <c r="E22" s="0">
         <v>65</v>
@@ -14507,7 +19129,7 @@
         <v>792</v>
       </c>
       <c r="D23" s="0">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="E23" s="0">
         <v>65</v>
@@ -14524,7 +19146,7 @@
         <v>415.59998908096031</v>
       </c>
       <c r="D24" s="0">
-        <v>300.18836282597613</v>
+        <v>313.18836282597613</v>
       </c>
       <c r="E24" s="0">
         <v>65</v>
@@ -14541,7 +19163,7 @@
         <v>425.52787151824356</v>
       </c>
       <c r="D25" s="0">
-        <v>838.00000000000011</v>
+        <v>851.00000000000011</v>
       </c>
       <c r="E25" s="0">
         <v>65</v>
